--- a/eta-giocatori.xlsx
+++ b/eta-giocatori.xlsx
@@ -3,7 +3,7 @@
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
   <workbookPr codeName="ThisWorkbook"/>
   <sheets>
-    <sheet name="Svincolati" sheetId="1" r:id="rId1"/>
+    <sheet name="Lista calciatori" sheetId="1" r:id="rId1"/>
   </sheets>
 </workbook>
 </file>
@@ -409,7 +409,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:N514"/>
+  <dimension ref="A1:L522"/>
   <sheetData>
     <row r="1">
       <c r="A1" s="2" t="str">
@@ -448,12 +448,6 @@
       <c r="L1" s="2" t="str">
         <v>QUOT.</v>
       </c>
-      <c r="M1" s="2" t="str">
-        <v>FantaSquadra</v>
-      </c>
-      <c r="N1" s="2" t="str">
-        <v>Costo</v>
-      </c>
     </row>
     <row r="2">
       <c r="A2" s="2">
@@ -2585,25 +2579,25 @@
     </row>
     <row r="58">
       <c r="A58" s="2">
-        <v>7484</v>
+        <v>4964</v>
       </c>
       <c r="B58" s="2" t="str">
-        <v>Adams A.</v>
+        <v>Vicario</v>
       </c>
       <c r="C58" s="2" t="str">
         <v/>
       </c>
       <c r="D58" s="2" t="str">
-        <v>Venezia</v>
+        <v>Juventus</v>
       </c>
       <c r="E58" s="2">
-        <v>26</v>
+        <v>30</v>
       </c>
       <c r="F58" s="2" t="str">
-        <v>A</v>
+        <v>P</v>
       </c>
       <c r="G58" s="2" t="str">
-        <v>Pc</v>
+        <v>Por</v>
       </c>
       <c r="H58" s="2">
         <v>0</v>
@@ -2615,33 +2609,33 @@
         <v>0</v>
       </c>
       <c r="K58" s="2">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="L58" s="2">
-        <v>11</v>
+        <v>16</v>
       </c>
     </row>
     <row r="59">
       <c r="A59" s="2">
-        <v>6967</v>
+        <v>7484</v>
       </c>
       <c r="B59" s="2" t="str">
-        <v>Diao</v>
+        <v>Adams A.</v>
       </c>
       <c r="C59" s="2" t="str">
         <v/>
       </c>
       <c r="D59" s="2" t="str">
-        <v>Como</v>
+        <v>Venezia</v>
       </c>
       <c r="E59" s="2">
-        <v>21</v>
+        <v>26</v>
       </c>
       <c r="F59" s="2" t="str">
         <v>A</v>
       </c>
       <c r="G59" s="2" t="str">
-        <v>W/A</v>
+        <v>Pc</v>
       </c>
       <c r="H59" s="2">
         <v>0</v>
@@ -2656,30 +2650,30 @@
         <v>12</v>
       </c>
       <c r="L59" s="2">
-        <v>12</v>
+        <v>11</v>
       </c>
     </row>
     <row r="60">
       <c r="A60" s="2">
-        <v>2038</v>
+        <v>6967</v>
       </c>
       <c r="B60" s="2" t="str">
-        <v>Pinamonti</v>
+        <v>Diao</v>
       </c>
       <c r="C60" s="2" t="str">
         <v/>
       </c>
       <c r="D60" s="2" t="str">
-        <v>Sassuolo</v>
+        <v>Como</v>
       </c>
       <c r="E60" s="2">
-        <v>27</v>
+        <v>21</v>
       </c>
       <c r="F60" s="2" t="str">
         <v>A</v>
       </c>
       <c r="G60" s="2" t="str">
-        <v>Pc</v>
+        <v>W/A</v>
       </c>
       <c r="H60" s="2">
         <v>0</v>
@@ -2699,25 +2693,25 @@
     </row>
     <row r="61">
       <c r="A61" s="2">
-        <v>5792</v>
+        <v>2038</v>
       </c>
       <c r="B61" s="2" t="str">
-        <v>Ederson D.S.</v>
+        <v>Pinamonti</v>
       </c>
       <c r="C61" s="2" t="str">
         <v/>
       </c>
       <c r="D61" s="2" t="str">
-        <v>Atalanta</v>
+        <v>Sassuolo</v>
       </c>
       <c r="E61" s="2">
         <v>27</v>
       </c>
       <c r="F61" s="2" t="str">
-        <v>C</v>
+        <v>A</v>
       </c>
       <c r="G61" s="2" t="str">
-        <v>M/C</v>
+        <v>Pc</v>
       </c>
       <c r="H61" s="2">
         <v>0</v>
@@ -2732,30 +2726,30 @@
         <v>12</v>
       </c>
       <c r="L61" s="2">
-        <v>13</v>
+        <v>12</v>
       </c>
     </row>
     <row r="62">
       <c r="A62" s="2">
-        <v>5022</v>
+        <v>5792</v>
       </c>
       <c r="B62" s="2" t="str">
-        <v>Pavlovic</v>
+        <v>Ederson D.S.</v>
       </c>
       <c r="C62" s="2" t="str">
         <v/>
       </c>
       <c r="D62" s="2" t="str">
-        <v>Milan</v>
+        <v>Atalanta</v>
       </c>
       <c r="E62" s="2">
-        <v>25</v>
+        <v>27</v>
       </c>
       <c r="F62" s="2" t="str">
-        <v>D</v>
+        <v>C</v>
       </c>
       <c r="G62" s="2" t="str">
-        <v>Dc</v>
+        <v>M/C</v>
       </c>
       <c r="H62" s="2">
         <v>0</v>
@@ -2770,30 +2764,30 @@
         <v>12</v>
       </c>
       <c r="L62" s="2">
-        <v>14</v>
+        <v>13</v>
       </c>
     </row>
     <row r="63">
       <c r="A63" s="2">
-        <v>4976</v>
+        <v>5022</v>
       </c>
       <c r="B63" s="2" t="str">
-        <v>Kalulu</v>
+        <v>Pavlovic</v>
       </c>
       <c r="C63" s="2" t="str">
         <v/>
       </c>
       <c r="D63" s="2" t="str">
-        <v>Juventus</v>
+        <v>Milan</v>
       </c>
       <c r="E63" s="2">
-        <v>26</v>
+        <v>25</v>
       </c>
       <c r="F63" s="2" t="str">
         <v>D</v>
       </c>
       <c r="G63" s="2" t="str">
-        <v>Dd/Dc</v>
+        <v>Dc</v>
       </c>
       <c r="H63" s="2">
         <v>0</v>
@@ -2813,10 +2807,10 @@
     </row>
     <row r="64">
       <c r="A64" s="2">
-        <v>2788</v>
+        <v>4976</v>
       </c>
       <c r="B64" s="2" t="str">
-        <v>Bremer</v>
+        <v>Kalulu</v>
       </c>
       <c r="C64" s="2" t="str">
         <v/>
@@ -2825,13 +2819,13 @@
         <v>Juventus</v>
       </c>
       <c r="E64" s="2">
-        <v>29</v>
+        <v>26</v>
       </c>
       <c r="F64" s="2" t="str">
         <v>D</v>
       </c>
       <c r="G64" s="2" t="str">
-        <v>Dc</v>
+        <v>Dd/Dc</v>
       </c>
       <c r="H64" s="2">
         <v>0</v>
@@ -2846,24 +2840,24 @@
         <v>12</v>
       </c>
       <c r="L64" s="2">
-        <v>15</v>
+        <v>14</v>
       </c>
     </row>
     <row r="65">
       <c r="A65" s="2">
-        <v>2296</v>
+        <v>2788</v>
       </c>
       <c r="B65" s="2" t="str">
-        <v>Mancini</v>
+        <v>Bremer</v>
       </c>
       <c r="C65" s="2" t="str">
         <v/>
       </c>
       <c r="D65" s="2" t="str">
-        <v>Roma</v>
+        <v>Juventus</v>
       </c>
       <c r="E65" s="2">
-        <v>30</v>
+        <v>29</v>
       </c>
       <c r="F65" s="2" t="str">
         <v>D</v>
@@ -2889,25 +2883,25 @@
     </row>
     <row r="66">
       <c r="A66" s="2">
-        <v>4431</v>
+        <v>2296</v>
       </c>
       <c r="B66" s="2" t="str">
-        <v>Carnesecchi</v>
+        <v>Mancini</v>
       </c>
       <c r="C66" s="2" t="str">
         <v/>
       </c>
       <c r="D66" s="2" t="str">
-        <v>Atalanta</v>
+        <v>Roma</v>
       </c>
       <c r="E66" s="2">
-        <v>26</v>
+        <v>30</v>
       </c>
       <c r="F66" s="2" t="str">
-        <v>P</v>
+        <v>D</v>
       </c>
       <c r="G66" s="2" t="str">
-        <v>Por</v>
+        <v>Dc</v>
       </c>
       <c r="H66" s="2">
         <v>0</v>
@@ -2922,24 +2916,24 @@
         <v>12</v>
       </c>
       <c r="L66" s="2">
-        <v>16</v>
+        <v>15</v>
       </c>
     </row>
     <row r="67">
       <c r="A67" s="2">
-        <v>4312</v>
+        <v>4431</v>
       </c>
       <c r="B67" s="2" t="str">
-        <v>Maignan</v>
+        <v>Carnesecchi</v>
       </c>
       <c r="C67" s="2" t="str">
         <v/>
       </c>
       <c r="D67" s="2" t="str">
-        <v>Milan</v>
+        <v>Atalanta</v>
       </c>
       <c r="E67" s="2">
-        <v>31</v>
+        <v>26</v>
       </c>
       <c r="F67" s="2" t="str">
         <v>P</v>
@@ -2960,30 +2954,30 @@
         <v>12</v>
       </c>
       <c r="L67" s="2">
-        <v>15</v>
+        <v>16</v>
       </c>
     </row>
     <row r="68">
       <c r="A68" s="2">
-        <v>7547</v>
+        <v>4312</v>
       </c>
       <c r="B68" s="2" t="str">
-        <v>Kevin Carlos</v>
+        <v>Maignan</v>
       </c>
       <c r="C68" s="2" t="str">
         <v/>
       </c>
       <c r="D68" s="2" t="str">
-        <v>Cagliari</v>
+        <v>Milan</v>
       </c>
       <c r="E68" s="2">
-        <v>25</v>
+        <v>31</v>
       </c>
       <c r="F68" s="2" t="str">
-        <v>A</v>
+        <v>P</v>
       </c>
       <c r="G68" s="2" t="str">
-        <v>Pc</v>
+        <v>Por</v>
       </c>
       <c r="H68" s="2">
         <v>0</v>
@@ -2995,33 +2989,33 @@
         <v>0</v>
       </c>
       <c r="K68" s="2">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="L68" s="2">
-        <v>12</v>
+        <v>15</v>
       </c>
     </row>
     <row r="69">
       <c r="A69" s="2">
-        <v>5589</v>
+        <v>7547</v>
       </c>
       <c r="B69" s="2" t="str">
-        <v>Konè M.</v>
+        <v>Kevin Carlos</v>
       </c>
       <c r="C69" s="2" t="str">
         <v/>
       </c>
       <c r="D69" s="2" t="str">
-        <v>Roma</v>
+        <v>Cagliari</v>
       </c>
       <c r="E69" s="2">
         <v>25</v>
       </c>
       <c r="F69" s="2" t="str">
-        <v>C</v>
+        <v>A</v>
       </c>
       <c r="G69" s="2" t="str">
-        <v>M/C</v>
+        <v>Pc</v>
       </c>
       <c r="H69" s="2">
         <v>0</v>
@@ -3036,30 +3030,30 @@
         <v>11</v>
       </c>
       <c r="L69" s="2">
-        <v>11</v>
+        <v>12</v>
       </c>
     </row>
     <row r="70">
       <c r="A70" s="2">
-        <v>4892</v>
+        <v>5589</v>
       </c>
       <c r="B70" s="2" t="str">
-        <v>Saelemaekers</v>
+        <v>Konè M.</v>
       </c>
       <c r="C70" s="2" t="str">
         <v/>
       </c>
       <c r="D70" s="2" t="str">
-        <v>Milan</v>
+        <v>Roma</v>
       </c>
       <c r="E70" s="2">
-        <v>27</v>
+        <v>25</v>
       </c>
       <c r="F70" s="2" t="str">
         <v>C</v>
       </c>
       <c r="G70" s="2" t="str">
-        <v>E/W</v>
+        <v>M/C</v>
       </c>
       <c r="H70" s="2">
         <v>0</v>
@@ -3079,25 +3073,25 @@
     </row>
     <row r="71">
       <c r="A71" s="2">
-        <v>6956</v>
+        <v>4892</v>
       </c>
       <c r="B71" s="2" t="str">
-        <v>Solet</v>
+        <v>Saelemaekers</v>
       </c>
       <c r="C71" s="2" t="str">
         <v/>
       </c>
       <c r="D71" s="2" t="str">
-        <v>Udinese</v>
+        <v>Milan</v>
       </c>
       <c r="E71" s="2">
-        <v>26</v>
+        <v>27</v>
       </c>
       <c r="F71" s="2" t="str">
-        <v>D</v>
+        <v>C</v>
       </c>
       <c r="G71" s="2" t="str">
-        <v>Dc</v>
+        <v>E/W</v>
       </c>
       <c r="H71" s="2">
         <v>0</v>
@@ -3112,24 +3106,24 @@
         <v>11</v>
       </c>
       <c r="L71" s="2">
-        <v>13</v>
+        <v>11</v>
       </c>
     </row>
     <row r="72">
       <c r="A72" s="2">
-        <v>4409</v>
+        <v>6956</v>
       </c>
       <c r="B72" s="2" t="str">
-        <v>Rrahmani</v>
+        <v>Solet</v>
       </c>
       <c r="C72" s="2" t="str">
         <v/>
       </c>
       <c r="D72" s="2" t="str">
-        <v>Napoli</v>
+        <v>Udinese</v>
       </c>
       <c r="E72" s="2">
-        <v>32</v>
+        <v>26</v>
       </c>
       <c r="F72" s="2" t="str">
         <v>D</v>
@@ -3150,24 +3144,24 @@
         <v>11</v>
       </c>
       <c r="L72" s="2">
-        <v>14</v>
+        <v>13</v>
       </c>
     </row>
     <row r="73">
       <c r="A73" s="2">
-        <v>4317</v>
+        <v>4409</v>
       </c>
       <c r="B73" s="2" t="str">
-        <v>N'Dicka</v>
+        <v>Rrahmani</v>
       </c>
       <c r="C73" s="2" t="str">
         <v/>
       </c>
       <c r="D73" s="2" t="str">
-        <v>Roma</v>
+        <v>Napoli</v>
       </c>
       <c r="E73" s="2">
-        <v>27</v>
+        <v>32</v>
       </c>
       <c r="F73" s="2" t="str">
         <v>D</v>
@@ -3188,21 +3182,21 @@
         <v>11</v>
       </c>
       <c r="L73" s="2">
-        <v>13</v>
+        <v>14</v>
       </c>
     </row>
     <row r="74">
       <c r="A74" s="2">
-        <v>2120</v>
+        <v>4317</v>
       </c>
       <c r="B74" s="2" t="str">
-        <v>Bastoni</v>
+        <v>N'Dicka</v>
       </c>
       <c r="C74" s="2" t="str">
         <v/>
       </c>
       <c r="D74" s="2" t="str">
-        <v>Inter</v>
+        <v>Roma</v>
       </c>
       <c r="E74" s="2">
         <v>27</v>
@@ -3226,30 +3220,30 @@
         <v>11</v>
       </c>
       <c r="L74" s="2">
-        <v>14</v>
+        <v>13</v>
       </c>
     </row>
     <row r="75">
       <c r="A75" s="2">
-        <v>2521</v>
+        <v>2120</v>
       </c>
       <c r="B75" s="2" t="str">
-        <v>De Gea</v>
+        <v>Bastoni</v>
       </c>
       <c r="C75" s="2" t="str">
         <v/>
       </c>
       <c r="D75" s="2" t="str">
-        <v>Fiorentina</v>
+        <v>Inter</v>
       </c>
       <c r="E75" s="2">
-        <v>36</v>
+        <v>27</v>
       </c>
       <c r="F75" s="2" t="str">
-        <v>P</v>
+        <v>D</v>
       </c>
       <c r="G75" s="2" t="str">
-        <v>Por</v>
+        <v>Dc</v>
       </c>
       <c r="H75" s="2">
         <v>0</v>
@@ -3264,24 +3258,24 @@
         <v>11</v>
       </c>
       <c r="L75" s="2">
-        <v>13</v>
+        <v>14</v>
       </c>
     </row>
     <row r="76">
       <c r="A76" s="2">
-        <v>572</v>
+        <v>2521</v>
       </c>
       <c r="B76" s="2" t="str">
-        <v>Meret</v>
+        <v>De Gea</v>
       </c>
       <c r="C76" s="2" t="str">
         <v/>
       </c>
       <c r="D76" s="2" t="str">
-        <v>Napoli</v>
+        <v>Fiorentina</v>
       </c>
       <c r="E76" s="2">
-        <v>29</v>
+        <v>36</v>
       </c>
       <c r="F76" s="2" t="str">
         <v>P</v>
@@ -3302,30 +3296,30 @@
         <v>11</v>
       </c>
       <c r="L76" s="2">
-        <v>11</v>
+        <v>13</v>
       </c>
     </row>
     <row r="77">
       <c r="A77" s="2">
-        <v>6229</v>
+        <v>572</v>
       </c>
       <c r="B77" s="2" t="str">
-        <v>Tourè E.</v>
+        <v>Meret</v>
       </c>
       <c r="C77" s="2" t="str">
         <v/>
       </c>
       <c r="D77" s="2" t="str">
-        <v>Parma</v>
+        <v>Napoli</v>
       </c>
       <c r="E77" s="2">
-        <v>25</v>
+        <v>29</v>
       </c>
       <c r="F77" s="2" t="str">
-        <v>A</v>
+        <v>P</v>
       </c>
       <c r="G77" s="2" t="str">
-        <v>Pc</v>
+        <v>Por</v>
       </c>
       <c r="H77" s="2">
         <v>0</v>
@@ -3337,7 +3331,7 @@
         <v>0</v>
       </c>
       <c r="K77" s="2">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="L77" s="2">
         <v>11</v>
@@ -3345,25 +3339,25 @@
     </row>
     <row r="78">
       <c r="A78" s="2">
-        <v>4463</v>
+        <v>6229</v>
       </c>
       <c r="B78" s="2" t="str">
-        <v>Esposito Se.</v>
+        <v>Tourè E.</v>
       </c>
       <c r="C78" s="2" t="str">
         <v/>
       </c>
       <c r="D78" s="2" t="str">
-        <v>Cagliari</v>
+        <v>Parma</v>
       </c>
       <c r="E78" s="2">
-        <v>24</v>
+        <v>25</v>
       </c>
       <c r="F78" s="2" t="str">
         <v>A</v>
       </c>
       <c r="G78" s="2" t="str">
-        <v>A</v>
+        <v>Pc</v>
       </c>
       <c r="H78" s="2">
         <v>0</v>
@@ -3378,30 +3372,30 @@
         <v>10</v>
       </c>
       <c r="L78" s="2">
-        <v>14</v>
+        <v>11</v>
       </c>
     </row>
     <row r="79">
       <c r="A79" s="2">
-        <v>2531</v>
+        <v>4463</v>
       </c>
       <c r="B79" s="2" t="str">
-        <v>Lukaku</v>
+        <v>Esposito Se.</v>
       </c>
       <c r="C79" s="2" t="str">
-        <v>*</v>
+        <v/>
       </c>
       <c r="D79" s="2" t="str">
-        <v>Napoli</v>
+        <v>Cagliari</v>
       </c>
       <c r="E79" s="2">
-        <v>33</v>
+        <v>24</v>
       </c>
       <c r="F79" s="2" t="str">
         <v>A</v>
       </c>
       <c r="G79" s="2" t="str">
-        <v>Pc</v>
+        <v>A</v>
       </c>
       <c r="H79" s="2">
         <v>0</v>
@@ -3416,30 +3410,30 @@
         <v>10</v>
       </c>
       <c r="L79" s="2">
-        <v>9</v>
+        <v>14</v>
       </c>
     </row>
     <row r="80">
       <c r="A80" s="2">
-        <v>6844</v>
+        <v>2531</v>
       </c>
       <c r="B80" s="2" t="str">
-        <v>Rowe</v>
+        <v>Lukaku</v>
       </c>
       <c r="C80" s="2" t="str">
-        <v/>
+        <v>*</v>
       </c>
       <c r="D80" s="2" t="str">
-        <v>Bologna</v>
+        <v>Napoli</v>
       </c>
       <c r="E80" s="2">
-        <v>23</v>
+        <v>33</v>
       </c>
       <c r="F80" s="2" t="str">
-        <v>C</v>
+        <v>A</v>
       </c>
       <c r="G80" s="2" t="str">
-        <v>W/T</v>
+        <v>Pc</v>
       </c>
       <c r="H80" s="2">
         <v>0</v>
@@ -3454,30 +3448,30 @@
         <v>10</v>
       </c>
       <c r="L80" s="2">
-        <v>11</v>
+        <v>9</v>
       </c>
     </row>
     <row r="81">
       <c r="A81" s="2">
-        <v>6684</v>
+        <v>6844</v>
       </c>
       <c r="B81" s="2" t="str">
-        <v>Ekkelenkamp</v>
+        <v>Rowe</v>
       </c>
       <c r="C81" s="2" t="str">
         <v/>
       </c>
       <c r="D81" s="2" t="str">
-        <v>Udinese</v>
+        <v>Bologna</v>
       </c>
       <c r="E81" s="2">
-        <v>26</v>
+        <v>23</v>
       </c>
       <c r="F81" s="2" t="str">
         <v>C</v>
       </c>
       <c r="G81" s="2" t="str">
-        <v>C/T</v>
+        <v>W/T</v>
       </c>
       <c r="H81" s="2">
         <v>0</v>
@@ -3492,30 +3486,30 @@
         <v>10</v>
       </c>
       <c r="L81" s="2">
-        <v>10</v>
+        <v>11</v>
       </c>
     </row>
     <row r="82">
       <c r="A82" s="2">
-        <v>6274</v>
+        <v>6684</v>
       </c>
       <c r="B82" s="2" t="str">
-        <v>Diouf</v>
+        <v>Ekkelenkamp</v>
       </c>
       <c r="C82" s="2" t="str">
         <v/>
       </c>
       <c r="D82" s="2" t="str">
-        <v>Inter</v>
+        <v>Udinese</v>
       </c>
       <c r="E82" s="2">
-        <v>23</v>
+        <v>26</v>
       </c>
       <c r="F82" s="2" t="str">
         <v>C</v>
       </c>
       <c r="G82" s="2" t="str">
-        <v>E/C</v>
+        <v>C/T</v>
       </c>
       <c r="H82" s="2">
         <v>0</v>
@@ -3530,21 +3524,21 @@
         <v>10</v>
       </c>
       <c r="L82" s="2">
-        <v>9</v>
+        <v>10</v>
       </c>
     </row>
     <row r="83">
       <c r="A83" s="2">
-        <v>6151</v>
+        <v>6274</v>
       </c>
       <c r="B83" s="2" t="str">
-        <v>Perrone</v>
+        <v>Diouf</v>
       </c>
       <c r="C83" s="2" t="str">
         <v/>
       </c>
       <c r="D83" s="2" t="str">
-        <v>Como</v>
+        <v>Inter</v>
       </c>
       <c r="E83" s="2">
         <v>23</v>
@@ -3553,7 +3547,7 @@
         <v>C</v>
       </c>
       <c r="G83" s="2" t="str">
-        <v>M/C</v>
+        <v>E/C</v>
       </c>
       <c r="H83" s="2">
         <v>0</v>
@@ -3568,30 +3562,30 @@
         <v>10</v>
       </c>
       <c r="L83" s="2">
-        <v>11</v>
+        <v>9</v>
       </c>
     </row>
     <row r="84">
       <c r="A84" s="2">
-        <v>5844</v>
+        <v>6151</v>
       </c>
       <c r="B84" s="2" t="str">
-        <v>Thorstvedt</v>
+        <v>Perrone</v>
       </c>
       <c r="C84" s="2" t="str">
         <v/>
       </c>
       <c r="D84" s="2" t="str">
-        <v>Sassuolo</v>
+        <v>Como</v>
       </c>
       <c r="E84" s="2">
-        <v>27</v>
+        <v>23</v>
       </c>
       <c r="F84" s="2" t="str">
         <v>C</v>
       </c>
       <c r="G84" s="2" t="str">
-        <v>C/T</v>
+        <v>M/C</v>
       </c>
       <c r="H84" s="2">
         <v>0</v>
@@ -3606,30 +3600,30 @@
         <v>10</v>
       </c>
       <c r="L84" s="2">
-        <v>10</v>
+        <v>11</v>
       </c>
     </row>
     <row r="85">
       <c r="A85" s="2">
-        <v>5562</v>
+        <v>5844</v>
       </c>
       <c r="B85" s="2" t="str">
-        <v>Thuram K.</v>
+        <v>Thorstvedt</v>
       </c>
       <c r="C85" s="2" t="str">
         <v/>
       </c>
       <c r="D85" s="2" t="str">
-        <v>Juventus</v>
+        <v>Sassuolo</v>
       </c>
       <c r="E85" s="2">
-        <v>25</v>
+        <v>27</v>
       </c>
       <c r="F85" s="2" t="str">
         <v>C</v>
       </c>
       <c r="G85" s="2" t="str">
-        <v>C</v>
+        <v>C/T</v>
       </c>
       <c r="H85" s="2">
         <v>0</v>
@@ -3649,25 +3643,25 @@
     </row>
     <row r="86">
       <c r="A86" s="2">
-        <v>5119</v>
+        <v>5562</v>
       </c>
       <c r="B86" s="2" t="str">
-        <v>Samardzic</v>
+        <v>Thuram K.</v>
       </c>
       <c r="C86" s="2" t="str">
         <v/>
       </c>
       <c r="D86" s="2" t="str">
-        <v>Atalanta</v>
+        <v>Juventus</v>
       </c>
       <c r="E86" s="2">
-        <v>24</v>
+        <v>25</v>
       </c>
       <c r="F86" s="2" t="str">
         <v>C</v>
       </c>
       <c r="G86" s="2" t="str">
-        <v>C/T</v>
+        <v>C</v>
       </c>
       <c r="H86" s="2">
         <v>0</v>
@@ -3682,30 +3676,30 @@
         <v>10</v>
       </c>
       <c r="L86" s="2">
-        <v>12</v>
+        <v>10</v>
       </c>
     </row>
     <row r="87">
       <c r="A87" s="2">
-        <v>536</v>
+        <v>5119</v>
       </c>
       <c r="B87" s="2" t="str">
-        <v>Politano</v>
+        <v>Samardzic</v>
       </c>
       <c r="C87" s="2" t="str">
         <v/>
       </c>
       <c r="D87" s="2" t="str">
-        <v>Napoli</v>
+        <v>Atalanta</v>
       </c>
       <c r="E87" s="2">
-        <v>33</v>
+        <v>24</v>
       </c>
       <c r="F87" s="2" t="str">
         <v>C</v>
       </c>
       <c r="G87" s="2" t="str">
-        <v>W</v>
+        <v>C/T</v>
       </c>
       <c r="H87" s="2">
         <v>0</v>
@@ -3720,30 +3714,30 @@
         <v>10</v>
       </c>
       <c r="L87" s="2">
-        <v>9</v>
+        <v>12</v>
       </c>
     </row>
     <row r="88">
       <c r="A88" s="2">
-        <v>152</v>
+        <v>536</v>
       </c>
       <c r="B88" s="2" t="str">
-        <v>Zielinski</v>
+        <v>Politano</v>
       </c>
       <c r="C88" s="2" t="str">
         <v/>
       </c>
       <c r="D88" s="2" t="str">
-        <v>Inter</v>
+        <v>Napoli</v>
       </c>
       <c r="E88" s="2">
-        <v>32</v>
+        <v>33</v>
       </c>
       <c r="F88" s="2" t="str">
         <v>C</v>
       </c>
       <c r="G88" s="2" t="str">
-        <v>C</v>
+        <v>W</v>
       </c>
       <c r="H88" s="2">
         <v>0</v>
@@ -3758,30 +3752,30 @@
         <v>10</v>
       </c>
       <c r="L88" s="2">
-        <v>10</v>
+        <v>9</v>
       </c>
     </row>
     <row r="89">
       <c r="A89" s="2">
-        <v>5750</v>
+        <v>152</v>
       </c>
       <c r="B89" s="2" t="str">
-        <v>Ostigard</v>
+        <v>Zielinski</v>
       </c>
       <c r="C89" s="2" t="str">
         <v/>
       </c>
       <c r="D89" s="2" t="str">
-        <v>Genoa</v>
+        <v>Inter</v>
       </c>
       <c r="E89" s="2">
-        <v>27</v>
+        <v>32</v>
       </c>
       <c r="F89" s="2" t="str">
-        <v>D</v>
+        <v>C</v>
       </c>
       <c r="G89" s="2" t="str">
-        <v>Dc</v>
+        <v>C</v>
       </c>
       <c r="H89" s="2">
         <v>0</v>
@@ -3796,30 +3790,30 @@
         <v>10</v>
       </c>
       <c r="L89" s="2">
-        <v>11</v>
+        <v>10</v>
       </c>
     </row>
     <row r="90">
       <c r="A90" s="2">
-        <v>2816</v>
+        <v>5750</v>
       </c>
       <c r="B90" s="2" t="str">
-        <v>Di Lorenzo</v>
+        <v>Ostigard</v>
       </c>
       <c r="C90" s="2" t="str">
         <v/>
       </c>
       <c r="D90" s="2" t="str">
-        <v>Napoli</v>
+        <v>Genoa</v>
       </c>
       <c r="E90" s="2">
-        <v>33</v>
+        <v>27</v>
       </c>
       <c r="F90" s="2" t="str">
         <v>D</v>
       </c>
       <c r="G90" s="2" t="str">
-        <v>Dd/E</v>
+        <v>Dc</v>
       </c>
       <c r="H90" s="2">
         <v>0</v>
@@ -3834,30 +3828,30 @@
         <v>10</v>
       </c>
       <c r="L90" s="2">
-        <v>12</v>
+        <v>11</v>
       </c>
     </row>
     <row r="91">
       <c r="A91" s="2">
-        <v>5876</v>
+        <v>2816</v>
       </c>
       <c r="B91" s="2" t="str">
-        <v>Di Gregorio</v>
+        <v>Di Lorenzo</v>
       </c>
       <c r="C91" s="2" t="str">
         <v/>
       </c>
       <c r="D91" s="2" t="str">
-        <v>Juventus</v>
+        <v>Napoli</v>
       </c>
       <c r="E91" s="2">
-        <v>29</v>
+        <v>33</v>
       </c>
       <c r="F91" s="2" t="str">
-        <v>P</v>
+        <v>D</v>
       </c>
       <c r="G91" s="2" t="str">
-        <v>Por</v>
+        <v>Dd/E</v>
       </c>
       <c r="H91" s="2">
         <v>0</v>
@@ -3872,7 +3866,7 @@
         <v>10</v>
       </c>
       <c r="L91" s="2">
-        <v>9</v>
+        <v>12</v>
       </c>
     </row>
     <row r="92">
@@ -9510,7 +9504,7 @@
         <v/>
       </c>
       <c r="D240" s="2" t="str">
-        <v>Bologna</v>
+        <v>Juventus</v>
       </c>
       <c r="E240" s="2">
         <v>28</v>
@@ -10185,25 +10179,25 @@
     </row>
     <row r="258">
       <c r="A258" s="2">
-        <v>7550</v>
+        <v>2012</v>
       </c>
       <c r="B258" s="2" t="str">
-        <v>Grillitsch</v>
+        <v>Milik</v>
       </c>
       <c r="C258" s="2" t="str">
         <v/>
       </c>
       <c r="D258" s="2" t="str">
-        <v>Frosinone</v>
+        <v>Juventus</v>
       </c>
       <c r="E258" s="2">
-        <v>31</v>
+        <v>32</v>
       </c>
       <c r="F258" s="2" t="str">
-        <v>C</v>
+        <v>A</v>
       </c>
       <c r="G258" s="2" t="str">
-        <v>M/C</v>
+        <v>Pc</v>
       </c>
       <c r="H258" s="2">
         <v>0</v>
@@ -10218,24 +10212,24 @@
         <v>3</v>
       </c>
       <c r="L258" s="2">
-        <v>5</v>
+        <v>4</v>
       </c>
     </row>
     <row r="259">
       <c r="A259" s="2">
-        <v>7528</v>
+        <v>7550</v>
       </c>
       <c r="B259" s="2" t="str">
-        <v>Amondarain</v>
+        <v>Grillitsch</v>
       </c>
       <c r="C259" s="2" t="str">
         <v/>
       </c>
       <c r="D259" s="2" t="str">
-        <v>Bologna</v>
+        <v>Frosinone</v>
       </c>
       <c r="E259" s="2">
-        <v>21</v>
+        <v>31</v>
       </c>
       <c r="F259" s="2" t="str">
         <v>C</v>
@@ -10256,30 +10250,30 @@
         <v>3</v>
       </c>
       <c r="L259" s="2">
-        <v>6</v>
+        <v>5</v>
       </c>
     </row>
     <row r="260">
       <c r="A260" s="2">
-        <v>7474</v>
+        <v>7528</v>
       </c>
       <c r="B260" s="2" t="str">
-        <v>Koutsoupias</v>
+        <v>Amondarain</v>
       </c>
       <c r="C260" s="2" t="str">
         <v/>
       </c>
       <c r="D260" s="2" t="str">
-        <v>Frosinone</v>
+        <v>Bologna</v>
       </c>
       <c r="E260" s="2">
-        <v>25</v>
+        <v>21</v>
       </c>
       <c r="F260" s="2" t="str">
         <v>C</v>
       </c>
       <c r="G260" s="2" t="str">
-        <v>C</v>
+        <v>M/C</v>
       </c>
       <c r="H260" s="2">
         <v>0</v>
@@ -10294,15 +10288,15 @@
         <v>3</v>
       </c>
       <c r="L260" s="2">
-        <v>4</v>
+        <v>6</v>
       </c>
     </row>
     <row r="261">
       <c r="A261" s="2">
-        <v>7473</v>
+        <v>7474</v>
       </c>
       <c r="B261" s="2" t="str">
-        <v>Cichella</v>
+        <v>Koutsoupias</v>
       </c>
       <c r="C261" s="2" t="str">
         <v/>
@@ -10311,13 +10305,13 @@
         <v>Frosinone</v>
       </c>
       <c r="E261" s="2">
-        <v>21</v>
+        <v>25</v>
       </c>
       <c r="F261" s="2" t="str">
         <v>C</v>
       </c>
       <c r="G261" s="2" t="str">
-        <v>M/C</v>
+        <v>C</v>
       </c>
       <c r="H261" s="2">
         <v>0</v>
@@ -10337,16 +10331,16 @@
     </row>
     <row r="262">
       <c r="A262" s="2">
-        <v>7409</v>
+        <v>7473</v>
       </c>
       <c r="B262" s="2" t="str">
-        <v>Meichtry</v>
+        <v>Cichella</v>
       </c>
       <c r="C262" s="2" t="str">
         <v/>
       </c>
       <c r="D262" s="2" t="str">
-        <v>Genoa</v>
+        <v>Frosinone</v>
       </c>
       <c r="E262" s="2">
         <v>21</v>
@@ -10355,7 +10349,7 @@
         <v>C</v>
       </c>
       <c r="G262" s="2" t="str">
-        <v>W/T</v>
+        <v>M/C</v>
       </c>
       <c r="H262" s="2">
         <v>0</v>
@@ -10370,15 +10364,15 @@
         <v>3</v>
       </c>
       <c r="L262" s="2">
-        <v>5</v>
+        <v>4</v>
       </c>
     </row>
     <row r="263">
       <c r="A263" s="2">
-        <v>7341</v>
+        <v>7409</v>
       </c>
       <c r="B263" s="2" t="str">
-        <v>Amorim</v>
+        <v>Meichtry</v>
       </c>
       <c r="C263" s="2" t="str">
         <v/>
@@ -10393,7 +10387,7 @@
         <v>C</v>
       </c>
       <c r="G263" s="2" t="str">
-        <v>M/C</v>
+        <v>W/T</v>
       </c>
       <c r="H263" s="2">
         <v>0</v>
@@ -10413,19 +10407,19 @@
     </row>
     <row r="264">
       <c r="A264" s="2">
-        <v>7322</v>
+        <v>7341</v>
       </c>
       <c r="B264" s="2" t="str">
-        <v>Ngom</v>
+        <v>Amorim</v>
       </c>
       <c r="C264" s="2" t="str">
         <v/>
       </c>
       <c r="D264" s="2" t="str">
-        <v>Lecce</v>
+        <v>Genoa</v>
       </c>
       <c r="E264" s="2">
-        <v>22</v>
+        <v>21</v>
       </c>
       <c r="F264" s="2" t="str">
         <v>C</v>
@@ -10451,10 +10445,10 @@
     </row>
     <row r="265">
       <c r="A265" s="2">
-        <v>7318</v>
+        <v>7322</v>
       </c>
       <c r="B265" s="2" t="str">
-        <v>Gandelman</v>
+        <v>Ngom</v>
       </c>
       <c r="C265" s="2" t="str">
         <v/>
@@ -10463,13 +10457,13 @@
         <v>Lecce</v>
       </c>
       <c r="E265" s="2">
-        <v>26</v>
+        <v>22</v>
       </c>
       <c r="F265" s="2" t="str">
         <v>C</v>
       </c>
       <c r="G265" s="2" t="str">
-        <v>C/T</v>
+        <v>M/C</v>
       </c>
       <c r="H265" s="2">
         <v>0</v>
@@ -10489,25 +10483,25 @@
     </row>
     <row r="266">
       <c r="A266" s="2">
-        <v>7209</v>
+        <v>7318</v>
       </c>
       <c r="B266" s="2" t="str">
-        <v>Sorensen O.</v>
+        <v>Gandelman</v>
       </c>
       <c r="C266" s="2" t="str">
         <v/>
       </c>
       <c r="D266" s="2" t="str">
-        <v>Parma</v>
+        <v>Lecce</v>
       </c>
       <c r="E266" s="2">
-        <v>24</v>
+        <v>26</v>
       </c>
       <c r="F266" s="2" t="str">
         <v>C</v>
       </c>
       <c r="G266" s="2" t="str">
-        <v>C</v>
+        <v>C/T</v>
       </c>
       <c r="H266" s="2">
         <v>0</v>
@@ -10522,24 +10516,24 @@
         <v>3</v>
       </c>
       <c r="L266" s="2">
-        <v>3</v>
+        <v>5</v>
       </c>
     </row>
     <row r="267">
       <c r="A267" s="2">
-        <v>7203</v>
+        <v>7209</v>
       </c>
       <c r="B267" s="2" t="str">
-        <v>Jashari</v>
+        <v>Sorensen O.</v>
       </c>
       <c r="C267" s="2" t="str">
         <v/>
       </c>
       <c r="D267" s="2" t="str">
-        <v>Milan</v>
+        <v>Parma</v>
       </c>
       <c r="E267" s="2">
-        <v>25</v>
+        <v>24</v>
       </c>
       <c r="F267" s="2" t="str">
         <v>C</v>
@@ -10560,30 +10554,30 @@
         <v>3</v>
       </c>
       <c r="L267" s="2">
-        <v>4</v>
+        <v>3</v>
       </c>
     </row>
     <row r="268">
       <c r="A268" s="2">
-        <v>7036</v>
+        <v>7203</v>
       </c>
       <c r="B268" s="2" t="str">
-        <v>Bakola</v>
+        <v>Jashari</v>
       </c>
       <c r="C268" s="2" t="str">
         <v/>
       </c>
       <c r="D268" s="2" t="str">
-        <v>Sassuolo</v>
+        <v>Milan</v>
       </c>
       <c r="E268" s="2">
-        <v>19</v>
+        <v>24</v>
       </c>
       <c r="F268" s="2" t="str">
         <v>C</v>
       </c>
       <c r="G268" s="2" t="str">
-        <v>C/T</v>
+        <v>C</v>
       </c>
       <c r="H268" s="2">
         <v>0</v>
@@ -10598,24 +10592,24 @@
         <v>3</v>
       </c>
       <c r="L268" s="2">
-        <v>5</v>
+        <v>4</v>
       </c>
     </row>
     <row r="269">
       <c r="A269" s="2">
-        <v>6994</v>
+        <v>7036</v>
       </c>
       <c r="B269" s="2" t="str">
-        <v>Perez K.</v>
+        <v>Bakola</v>
       </c>
       <c r="C269" s="2" t="str">
         <v/>
       </c>
       <c r="D269" s="2" t="str">
-        <v>Venezia</v>
+        <v>Sassuolo</v>
       </c>
       <c r="E269" s="2">
-        <v>29</v>
+        <v>19</v>
       </c>
       <c r="F269" s="2" t="str">
         <v>C</v>
@@ -10641,25 +10635,25 @@
     </row>
     <row r="270">
       <c r="A270" s="2">
-        <v>6895</v>
+        <v>6994</v>
       </c>
       <c r="B270" s="2" t="str">
-        <v>Dominguez B.</v>
+        <v>Perez K.</v>
       </c>
       <c r="C270" s="2" t="str">
         <v/>
       </c>
       <c r="D270" s="2" t="str">
-        <v>Sassuolo</v>
+        <v>Venezia</v>
       </c>
       <c r="E270" s="2">
-        <v>23</v>
+        <v>29</v>
       </c>
       <c r="F270" s="2" t="str">
         <v>C</v>
       </c>
       <c r="G270" s="2" t="str">
-        <v>W/A</v>
+        <v>C/T</v>
       </c>
       <c r="H270" s="2">
         <v>0</v>
@@ -10674,30 +10668,30 @@
         <v>3</v>
       </c>
       <c r="L270" s="2">
-        <v>2</v>
+        <v>5</v>
       </c>
     </row>
     <row r="271">
       <c r="A271" s="2">
-        <v>6629</v>
+        <v>6895</v>
       </c>
       <c r="B271" s="2" t="str">
-        <v>Dele-Bashiru</v>
+        <v>Dominguez B.</v>
       </c>
       <c r="C271" s="2" t="str">
         <v/>
       </c>
       <c r="D271" s="2" t="str">
-        <v>Lazio</v>
+        <v>Sassuolo</v>
       </c>
       <c r="E271" s="2">
-        <v>25</v>
+        <v>23</v>
       </c>
       <c r="F271" s="2" t="str">
         <v>C</v>
       </c>
       <c r="G271" s="2" t="str">
-        <v>C/T</v>
+        <v>W/A</v>
       </c>
       <c r="H271" s="2">
         <v>0</v>
@@ -10712,30 +10706,30 @@
         <v>3</v>
       </c>
       <c r="L271" s="2">
-        <v>5</v>
+        <v>2</v>
       </c>
     </row>
     <row r="272">
       <c r="A272" s="2">
-        <v>6503</v>
+        <v>6629</v>
       </c>
       <c r="B272" s="2" t="str">
-        <v>Stankovic A.</v>
+        <v>Dele-Bashiru</v>
       </c>
       <c r="C272" s="2" t="str">
         <v/>
       </c>
       <c r="D272" s="2" t="str">
-        <v>Inter</v>
+        <v>Lazio</v>
       </c>
       <c r="E272" s="2">
-        <v>21</v>
+        <v>25</v>
       </c>
       <c r="F272" s="2" t="str">
         <v>C</v>
       </c>
       <c r="G272" s="2" t="str">
-        <v>M/C</v>
+        <v>C/T</v>
       </c>
       <c r="H272" s="2">
         <v>0</v>
@@ -10750,30 +10744,30 @@
         <v>3</v>
       </c>
       <c r="L272" s="2">
-        <v>3</v>
+        <v>5</v>
       </c>
     </row>
     <row r="273">
       <c r="A273" s="2">
-        <v>6207</v>
+        <v>6503</v>
       </c>
       <c r="B273" s="2" t="str">
-        <v>Almqvist</v>
+        <v>Stankovic A.</v>
       </c>
       <c r="C273" s="2" t="str">
         <v/>
       </c>
       <c r="D273" s="2" t="str">
-        <v>Parma</v>
+        <v>Inter</v>
       </c>
       <c r="E273" s="2">
-        <v>27</v>
+        <v>21</v>
       </c>
       <c r="F273" s="2" t="str">
         <v>C</v>
       </c>
       <c r="G273" s="2" t="str">
-        <v>W/A</v>
+        <v>M/C</v>
       </c>
       <c r="H273" s="2">
         <v>0</v>
@@ -10793,25 +10787,25 @@
     </row>
     <row r="274">
       <c r="A274" s="2">
-        <v>6054</v>
+        <v>6207</v>
       </c>
       <c r="B274" s="2" t="str">
-        <v>Moro N.</v>
+        <v>Almqvist</v>
       </c>
       <c r="C274" s="2" t="str">
         <v/>
       </c>
       <c r="D274" s="2" t="str">
-        <v>Bologna</v>
+        <v>Parma</v>
       </c>
       <c r="E274" s="2">
-        <v>28</v>
+        <v>27</v>
       </c>
       <c r="F274" s="2" t="str">
         <v>C</v>
       </c>
       <c r="G274" s="2" t="str">
-        <v>M/C</v>
+        <v>W/A</v>
       </c>
       <c r="H274" s="2">
         <v>0</v>
@@ -10826,24 +10820,24 @@
         <v>3</v>
       </c>
       <c r="L274" s="2">
-        <v>4</v>
+        <v>3</v>
       </c>
     </row>
     <row r="275">
       <c r="A275" s="2">
-        <v>6005</v>
+        <v>6054</v>
       </c>
       <c r="B275" s="2" t="str">
-        <v>Ilkhan</v>
+        <v>Moro N.</v>
       </c>
       <c r="C275" s="2" t="str">
         <v/>
       </c>
       <c r="D275" s="2" t="str">
-        <v>Torino</v>
+        <v>Bologna</v>
       </c>
       <c r="E275" s="2">
-        <v>22</v>
+        <v>28</v>
       </c>
       <c r="F275" s="2" t="str">
         <v>C</v>
@@ -10864,30 +10858,30 @@
         <v>3</v>
       </c>
       <c r="L275" s="2">
-        <v>5</v>
+        <v>4</v>
       </c>
     </row>
     <row r="276">
       <c r="A276" s="2">
-        <v>5998</v>
+        <v>6005</v>
       </c>
       <c r="B276" s="2" t="str">
-        <v>Zerbin</v>
+        <v>Ilkhan</v>
       </c>
       <c r="C276" s="2" t="str">
         <v/>
       </c>
       <c r="D276" s="2" t="str">
-        <v>Frosinone</v>
+        <v>Torino</v>
       </c>
       <c r="E276" s="2">
-        <v>27</v>
+        <v>22</v>
       </c>
       <c r="F276" s="2" t="str">
         <v>C</v>
       </c>
       <c r="G276" s="2" t="str">
-        <v>W</v>
+        <v>M/C</v>
       </c>
       <c r="H276" s="2">
         <v>0</v>
@@ -10902,30 +10896,30 @@
         <v>3</v>
       </c>
       <c r="L276" s="2">
-        <v>4</v>
+        <v>5</v>
       </c>
     </row>
     <row r="277">
       <c r="A277" s="2">
-        <v>5813</v>
+        <v>5998</v>
       </c>
       <c r="B277" s="2" t="str">
-        <v>Miretti</v>
+        <v>Zerbin</v>
       </c>
       <c r="C277" s="2" t="str">
         <v/>
       </c>
       <c r="D277" s="2" t="str">
-        <v>Juventus</v>
+        <v>Frosinone</v>
       </c>
       <c r="E277" s="2">
-        <v>23</v>
+        <v>27</v>
       </c>
       <c r="F277" s="2" t="str">
         <v>C</v>
       </c>
       <c r="G277" s="2" t="str">
-        <v>C/T</v>
+        <v>W</v>
       </c>
       <c r="H277" s="2">
         <v>0</v>
@@ -10940,15 +10934,15 @@
         <v>3</v>
       </c>
       <c r="L277" s="2">
-        <v>3</v>
+        <v>4</v>
       </c>
     </row>
     <row r="278">
       <c r="A278" s="2">
-        <v>5685</v>
+        <v>5813</v>
       </c>
       <c r="B278" s="2" t="str">
-        <v>Koopmeiners</v>
+        <v>Miretti</v>
       </c>
       <c r="C278" s="2" t="str">
         <v/>
@@ -10957,7 +10951,7 @@
         <v>Juventus</v>
       </c>
       <c r="E278" s="2">
-        <v>28</v>
+        <v>23</v>
       </c>
       <c r="F278" s="2" t="str">
         <v>C</v>
@@ -10978,30 +10972,30 @@
         <v>3</v>
       </c>
       <c r="L278" s="2">
-        <v>5</v>
+        <v>3</v>
       </c>
     </row>
     <row r="279">
       <c r="A279" s="2">
-        <v>5453</v>
+        <v>5685</v>
       </c>
       <c r="B279" s="2" t="str">
-        <v>Ricci S.</v>
+        <v>Koopmeiners</v>
       </c>
       <c r="C279" s="2" t="str">
         <v/>
       </c>
       <c r="D279" s="2" t="str">
-        <v>Milan</v>
+        <v>Juventus</v>
       </c>
       <c r="E279" s="2">
-        <v>25</v>
+        <v>28</v>
       </c>
       <c r="F279" s="2" t="str">
         <v>C</v>
       </c>
       <c r="G279" s="2" t="str">
-        <v>M/C</v>
+        <v>C/T</v>
       </c>
       <c r="H279" s="2">
         <v>0</v>
@@ -11016,21 +11010,21 @@
         <v>3</v>
       </c>
       <c r="L279" s="2">
-        <v>4</v>
+        <v>5</v>
       </c>
     </row>
     <row r="280">
       <c r="A280" s="2">
-        <v>5319</v>
+        <v>5453</v>
       </c>
       <c r="B280" s="2" t="str">
-        <v>Sohm</v>
+        <v>Ricci S.</v>
       </c>
       <c r="C280" s="2" t="str">
         <v/>
       </c>
       <c r="D280" s="2" t="str">
-        <v>Venezia</v>
+        <v>Milan</v>
       </c>
       <c r="E280" s="2">
         <v>25</v>
@@ -11039,7 +11033,7 @@
         <v>C</v>
       </c>
       <c r="G280" s="2" t="str">
-        <v>C</v>
+        <v>M/C</v>
       </c>
       <c r="H280" s="2">
         <v>0</v>
@@ -11054,24 +11048,24 @@
         <v>3</v>
       </c>
       <c r="L280" s="2">
-        <v>5</v>
+        <v>4</v>
       </c>
     </row>
     <row r="281">
       <c r="A281" s="2">
-        <v>4911</v>
+        <v>5319</v>
       </c>
       <c r="B281" s="2" t="str">
-        <v>Douglas Luiz</v>
+        <v>Sohm</v>
       </c>
       <c r="C281" s="2" t="str">
         <v/>
       </c>
       <c r="D281" s="2" t="str">
-        <v>Juventus</v>
+        <v>Venezia</v>
       </c>
       <c r="E281" s="2">
-        <v>28</v>
+        <v>25</v>
       </c>
       <c r="F281" s="2" t="str">
         <v>C</v>
@@ -11092,30 +11086,30 @@
         <v>3</v>
       </c>
       <c r="L281" s="2">
-        <v>4</v>
+        <v>5</v>
       </c>
     </row>
     <row r="282">
       <c r="A282" s="2">
-        <v>4199</v>
+        <v>4911</v>
       </c>
       <c r="B282" s="2" t="str">
-        <v>Loftus-Cheek</v>
+        <v>Douglas Luiz</v>
       </c>
       <c r="C282" s="2" t="str">
         <v/>
       </c>
       <c r="D282" s="2" t="str">
-        <v>Milan</v>
+        <v>Juventus</v>
       </c>
       <c r="E282" s="2">
-        <v>30</v>
+        <v>28</v>
       </c>
       <c r="F282" s="2" t="str">
         <v>C</v>
       </c>
       <c r="G282" s="2" t="str">
-        <v>C/T</v>
+        <v>C</v>
       </c>
       <c r="H282" s="2">
         <v>0</v>
@@ -11135,25 +11129,25 @@
     </row>
     <row r="283">
       <c r="A283" s="2">
-        <v>2857</v>
+        <v>4199</v>
       </c>
       <c r="B283" s="2" t="str">
-        <v>Traorè Hj.</v>
+        <v>Loftus-Cheek</v>
       </c>
       <c r="C283" s="2" t="str">
         <v/>
       </c>
       <c r="D283" s="2" t="str">
-        <v>Genoa</v>
+        <v>Milan</v>
       </c>
       <c r="E283" s="2">
-        <v>26</v>
+        <v>30</v>
       </c>
       <c r="F283" s="2" t="str">
         <v>C</v>
       </c>
       <c r="G283" s="2" t="str">
-        <v>W/T</v>
+        <v>C/T</v>
       </c>
       <c r="H283" s="2">
         <v>0</v>
@@ -11168,30 +11162,30 @@
         <v>3</v>
       </c>
       <c r="L283" s="2">
-        <v>5</v>
+        <v>4</v>
       </c>
     </row>
     <row r="284">
       <c r="A284" s="2">
-        <v>22</v>
+        <v>2857</v>
       </c>
       <c r="B284" s="2" t="str">
-        <v>De Roon</v>
+        <v>Traorè Hj.</v>
       </c>
       <c r="C284" s="2" t="str">
         <v/>
       </c>
       <c r="D284" s="2" t="str">
-        <v>Atalanta</v>
+        <v>Genoa</v>
       </c>
       <c r="E284" s="2">
-        <v>35</v>
+        <v>26</v>
       </c>
       <c r="F284" s="2" t="str">
         <v>C</v>
       </c>
       <c r="G284" s="2" t="str">
-        <v>M/C</v>
+        <v>W/T</v>
       </c>
       <c r="H284" s="2">
         <v>0</v>
@@ -11211,25 +11205,25 @@
     </row>
     <row r="285">
       <c r="A285" s="2">
-        <v>7532</v>
+        <v>22</v>
       </c>
       <c r="B285" s="2" t="str">
-        <v>Kofler</v>
+        <v>De Roon</v>
       </c>
       <c r="C285" s="2" t="str">
         <v/>
       </c>
       <c r="D285" s="2" t="str">
-        <v>Cagliari</v>
+        <v>Atalanta</v>
       </c>
       <c r="E285" s="2">
-        <v>21</v>
+        <v>35</v>
       </c>
       <c r="F285" s="2" t="str">
-        <v>D</v>
+        <v>C</v>
       </c>
       <c r="G285" s="2" t="str">
-        <v>Dc</v>
+        <v>M/C</v>
       </c>
       <c r="H285" s="2">
         <v>0</v>
@@ -11249,25 +11243,25 @@
     </row>
     <row r="286">
       <c r="A286" s="2">
-        <v>7469</v>
+        <v>7532</v>
       </c>
       <c r="B286" s="2" t="str">
-        <v>Bracaglia</v>
+        <v>Kofler</v>
       </c>
       <c r="C286" s="2" t="str">
         <v/>
       </c>
       <c r="D286" s="2" t="str">
-        <v>Frosinone</v>
+        <v>Cagliari</v>
       </c>
       <c r="E286" s="2">
-        <v>23</v>
+        <v>21</v>
       </c>
       <c r="F286" s="2" t="str">
         <v>D</v>
       </c>
       <c r="G286" s="2" t="str">
-        <v>Ds/Dc</v>
+        <v>Dc</v>
       </c>
       <c r="H286" s="2">
         <v>0</v>
@@ -11287,25 +11281,25 @@
     </row>
     <row r="287">
       <c r="A287" s="2">
-        <v>7274</v>
+        <v>7469</v>
       </c>
       <c r="B287" s="2" t="str">
-        <v>Zè Pedro</v>
+        <v>Bracaglia</v>
       </c>
       <c r="C287" s="2" t="str">
         <v/>
       </c>
       <c r="D287" s="2" t="str">
-        <v>Cagliari</v>
+        <v>Frosinone</v>
       </c>
       <c r="E287" s="2">
-        <v>29</v>
+        <v>23</v>
       </c>
       <c r="F287" s="2" t="str">
         <v>D</v>
       </c>
       <c r="G287" s="2" t="str">
-        <v>Dd/Dc</v>
+        <v>Ds/Dc</v>
       </c>
       <c r="H287" s="2">
         <v>0</v>
@@ -11320,15 +11314,15 @@
         <v>3</v>
       </c>
       <c r="L287" s="2">
-        <v>6</v>
+        <v>5</v>
       </c>
     </row>
     <row r="288">
       <c r="A288" s="2">
-        <v>7268</v>
+        <v>7274</v>
       </c>
       <c r="B288" s="2" t="str">
-        <v>Rodriguez Ju.</v>
+        <v>Zè Pedro</v>
       </c>
       <c r="C288" s="2" t="str">
         <v/>
@@ -11337,13 +11331,13 @@
         <v>Cagliari</v>
       </c>
       <c r="E288" s="2">
-        <v>21</v>
+        <v>29</v>
       </c>
       <c r="F288" s="2" t="str">
         <v>D</v>
       </c>
       <c r="G288" s="2" t="str">
-        <v>Ds/Dc</v>
+        <v>Dd/Dc</v>
       </c>
       <c r="H288" s="2">
         <v>0</v>
@@ -11358,30 +11352,30 @@
         <v>3</v>
       </c>
       <c r="L288" s="2">
-        <v>4</v>
+        <v>6</v>
       </c>
     </row>
     <row r="289">
       <c r="A289" s="2">
-        <v>7255</v>
+        <v>7268</v>
       </c>
       <c r="B289" s="2" t="str">
-        <v>Britschgi</v>
+        <v>Rodriguez Ju.</v>
       </c>
       <c r="C289" s="2" t="str">
         <v/>
       </c>
       <c r="D289" s="2" t="str">
-        <v>Parma</v>
+        <v>Cagliari</v>
       </c>
       <c r="E289" s="2">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="F289" s="2" t="str">
         <v>D</v>
       </c>
       <c r="G289" s="2" t="str">
-        <v>Dd/Ds/E</v>
+        <v>Ds/Dc</v>
       </c>
       <c r="H289" s="2">
         <v>0</v>
@@ -11401,25 +11395,25 @@
     </row>
     <row r="290">
       <c r="A290" s="2">
-        <v>7253</v>
+        <v>7255</v>
       </c>
       <c r="B290" s="2" t="str">
-        <v>Bella-Kotchap</v>
+        <v>Britschgi</v>
       </c>
       <c r="C290" s="2" t="str">
         <v/>
       </c>
       <c r="D290" s="2" t="str">
-        <v>Venezia</v>
+        <v>Parma</v>
       </c>
       <c r="E290" s="2">
-        <v>25</v>
+        <v>20</v>
       </c>
       <c r="F290" s="2" t="str">
         <v>D</v>
       </c>
       <c r="G290" s="2" t="str">
-        <v>Dc</v>
+        <v>Dd/Ds/E</v>
       </c>
       <c r="H290" s="2">
         <v>0</v>
@@ -11434,24 +11428,24 @@
         <v>3</v>
       </c>
       <c r="L290" s="2">
-        <v>6</v>
+        <v>4</v>
       </c>
     </row>
     <row r="291">
       <c r="A291" s="2">
-        <v>7240</v>
+        <v>7253</v>
       </c>
       <c r="B291" s="2" t="str">
-        <v>Siebert</v>
+        <v>Bella-Kotchap</v>
       </c>
       <c r="C291" s="2" t="str">
         <v/>
       </c>
       <c r="D291" s="2" t="str">
-        <v>Lecce</v>
+        <v>Venezia</v>
       </c>
       <c r="E291" s="2">
-        <v>24</v>
+        <v>25</v>
       </c>
       <c r="F291" s="2" t="str">
         <v>D</v>
@@ -11472,30 +11466,30 @@
         <v>3</v>
       </c>
       <c r="L291" s="2">
-        <v>4</v>
+        <v>6</v>
       </c>
     </row>
     <row r="292">
       <c r="A292" s="2">
-        <v>7131</v>
+        <v>7240</v>
       </c>
       <c r="B292" s="2" t="str">
-        <v>Floriani Mussolini</v>
+        <v>Siebert</v>
       </c>
       <c r="C292" s="2" t="str">
         <v/>
       </c>
       <c r="D292" s="2" t="str">
-        <v>Lazio</v>
+        <v>Lecce</v>
       </c>
       <c r="E292" s="2">
-        <v>23</v>
+        <v>24</v>
       </c>
       <c r="F292" s="2" t="str">
         <v>D</v>
       </c>
       <c r="G292" s="2" t="str">
-        <v>Dd/E</v>
+        <v>Dc</v>
       </c>
       <c r="H292" s="2">
         <v>0</v>
@@ -11510,21 +11504,21 @@
         <v>3</v>
       </c>
       <c r="L292" s="2">
-        <v>3</v>
+        <v>4</v>
       </c>
     </row>
     <row r="293">
       <c r="A293" s="2">
-        <v>7068</v>
+        <v>7131</v>
       </c>
       <c r="B293" s="2" t="str">
-        <v>Vitik</v>
+        <v>Floriani Mussolini</v>
       </c>
       <c r="C293" s="2" t="str">
         <v/>
       </c>
       <c r="D293" s="2" t="str">
-        <v>Bologna</v>
+        <v>Lazio</v>
       </c>
       <c r="E293" s="2">
         <v>23</v>
@@ -11533,7 +11527,7 @@
         <v>D</v>
       </c>
       <c r="G293" s="2" t="str">
-        <v>Dc</v>
+        <v>Dd/E</v>
       </c>
       <c r="H293" s="2">
         <v>0</v>
@@ -11548,30 +11542,30 @@
         <v>3</v>
       </c>
       <c r="L293" s="2">
-        <v>5</v>
+        <v>3</v>
       </c>
     </row>
     <row r="294">
       <c r="A294" s="2">
-        <v>6990</v>
+        <v>7068</v>
       </c>
       <c r="B294" s="2" t="str">
-        <v>Veiga D.</v>
+        <v>Vitik</v>
       </c>
       <c r="C294" s="2" t="str">
         <v/>
       </c>
       <c r="D294" s="2" t="str">
-        <v>Lecce</v>
+        <v>Bologna</v>
       </c>
       <c r="E294" s="2">
-        <v>24</v>
+        <v>23</v>
       </c>
       <c r="F294" s="2" t="str">
         <v>D</v>
       </c>
       <c r="G294" s="2" t="str">
-        <v>Dd/E</v>
+        <v>Dc</v>
       </c>
       <c r="H294" s="2">
         <v>0</v>
@@ -11591,25 +11585,25 @@
     </row>
     <row r="295">
       <c r="A295" s="2">
-        <v>6985</v>
+        <v>6990</v>
       </c>
       <c r="B295" s="2" t="str">
-        <v>Candè</v>
+        <v>Veiga D.</v>
       </c>
       <c r="C295" s="2" t="str">
         <v/>
       </c>
       <c r="D295" s="2" t="str">
-        <v>Sassuolo</v>
+        <v>Lecce</v>
       </c>
       <c r="E295" s="2">
-        <v>28</v>
+        <v>24</v>
       </c>
       <c r="F295" s="2" t="str">
         <v>D</v>
       </c>
       <c r="G295" s="2" t="str">
-        <v>Ds/Dc</v>
+        <v>Dd/E</v>
       </c>
       <c r="H295" s="2">
         <v>0</v>
@@ -11624,30 +11618,30 @@
         <v>3</v>
       </c>
       <c r="L295" s="2">
-        <v>3</v>
+        <v>5</v>
       </c>
     </row>
     <row r="296">
       <c r="A296" s="2">
-        <v>6893</v>
+        <v>6985</v>
       </c>
       <c r="B296" s="2" t="str">
-        <v>Kempf</v>
+        <v>Candè</v>
       </c>
       <c r="C296" s="2" t="str">
         <v/>
       </c>
       <c r="D296" s="2" t="str">
-        <v>Como</v>
+        <v>Sassuolo</v>
       </c>
       <c r="E296" s="2">
-        <v>31</v>
+        <v>28</v>
       </c>
       <c r="F296" s="2" t="str">
         <v>D</v>
       </c>
       <c r="G296" s="2" t="str">
-        <v>Dc</v>
+        <v>Ds/Dc</v>
       </c>
       <c r="H296" s="2">
         <v>0</v>
@@ -11662,24 +11656,24 @@
         <v>3</v>
       </c>
       <c r="L296" s="2">
-        <v>5</v>
+        <v>3</v>
       </c>
     </row>
     <row r="297">
       <c r="A297" s="2">
-        <v>6890</v>
+        <v>6893</v>
       </c>
       <c r="B297" s="2" t="str">
-        <v>Moreno M.</v>
+        <v>Kempf</v>
       </c>
       <c r="C297" s="2" t="str">
         <v/>
       </c>
       <c r="D297" s="2" t="str">
-        <v>Venezia</v>
+        <v>Como</v>
       </c>
       <c r="E297" s="2">
-        <v>23</v>
+        <v>31</v>
       </c>
       <c r="F297" s="2" t="str">
         <v>D</v>
@@ -11705,25 +11699,25 @@
     </row>
     <row r="298">
       <c r="A298" s="2">
-        <v>6766</v>
+        <v>6890</v>
       </c>
       <c r="B298" s="2" t="str">
-        <v>Kelly L.</v>
+        <v>Moreno M.</v>
       </c>
       <c r="C298" s="2" t="str">
         <v/>
       </c>
       <c r="D298" s="2" t="str">
-        <v>Juventus</v>
+        <v>Venezia</v>
       </c>
       <c r="E298" s="2">
-        <v>28</v>
+        <v>23</v>
       </c>
       <c r="F298" s="2" t="str">
         <v>D</v>
       </c>
       <c r="G298" s="2" t="str">
-        <v>Ds/Dc</v>
+        <v>Dc</v>
       </c>
       <c r="H298" s="2">
         <v>0</v>
@@ -11738,30 +11732,30 @@
         <v>3</v>
       </c>
       <c r="L298" s="2">
-        <v>6</v>
+        <v>5</v>
       </c>
     </row>
     <row r="299">
       <c r="A299" s="2">
-        <v>6660</v>
+        <v>6766</v>
       </c>
       <c r="B299" s="2" t="str">
-        <v>Marcandalli</v>
+        <v>Kelly L.</v>
       </c>
       <c r="C299" s="2" t="str">
         <v/>
       </c>
       <c r="D299" s="2" t="str">
-        <v>Genoa</v>
+        <v>Juventus</v>
       </c>
       <c r="E299" s="2">
-        <v>24</v>
+        <v>28</v>
       </c>
       <c r="F299" s="2" t="str">
         <v>D</v>
       </c>
       <c r="G299" s="2" t="str">
-        <v>Dc</v>
+        <v>Ds/Dc</v>
       </c>
       <c r="H299" s="2">
         <v>0</v>
@@ -11781,19 +11775,19 @@
     </row>
     <row r="300">
       <c r="A300" s="2">
-        <v>6659</v>
+        <v>6660</v>
       </c>
       <c r="B300" s="2" t="str">
-        <v>Lucchesi</v>
+        <v>Marcandalli</v>
       </c>
       <c r="C300" s="2" t="str">
         <v/>
       </c>
       <c r="D300" s="2" t="str">
-        <v>Monza</v>
+        <v>Genoa</v>
       </c>
       <c r="E300" s="2">
-        <v>23</v>
+        <v>24</v>
       </c>
       <c r="F300" s="2" t="str">
         <v>D</v>
@@ -11814,24 +11808,24 @@
         <v>3</v>
       </c>
       <c r="L300" s="2">
-        <v>4</v>
+        <v>6</v>
       </c>
     </row>
     <row r="301">
       <c r="A301" s="2">
-        <v>6632</v>
+        <v>6659</v>
       </c>
       <c r="B301" s="2" t="str">
-        <v>Gaspar K.</v>
+        <v>Lucchesi</v>
       </c>
       <c r="C301" s="2" t="str">
         <v/>
       </c>
       <c r="D301" s="2" t="str">
-        <v>Lecce</v>
+        <v>Monza</v>
       </c>
       <c r="E301" s="2">
-        <v>29</v>
+        <v>23</v>
       </c>
       <c r="F301" s="2" t="str">
         <v>D</v>
@@ -11852,24 +11846,24 @@
         <v>3</v>
       </c>
       <c r="L301" s="2">
-        <v>5</v>
+        <v>4</v>
       </c>
     </row>
     <row r="302">
       <c r="A302" s="2">
-        <v>6495</v>
+        <v>6632</v>
       </c>
       <c r="B302" s="2" t="str">
-        <v>Comuzzo</v>
+        <v>Gaspar K.</v>
       </c>
       <c r="C302" s="2" t="str">
         <v/>
       </c>
       <c r="D302" s="2" t="str">
-        <v>Torino</v>
+        <v>Lecce</v>
       </c>
       <c r="E302" s="2">
-        <v>21</v>
+        <v>29</v>
       </c>
       <c r="F302" s="2" t="str">
         <v>D</v>
@@ -11890,15 +11884,15 @@
         <v>3</v>
       </c>
       <c r="L302" s="2">
-        <v>6</v>
+        <v>5</v>
       </c>
     </row>
     <row r="303">
       <c r="A303" s="2">
-        <v>6426</v>
+        <v>6495</v>
       </c>
       <c r="B303" s="2" t="str">
-        <v>Pedersen</v>
+        <v>Comuzzo</v>
       </c>
       <c r="C303" s="2" t="str">
         <v/>
@@ -11907,13 +11901,13 @@
         <v>Torino</v>
       </c>
       <c r="E303" s="2">
-        <v>26</v>
+        <v>21</v>
       </c>
       <c r="F303" s="2" t="str">
         <v>D</v>
       </c>
       <c r="G303" s="2" t="str">
-        <v>Dd/E</v>
+        <v>Dc</v>
       </c>
       <c r="H303" s="2">
         <v>0</v>
@@ -11928,24 +11922,24 @@
         <v>3</v>
       </c>
       <c r="L303" s="2">
-        <v>5</v>
+        <v>6</v>
       </c>
     </row>
     <row r="304">
       <c r="A304" s="2">
-        <v>6238</v>
+        <v>6426</v>
       </c>
       <c r="B304" s="2" t="str">
-        <v>Oyono A.</v>
+        <v>Pedersen</v>
       </c>
       <c r="C304" s="2" t="str">
         <v/>
       </c>
       <c r="D304" s="2" t="str">
-        <v>Frosinone</v>
+        <v>Torino</v>
       </c>
       <c r="E304" s="2">
-        <v>25</v>
+        <v>26</v>
       </c>
       <c r="F304" s="2" t="str">
         <v>D</v>
@@ -11971,25 +11965,25 @@
     </row>
     <row r="305">
       <c r="A305" s="2">
-        <v>6202</v>
+        <v>6238</v>
       </c>
       <c r="B305" s="2" t="str">
-        <v>Beukema</v>
+        <v>Oyono A.</v>
       </c>
       <c r="C305" s="2" t="str">
         <v/>
       </c>
       <c r="D305" s="2" t="str">
-        <v>Napoli</v>
+        <v>Frosinone</v>
       </c>
       <c r="E305" s="2">
-        <v>28</v>
+        <v>25</v>
       </c>
       <c r="F305" s="2" t="str">
         <v>D</v>
       </c>
       <c r="G305" s="2" t="str">
-        <v>Dc</v>
+        <v>Dd/E</v>
       </c>
       <c r="H305" s="2">
         <v>0</v>
@@ -12004,30 +11998,30 @@
         <v>3</v>
       </c>
       <c r="L305" s="2">
-        <v>6</v>
+        <v>5</v>
       </c>
     </row>
     <row r="306">
       <c r="A306" s="2">
-        <v>5838</v>
+        <v>6202</v>
       </c>
       <c r="B306" s="2" t="str">
-        <v>Birindelli</v>
+        <v>Beukema</v>
       </c>
       <c r="C306" s="2" t="str">
         <v/>
       </c>
       <c r="D306" s="2" t="str">
-        <v>Monza</v>
+        <v>Napoli</v>
       </c>
       <c r="E306" s="2">
-        <v>27</v>
+        <v>28</v>
       </c>
       <c r="F306" s="2" t="str">
         <v>D</v>
       </c>
       <c r="G306" s="2" t="str">
-        <v>Dd/Ds/E</v>
+        <v>Dc</v>
       </c>
       <c r="H306" s="2">
         <v>0</v>
@@ -12042,30 +12036,30 @@
         <v>3</v>
       </c>
       <c r="L306" s="2">
-        <v>5</v>
+        <v>6</v>
       </c>
     </row>
     <row r="307">
       <c r="A307" s="2">
-        <v>5820</v>
+        <v>5838</v>
       </c>
       <c r="B307" s="2" t="str">
-        <v>Bertola</v>
+        <v>Birindelli</v>
       </c>
       <c r="C307" s="2" t="str">
         <v/>
       </c>
       <c r="D307" s="2" t="str">
-        <v>Udinese</v>
+        <v>Monza</v>
       </c>
       <c r="E307" s="2">
-        <v>23</v>
+        <v>27</v>
       </c>
       <c r="F307" s="2" t="str">
         <v>D</v>
       </c>
       <c r="G307" s="2" t="str">
-        <v>Dd/Ds/Dc</v>
+        <v>Dd/Ds/E</v>
       </c>
       <c r="H307" s="2">
         <v>0</v>
@@ -12080,30 +12074,30 @@
         <v>3</v>
       </c>
       <c r="L307" s="2">
-        <v>6</v>
+        <v>5</v>
       </c>
     </row>
     <row r="308">
       <c r="A308" s="2">
-        <v>5739</v>
+        <v>5820</v>
       </c>
       <c r="B308" s="2" t="str">
-        <v>De Winter</v>
+        <v>Bertola</v>
       </c>
       <c r="C308" s="2" t="str">
         <v/>
       </c>
       <c r="D308" s="2" t="str">
-        <v>Milan</v>
+        <v>Udinese</v>
       </c>
       <c r="E308" s="2">
-        <v>24</v>
+        <v>23</v>
       </c>
       <c r="F308" s="2" t="str">
         <v>D</v>
       </c>
       <c r="G308" s="2" t="str">
-        <v>Dd/Dc</v>
+        <v>Dd/Ds/Dc</v>
       </c>
       <c r="H308" s="2">
         <v>0</v>
@@ -12118,30 +12112,30 @@
         <v>3</v>
       </c>
       <c r="L308" s="2">
-        <v>4</v>
+        <v>6</v>
       </c>
     </row>
     <row r="309">
       <c r="A309" s="2">
-        <v>5695</v>
+        <v>5739</v>
       </c>
       <c r="B309" s="2" t="str">
-        <v>Haps</v>
+        <v>De Winter</v>
       </c>
       <c r="C309" s="2" t="str">
         <v/>
       </c>
       <c r="D309" s="2" t="str">
-        <v>Venezia</v>
+        <v>Milan</v>
       </c>
       <c r="E309" s="2">
-        <v>33</v>
+        <v>24</v>
       </c>
       <c r="F309" s="2" t="str">
         <v>D</v>
       </c>
       <c r="G309" s="2" t="str">
-        <v>Ds/E</v>
+        <v>Dd/Dc</v>
       </c>
       <c r="H309" s="2">
         <v>0</v>
@@ -12156,30 +12150,30 @@
         <v>3</v>
       </c>
       <c r="L309" s="2">
-        <v>5</v>
+        <v>4</v>
       </c>
     </row>
     <row r="310">
       <c r="A310" s="2">
-        <v>5678</v>
+        <v>5695</v>
       </c>
       <c r="B310" s="2" t="str">
-        <v>Holm</v>
+        <v>Haps</v>
       </c>
       <c r="C310" s="2" t="str">
         <v/>
       </c>
       <c r="D310" s="2" t="str">
-        <v>Bologna</v>
+        <v>Venezia</v>
       </c>
       <c r="E310" s="2">
-        <v>26</v>
+        <v>33</v>
       </c>
       <c r="F310" s="2" t="str">
         <v>D</v>
       </c>
       <c r="G310" s="2" t="str">
-        <v>Dd/E</v>
+        <v>Ds/E</v>
       </c>
       <c r="H310" s="2">
         <v>0</v>
@@ -12199,25 +12193,25 @@
     </row>
     <row r="311">
       <c r="A311" s="2">
-        <v>5555</v>
+        <v>5678</v>
       </c>
       <c r="B311" s="2" t="str">
-        <v>Kamara H.</v>
+        <v>Holm</v>
       </c>
       <c r="C311" s="2" t="str">
         <v/>
       </c>
       <c r="D311" s="2" t="str">
-        <v>Udinese</v>
+        <v>Bologna</v>
       </c>
       <c r="E311" s="2">
-        <v>32</v>
+        <v>26</v>
       </c>
       <c r="F311" s="2" t="str">
         <v>D</v>
       </c>
       <c r="G311" s="2" t="str">
-        <v>Ds/E</v>
+        <v>Dd/E</v>
       </c>
       <c r="H311" s="2">
         <v>0</v>
@@ -12232,24 +12226,24 @@
         <v>3</v>
       </c>
       <c r="L311" s="2">
-        <v>6</v>
+        <v>5</v>
       </c>
     </row>
     <row r="312">
       <c r="A312" s="2">
-        <v>5449</v>
+        <v>5555</v>
       </c>
       <c r="B312" s="2" t="str">
-        <v>Parisi</v>
+        <v>Kamara H.</v>
       </c>
       <c r="C312" s="2" t="str">
         <v/>
       </c>
       <c r="D312" s="2" t="str">
-        <v>Fiorentina</v>
+        <v>Udinese</v>
       </c>
       <c r="E312" s="2">
-        <v>26</v>
+        <v>32</v>
       </c>
       <c r="F312" s="2" t="str">
         <v>D</v>
@@ -12270,30 +12264,30 @@
         <v>3</v>
       </c>
       <c r="L312" s="2">
-        <v>5</v>
+        <v>6</v>
       </c>
     </row>
     <row r="313">
       <c r="A313" s="2">
-        <v>4952</v>
+        <v>5449</v>
       </c>
       <c r="B313" s="2" t="str">
-        <v>Monterisi</v>
+        <v>Parisi</v>
       </c>
       <c r="C313" s="2" t="str">
         <v/>
       </c>
       <c r="D313" s="2" t="str">
-        <v>Frosinone</v>
+        <v>Fiorentina</v>
       </c>
       <c r="E313" s="2">
-        <v>25</v>
+        <v>26</v>
       </c>
       <c r="F313" s="2" t="str">
         <v>D</v>
       </c>
       <c r="G313" s="2" t="str">
-        <v>Dc</v>
+        <v>Ds/E</v>
       </c>
       <c r="H313" s="2">
         <v>0</v>
@@ -12308,21 +12302,21 @@
         <v>3</v>
       </c>
       <c r="L313" s="2">
-        <v>6</v>
+        <v>5</v>
       </c>
     </row>
     <row r="314">
       <c r="A314" s="2">
-        <v>4925</v>
+        <v>4952</v>
       </c>
       <c r="B314" s="2" t="str">
-        <v>Carboni A.</v>
+        <v>Monterisi</v>
       </c>
       <c r="C314" s="2" t="str">
         <v/>
       </c>
       <c r="D314" s="2" t="str">
-        <v>Monza</v>
+        <v>Frosinone</v>
       </c>
       <c r="E314" s="2">
         <v>25</v>
@@ -12331,7 +12325,7 @@
         <v>D</v>
       </c>
       <c r="G314" s="2" t="str">
-        <v>Ds/Dc</v>
+        <v>Dc</v>
       </c>
       <c r="H314" s="2">
         <v>0</v>
@@ -12346,30 +12340,30 @@
         <v>3</v>
       </c>
       <c r="L314" s="2">
-        <v>4</v>
+        <v>6</v>
       </c>
     </row>
     <row r="315">
       <c r="A315" s="2">
-        <v>4845</v>
+        <v>4925</v>
       </c>
       <c r="B315" s="2" t="str">
-        <v>Correia T.</v>
+        <v>Carboni A.</v>
       </c>
       <c r="C315" s="2" t="str">
         <v/>
       </c>
       <c r="D315" s="2" t="str">
-        <v>Venezia</v>
+        <v>Monza</v>
       </c>
       <c r="E315" s="2">
-        <v>27</v>
+        <v>25</v>
       </c>
       <c r="F315" s="2" t="str">
         <v>D</v>
       </c>
       <c r="G315" s="2" t="str">
-        <v>Dd/E</v>
+        <v>Ds/Dc</v>
       </c>
       <c r="H315" s="2">
         <v>0</v>
@@ -12389,25 +12383,25 @@
     </row>
     <row r="316">
       <c r="A316" s="2">
-        <v>4772</v>
+        <v>4845</v>
       </c>
       <c r="B316" s="2" t="str">
-        <v>Angelino</v>
+        <v>Correia T.</v>
       </c>
       <c r="C316" s="2" t="str">
-        <v>*</v>
+        <v/>
       </c>
       <c r="D316" s="2" t="str">
-        <v>Roma</v>
+        <v>Venezia</v>
       </c>
       <c r="E316" s="2">
-        <v>29</v>
+        <v>27</v>
       </c>
       <c r="F316" s="2" t="str">
         <v>D</v>
       </c>
       <c r="G316" s="2" t="str">
-        <v>E</v>
+        <v>Dd/E</v>
       </c>
       <c r="H316" s="2">
         <v>0</v>
@@ -12422,21 +12416,21 @@
         <v>3</v>
       </c>
       <c r="L316" s="2">
-        <v>3</v>
+        <v>4</v>
       </c>
     </row>
     <row r="317">
       <c r="A317" s="2">
-        <v>4751</v>
+        <v>4772</v>
       </c>
       <c r="B317" s="2" t="str">
-        <v>Tomori</v>
+        <v>Angelino</v>
       </c>
       <c r="C317" s="2" t="str">
-        <v/>
+        <v>*</v>
       </c>
       <c r="D317" s="2" t="str">
-        <v>Milan</v>
+        <v>Roma</v>
       </c>
       <c r="E317" s="2">
         <v>29</v>
@@ -12445,7 +12439,7 @@
         <v>D</v>
       </c>
       <c r="G317" s="2" t="str">
-        <v>Dc</v>
+        <v>E</v>
       </c>
       <c r="H317" s="2">
         <v>0</v>
@@ -12460,30 +12454,30 @@
         <v>3</v>
       </c>
       <c r="L317" s="2">
-        <v>7</v>
+        <v>3</v>
       </c>
     </row>
     <row r="318">
       <c r="A318" s="2">
-        <v>4502</v>
+        <v>4751</v>
       </c>
       <c r="B318" s="2" t="str">
-        <v>Gallo</v>
+        <v>Tomori</v>
       </c>
       <c r="C318" s="2" t="str">
         <v/>
       </c>
       <c r="D318" s="2" t="str">
-        <v>Lecce</v>
+        <v>Milan</v>
       </c>
       <c r="E318" s="2">
-        <v>26</v>
+        <v>29</v>
       </c>
       <c r="F318" s="2" t="str">
         <v>D</v>
       </c>
       <c r="G318" s="2" t="str">
-        <v>Ds/E</v>
+        <v>Dc</v>
       </c>
       <c r="H318" s="2">
         <v>0</v>
@@ -12498,30 +12492,30 @@
         <v>3</v>
       </c>
       <c r="L318" s="2">
-        <v>6</v>
+        <v>7</v>
       </c>
     </row>
     <row r="319">
       <c r="A319" s="2">
-        <v>4461</v>
+        <v>4502</v>
       </c>
       <c r="B319" s="2" t="str">
-        <v>Zappa</v>
+        <v>Gallo</v>
       </c>
       <c r="C319" s="2" t="str">
         <v/>
       </c>
       <c r="D319" s="2" t="str">
-        <v>Cagliari</v>
+        <v>Lecce</v>
       </c>
       <c r="E319" s="2">
-        <v>27</v>
+        <v>26</v>
       </c>
       <c r="F319" s="2" t="str">
         <v>D</v>
       </c>
       <c r="G319" s="2" t="str">
-        <v>B/Dd/E</v>
+        <v>Ds/E</v>
       </c>
       <c r="H319" s="2">
         <v>0</v>
@@ -12536,21 +12530,21 @@
         <v>3</v>
       </c>
       <c r="L319" s="2">
-        <v>4</v>
+        <v>6</v>
       </c>
     </row>
     <row r="320">
       <c r="A320" s="2">
-        <v>4375</v>
+        <v>4461</v>
       </c>
       <c r="B320" s="2" t="str">
-        <v>Terzic</v>
+        <v>Zappa</v>
       </c>
       <c r="C320" s="2" t="str">
         <v/>
       </c>
       <c r="D320" s="2" t="str">
-        <v>Frosinone</v>
+        <v>Cagliari</v>
       </c>
       <c r="E320" s="2">
         <v>27</v>
@@ -12559,7 +12553,7 @@
         <v>D</v>
       </c>
       <c r="G320" s="2" t="str">
-        <v>Ds/E</v>
+        <v>B/Dd/E</v>
       </c>
       <c r="H320" s="2">
         <v>0</v>
@@ -12579,25 +12573,25 @@
     </row>
     <row r="321">
       <c r="A321" s="2">
-        <v>4374</v>
+        <v>4375</v>
       </c>
       <c r="B321" s="2" t="str">
-        <v>Walukiewicz</v>
+        <v>Terzic</v>
       </c>
       <c r="C321" s="2" t="str">
         <v/>
       </c>
       <c r="D321" s="2" t="str">
-        <v>Sassuolo</v>
+        <v>Frosinone</v>
       </c>
       <c r="E321" s="2">
-        <v>26</v>
+        <v>27</v>
       </c>
       <c r="F321" s="2" t="str">
         <v>D</v>
       </c>
       <c r="G321" s="2" t="str">
-        <v>Dd/Dc</v>
+        <v>Ds/E</v>
       </c>
       <c r="H321" s="2">
         <v>0</v>
@@ -12617,25 +12611,25 @@
     </row>
     <row r="322">
       <c r="A322" s="2">
-        <v>2640</v>
+        <v>4374</v>
       </c>
       <c r="B322" s="2" t="str">
-        <v>Kolasinac</v>
+        <v>Walukiewicz</v>
       </c>
       <c r="C322" s="2" t="str">
         <v/>
       </c>
       <c r="D322" s="2" t="str">
-        <v>Atalanta</v>
+        <v>Sassuolo</v>
       </c>
       <c r="E322" s="2">
-        <v>33</v>
+        <v>26</v>
       </c>
       <c r="F322" s="2" t="str">
         <v>D</v>
       </c>
       <c r="G322" s="2" t="str">
-        <v>Ds/Dc</v>
+        <v>Dd/Dc</v>
       </c>
       <c r="H322" s="2">
         <v>0</v>
@@ -12650,30 +12644,30 @@
         <v>3</v>
       </c>
       <c r="L322" s="2">
-        <v>6</v>
+        <v>4</v>
       </c>
     </row>
     <row r="323">
       <c r="A323" s="2">
-        <v>2115</v>
+        <v>2640</v>
       </c>
       <c r="B323" s="2" t="str">
-        <v>Delli Carri</v>
+        <v>Kolasinac</v>
       </c>
       <c r="C323" s="2" t="str">
         <v/>
       </c>
       <c r="D323" s="2" t="str">
-        <v>Monza</v>
+        <v>Atalanta</v>
       </c>
       <c r="E323" s="2">
-        <v>27</v>
+        <v>33</v>
       </c>
       <c r="F323" s="2" t="str">
         <v>D</v>
       </c>
       <c r="G323" s="2" t="str">
-        <v>Dc</v>
+        <v>Ds/Dc</v>
       </c>
       <c r="H323" s="2">
         <v>0</v>
@@ -12688,30 +12682,30 @@
         <v>3</v>
       </c>
       <c r="L323" s="2">
-        <v>4</v>
+        <v>6</v>
       </c>
     </row>
     <row r="324">
       <c r="A324" s="2">
-        <v>6248</v>
+        <v>2115</v>
       </c>
       <c r="B324" s="2" t="str">
-        <v>Stankovic F.</v>
+        <v>Delli Carri</v>
       </c>
       <c r="C324" s="2" t="str">
         <v/>
       </c>
       <c r="D324" s="2" t="str">
-        <v>Venezia</v>
+        <v>Monza</v>
       </c>
       <c r="E324" s="2">
-        <v>24</v>
+        <v>27</v>
       </c>
       <c r="F324" s="2" t="str">
-        <v>P</v>
+        <v>D</v>
       </c>
       <c r="G324" s="2" t="str">
-        <v>Por</v>
+        <v>Dc</v>
       </c>
       <c r="H324" s="2">
         <v>0</v>
@@ -12726,24 +12720,24 @@
         <v>3</v>
       </c>
       <c r="L324" s="2">
-        <v>6</v>
+        <v>4</v>
       </c>
     </row>
     <row r="325">
       <c r="A325" s="2">
-        <v>4485</v>
+        <v>6248</v>
       </c>
       <c r="B325" s="2" t="str">
-        <v>Thiam</v>
+        <v>Stankovic F.</v>
       </c>
       <c r="C325" s="2" t="str">
         <v/>
       </c>
       <c r="D325" s="2" t="str">
-        <v>Monza</v>
+        <v>Venezia</v>
       </c>
       <c r="E325" s="2">
-        <v>28</v>
+        <v>24</v>
       </c>
       <c r="F325" s="2" t="str">
         <v>P</v>
@@ -12764,15 +12758,15 @@
         <v>3</v>
       </c>
       <c r="L325" s="2">
-        <v>5</v>
+        <v>6</v>
       </c>
     </row>
     <row r="326">
       <c r="A326" s="2">
-        <v>7546</v>
+        <v>4485</v>
       </c>
       <c r="B326" s="2" t="str">
-        <v>Robinson J.</v>
+        <v>Thiam</v>
       </c>
       <c r="C326" s="2" t="str">
         <v/>
@@ -12781,13 +12775,13 @@
         <v>Monza</v>
       </c>
       <c r="E326" s="2">
-        <v>19</v>
+        <v>28</v>
       </c>
       <c r="F326" s="2" t="str">
-        <v>A</v>
+        <v>P</v>
       </c>
       <c r="G326" s="2" t="str">
-        <v>A</v>
+        <v>Por</v>
       </c>
       <c r="H326" s="2">
         <v>0</v>
@@ -12799,33 +12793,33 @@
         <v>0</v>
       </c>
       <c r="K326" s="2">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="L326" s="2">
-        <v>4</v>
+        <v>5</v>
       </c>
     </row>
     <row r="327">
       <c r="A327" s="2">
-        <v>7453</v>
+        <v>7546</v>
       </c>
       <c r="B327" s="2" t="str">
-        <v>Havel</v>
+        <v>Robinson J.</v>
       </c>
       <c r="C327" s="2" t="str">
         <v/>
       </c>
       <c r="D327" s="2" t="str">
-        <v>Genoa</v>
+        <v>Monza</v>
       </c>
       <c r="E327" s="2">
-        <v>23</v>
+        <v>19</v>
       </c>
       <c r="F327" s="2" t="str">
         <v>A</v>
       </c>
       <c r="G327" s="2" t="str">
-        <v>Pc</v>
+        <v>A</v>
       </c>
       <c r="H327" s="2">
         <v>0</v>
@@ -12840,24 +12834,24 @@
         <v>2</v>
       </c>
       <c r="L327" s="2">
-        <v>3</v>
+        <v>4</v>
       </c>
     </row>
     <row r="328">
       <c r="A328" s="2">
-        <v>7374</v>
+        <v>7453</v>
       </c>
       <c r="B328" s="2" t="str">
-        <v>Mendy P.</v>
+        <v>Havel</v>
       </c>
       <c r="C328" s="2" t="str">
         <v/>
       </c>
       <c r="D328" s="2" t="str">
-        <v>Cagliari</v>
+        <v>Genoa</v>
       </c>
       <c r="E328" s="2">
-        <v>19</v>
+        <v>23</v>
       </c>
       <c r="F328" s="2" t="str">
         <v>A</v>
@@ -12883,19 +12877,19 @@
     </row>
     <row r="329">
       <c r="A329" s="2">
-        <v>7349</v>
+        <v>7374</v>
       </c>
       <c r="B329" s="2" t="str">
-        <v>Kulenovic</v>
+        <v>Mendy P.</v>
       </c>
       <c r="C329" s="2" t="str">
         <v/>
       </c>
       <c r="D329" s="2" t="str">
-        <v>Torino</v>
+        <v>Cagliari</v>
       </c>
       <c r="E329" s="2">
-        <v>27</v>
+        <v>19</v>
       </c>
       <c r="F329" s="2" t="str">
         <v>A</v>
@@ -12921,19 +12915,19 @@
     </row>
     <row r="330">
       <c r="A330" s="2">
-        <v>7342</v>
+        <v>7349</v>
       </c>
       <c r="B330" s="2" t="str">
-        <v>Elphege</v>
+        <v>Kulenovic</v>
       </c>
       <c r="C330" s="2" t="str">
         <v/>
       </c>
       <c r="D330" s="2" t="str">
-        <v>Parma</v>
+        <v>Torino</v>
       </c>
       <c r="E330" s="2">
-        <v>25</v>
+        <v>27</v>
       </c>
       <c r="F330" s="2" t="str">
         <v>A</v>
@@ -12959,25 +12953,25 @@
     </row>
     <row r="331">
       <c r="A331" s="2">
-        <v>7162</v>
+        <v>7342</v>
       </c>
       <c r="B331" s="2" t="str">
-        <v>Giovane</v>
+        <v>Elphege</v>
       </c>
       <c r="C331" s="2" t="str">
         <v/>
       </c>
       <c r="D331" s="2" t="str">
-        <v>Napoli</v>
+        <v>Parma</v>
       </c>
       <c r="E331" s="2">
-        <v>23</v>
+        <v>25</v>
       </c>
       <c r="F331" s="2" t="str">
         <v>A</v>
       </c>
       <c r="G331" s="2" t="str">
-        <v>A</v>
+        <v>Pc</v>
       </c>
       <c r="H331" s="2">
         <v>0</v>
@@ -12992,30 +12986,30 @@
         <v>2</v>
       </c>
       <c r="L331" s="2">
-        <v>4</v>
+        <v>3</v>
       </c>
     </row>
     <row r="332">
       <c r="A332" s="2">
-        <v>7128</v>
+        <v>7162</v>
       </c>
       <c r="B332" s="2" t="str">
-        <v>Kuhn</v>
+        <v>Giovane</v>
       </c>
       <c r="C332" s="2" t="str">
         <v/>
       </c>
       <c r="D332" s="2" t="str">
-        <v>Como</v>
+        <v>Napoli</v>
       </c>
       <c r="E332" s="2">
-        <v>26</v>
+        <v>23</v>
       </c>
       <c r="F332" s="2" t="str">
         <v>A</v>
       </c>
       <c r="G332" s="2" t="str">
-        <v>W/A</v>
+        <v>A</v>
       </c>
       <c r="H332" s="2">
         <v>0</v>
@@ -13035,25 +13029,25 @@
     </row>
     <row r="333">
       <c r="A333" s="2">
-        <v>7120</v>
+        <v>7128</v>
       </c>
       <c r="B333" s="2" t="str">
-        <v>Lang</v>
+        <v>Kuhn</v>
       </c>
       <c r="C333" s="2" t="str">
         <v/>
       </c>
       <c r="D333" s="2" t="str">
-        <v>Napoli</v>
+        <v>Como</v>
       </c>
       <c r="E333" s="2">
-        <v>27</v>
+        <v>26</v>
       </c>
       <c r="F333" s="2" t="str">
         <v>A</v>
       </c>
       <c r="G333" s="2" t="str">
-        <v>A</v>
+        <v>W/A</v>
       </c>
       <c r="H333" s="2">
         <v>0</v>
@@ -13068,24 +13062,24 @@
         <v>2</v>
       </c>
       <c r="L333" s="2">
-        <v>3</v>
+        <v>4</v>
       </c>
     </row>
     <row r="334">
       <c r="A334" s="2">
-        <v>6822</v>
+        <v>7120</v>
       </c>
       <c r="B334" s="2" t="str">
-        <v>Ekhator</v>
+        <v>Lang</v>
       </c>
       <c r="C334" s="2" t="str">
         <v/>
       </c>
       <c r="D334" s="2" t="str">
-        <v>Juventus</v>
+        <v>Napoli</v>
       </c>
       <c r="E334" s="2">
-        <v>20</v>
+        <v>27</v>
       </c>
       <c r="F334" s="2" t="str">
         <v>A</v>
@@ -13111,25 +13105,25 @@
     </row>
     <row r="335">
       <c r="A335" s="2">
-        <v>6643</v>
+        <v>6822</v>
       </c>
       <c r="B335" s="2" t="str">
-        <v>Dallinga</v>
+        <v>Ekhator</v>
       </c>
       <c r="C335" s="2" t="str">
         <v/>
       </c>
       <c r="D335" s="2" t="str">
-        <v>Bologna</v>
+        <v>Juventus</v>
       </c>
       <c r="E335" s="2">
-        <v>26</v>
+        <v>20</v>
       </c>
       <c r="F335" s="2" t="str">
         <v>A</v>
       </c>
       <c r="G335" s="2" t="str">
-        <v>Pc</v>
+        <v>A</v>
       </c>
       <c r="H335" s="2">
         <v>0</v>
@@ -13144,21 +13138,21 @@
         <v>2</v>
       </c>
       <c r="L335" s="2">
-        <v>7</v>
+        <v>3</v>
       </c>
     </row>
     <row r="336">
       <c r="A336" s="2">
-        <v>6243</v>
+        <v>6643</v>
       </c>
       <c r="B336" s="2" t="str">
-        <v>Borrelli</v>
+        <v>Dallinga</v>
       </c>
       <c r="C336" s="2" t="str">
-        <v/>
+        <v>*</v>
       </c>
       <c r="D336" s="2" t="str">
-        <v>Cagliari</v>
+        <v>Bologna</v>
       </c>
       <c r="E336" s="2">
         <v>26</v>
@@ -13182,21 +13176,21 @@
         <v>2</v>
       </c>
       <c r="L336" s="2">
-        <v>3</v>
+        <v>7</v>
       </c>
     </row>
     <row r="337">
       <c r="A337" s="2">
-        <v>6215</v>
+        <v>6243</v>
       </c>
       <c r="B337" s="2" t="str">
-        <v>Lucca</v>
+        <v>Borrelli</v>
       </c>
       <c r="C337" s="2" t="str">
         <v/>
       </c>
       <c r="D337" s="2" t="str">
-        <v>Napoli</v>
+        <v>Cagliari</v>
       </c>
       <c r="E337" s="2">
         <v>26</v>
@@ -13225,19 +13219,19 @@
     </row>
     <row r="338">
       <c r="A338" s="2">
-        <v>313</v>
+        <v>6215</v>
       </c>
       <c r="B338" s="2" t="str">
-        <v>Morata</v>
+        <v>Lucca</v>
       </c>
       <c r="C338" s="2" t="str">
         <v/>
       </c>
       <c r="D338" s="2" t="str">
-        <v>Como</v>
+        <v>Napoli</v>
       </c>
       <c r="E338" s="2">
-        <v>34</v>
+        <v>26</v>
       </c>
       <c r="F338" s="2" t="str">
         <v>A</v>
@@ -13263,25 +13257,25 @@
     </row>
     <row r="339">
       <c r="A339" s="2">
-        <v>7536</v>
+        <v>313</v>
       </c>
       <c r="B339" s="2" t="str">
-        <v>Diallo O.</v>
+        <v>Morata</v>
       </c>
       <c r="C339" s="2" t="str">
         <v/>
       </c>
       <c r="D339" s="2" t="str">
-        <v>Parma</v>
+        <v>Como</v>
       </c>
       <c r="E339" s="2">
-        <v>19</v>
+        <v>34</v>
       </c>
       <c r="F339" s="2" t="str">
-        <v>C</v>
+        <v>A</v>
       </c>
       <c r="G339" s="2" t="str">
-        <v>W/A</v>
+        <v>Pc</v>
       </c>
       <c r="H339" s="2">
         <v>0</v>
@@ -13296,30 +13290,30 @@
         <v>2</v>
       </c>
       <c r="L339" s="2">
-        <v>2</v>
+        <v>3</v>
       </c>
     </row>
     <row r="340">
       <c r="A340" s="2">
-        <v>7477</v>
+        <v>7536</v>
       </c>
       <c r="B340" s="2" t="str">
-        <v>Colombo L.</v>
+        <v>Diallo O.</v>
       </c>
       <c r="C340" s="2" t="str">
         <v/>
       </c>
       <c r="D340" s="2" t="str">
-        <v>Monza</v>
+        <v>Parma</v>
       </c>
       <c r="E340" s="2">
-        <v>21</v>
+        <v>19</v>
       </c>
       <c r="F340" s="2" t="str">
         <v>C</v>
       </c>
       <c r="G340" s="2" t="str">
-        <v>M/C</v>
+        <v>W/A</v>
       </c>
       <c r="H340" s="2">
         <v>0</v>
@@ -13334,21 +13328,21 @@
         <v>2</v>
       </c>
       <c r="L340" s="2">
-        <v>3</v>
+        <v>2</v>
       </c>
     </row>
     <row r="341">
       <c r="A341" s="2">
-        <v>7127</v>
+        <v>7477</v>
       </c>
       <c r="B341" s="2" t="str">
-        <v>Addai</v>
+        <v>Colombo L.</v>
       </c>
       <c r="C341" s="2" t="str">
         <v/>
       </c>
       <c r="D341" s="2" t="str">
-        <v>Como</v>
+        <v>Monza</v>
       </c>
       <c r="E341" s="2">
         <v>21</v>
@@ -13357,7 +13351,7 @@
         <v>C</v>
       </c>
       <c r="G341" s="2" t="str">
-        <v>W/A</v>
+        <v>M/C</v>
       </c>
       <c r="H341" s="2">
         <v>0</v>
@@ -13372,30 +13366,30 @@
         <v>2</v>
       </c>
       <c r="L341" s="2">
-        <v>4</v>
+        <v>3</v>
       </c>
     </row>
     <row r="342">
       <c r="A342" s="2">
-        <v>6640</v>
+        <v>7127</v>
       </c>
       <c r="B342" s="2" t="str">
-        <v>Felici</v>
+        <v>Addai</v>
       </c>
       <c r="C342" s="2" t="str">
         <v/>
       </c>
       <c r="D342" s="2" t="str">
-        <v>Cagliari</v>
+        <v>Como</v>
       </c>
       <c r="E342" s="2">
-        <v>25</v>
+        <v>21</v>
       </c>
       <c r="F342" s="2" t="str">
         <v>C</v>
       </c>
       <c r="G342" s="2" t="str">
-        <v>W</v>
+        <v>W/A</v>
       </c>
       <c r="H342" s="2">
         <v>0</v>
@@ -13415,19 +13409,19 @@
     </row>
     <row r="343">
       <c r="A343" s="2">
-        <v>6506</v>
+        <v>6640</v>
       </c>
       <c r="B343" s="2" t="str">
-        <v xml:space="preserve">Fini </v>
+        <v>Felici</v>
       </c>
       <c r="C343" s="2" t="str">
         <v/>
       </c>
       <c r="D343" s="2" t="str">
-        <v>Frosinone</v>
+        <v>Cagliari</v>
       </c>
       <c r="E343" s="2">
-        <v>20</v>
+        <v>25</v>
       </c>
       <c r="F343" s="2" t="str">
         <v>C</v>
@@ -13448,30 +13442,30 @@
         <v>2</v>
       </c>
       <c r="L343" s="2">
-        <v>2</v>
+        <v>4</v>
       </c>
     </row>
     <row r="344">
       <c r="A344" s="2">
-        <v>6424</v>
+        <v>6618</v>
       </c>
       <c r="B344" s="2" t="str">
-        <v>Prati</v>
+        <v>Cissè A.</v>
       </c>
       <c r="C344" s="2" t="str">
         <v/>
       </c>
       <c r="D344" s="2" t="str">
-        <v>Cagliari</v>
+        <v>Milan</v>
       </c>
       <c r="E344" s="2">
-        <v>23</v>
+        <v>20</v>
       </c>
       <c r="F344" s="2" t="str">
         <v>C</v>
       </c>
       <c r="G344" s="2" t="str">
-        <v>M/C</v>
+        <v>W/T</v>
       </c>
       <c r="H344" s="2">
         <v>0</v>
@@ -13486,30 +13480,30 @@
         <v>2</v>
       </c>
       <c r="L344" s="2">
-        <v>4</v>
+        <v>3</v>
       </c>
     </row>
     <row r="345">
       <c r="A345" s="2">
-        <v>6252</v>
+        <v>6506</v>
       </c>
       <c r="B345" s="2" t="str">
-        <v>Folorunsho</v>
+        <v xml:space="preserve">Fini </v>
       </c>
       <c r="C345" s="2" t="str">
         <v/>
       </c>
       <c r="D345" s="2" t="str">
-        <v>Napoli</v>
+        <v>Frosinone</v>
       </c>
       <c r="E345" s="2">
-        <v>28</v>
+        <v>20</v>
       </c>
       <c r="F345" s="2" t="str">
         <v>C</v>
       </c>
       <c r="G345" s="2" t="str">
-        <v>C/T</v>
+        <v>W</v>
       </c>
       <c r="H345" s="2">
         <v>0</v>
@@ -13524,30 +13518,30 @@
         <v>2</v>
       </c>
       <c r="L345" s="2">
-        <v>4</v>
+        <v>2</v>
       </c>
     </row>
     <row r="346">
       <c r="A346" s="2">
-        <v>6241</v>
+        <v>6424</v>
       </c>
       <c r="B346" s="2" t="str">
-        <v>Gelli F.</v>
+        <v>Prati</v>
       </c>
       <c r="C346" s="2" t="str">
         <v/>
       </c>
       <c r="D346" s="2" t="str">
-        <v>Frosinone</v>
+        <v>Cagliari</v>
       </c>
       <c r="E346" s="2">
-        <v>30</v>
+        <v>23</v>
       </c>
       <c r="F346" s="2" t="str">
         <v>C</v>
       </c>
       <c r="G346" s="2" t="str">
-        <v>C/T</v>
+        <v>M/C</v>
       </c>
       <c r="H346" s="2">
         <v>0</v>
@@ -13562,24 +13556,24 @@
         <v>2</v>
       </c>
       <c r="L346" s="2">
-        <v>3</v>
+        <v>4</v>
       </c>
     </row>
     <row r="347">
       <c r="A347" s="2">
-        <v>6206</v>
+        <v>6252</v>
       </c>
       <c r="B347" s="2" t="str">
-        <v>Fabbian</v>
+        <v>Folorunsho</v>
       </c>
       <c r="C347" s="2" t="str">
         <v/>
       </c>
       <c r="D347" s="2" t="str">
-        <v>Fiorentina</v>
+        <v>Napoli</v>
       </c>
       <c r="E347" s="2">
-        <v>23</v>
+        <v>28</v>
       </c>
       <c r="F347" s="2" t="str">
         <v>C</v>
@@ -13605,25 +13599,25 @@
     </row>
     <row r="348">
       <c r="A348" s="2">
-        <v>6024</v>
+        <v>6241</v>
       </c>
       <c r="B348" s="2" t="str">
-        <v>Sulemana I.</v>
+        <v>Gelli F.</v>
       </c>
       <c r="C348" s="2" t="str">
         <v/>
       </c>
       <c r="D348" s="2" t="str">
-        <v>Atalanta</v>
+        <v>Frosinone</v>
       </c>
       <c r="E348" s="2">
-        <v>23</v>
+        <v>30</v>
       </c>
       <c r="F348" s="2" t="str">
         <v>C</v>
       </c>
       <c r="G348" s="2" t="str">
-        <v>M/C</v>
+        <v>C/T</v>
       </c>
       <c r="H348" s="2">
         <v>0</v>
@@ -13643,19 +13637,19 @@
     </row>
     <row r="349">
       <c r="A349" s="2">
-        <v>5872</v>
+        <v>6206</v>
       </c>
       <c r="B349" s="2" t="str">
-        <v>Helgason</v>
+        <v>Fabbian</v>
       </c>
       <c r="C349" s="2" t="str">
         <v/>
       </c>
       <c r="D349" s="2" t="str">
-        <v>Venezia</v>
+        <v>Fiorentina</v>
       </c>
       <c r="E349" s="2">
-        <v>26</v>
+        <v>23</v>
       </c>
       <c r="F349" s="2" t="str">
         <v>C</v>
@@ -13676,24 +13670,24 @@
         <v>2</v>
       </c>
       <c r="L349" s="2">
-        <v>3</v>
+        <v>4</v>
       </c>
     </row>
     <row r="350">
       <c r="A350" s="2">
-        <v>5131</v>
+        <v>6024</v>
       </c>
       <c r="B350" s="2" t="str">
-        <v>Gilmour</v>
+        <v>Sulemana I.</v>
       </c>
       <c r="C350" s="2" t="str">
         <v/>
       </c>
       <c r="D350" s="2" t="str">
-        <v>Napoli</v>
+        <v>Atalanta</v>
       </c>
       <c r="E350" s="2">
-        <v>25</v>
+        <v>23</v>
       </c>
       <c r="F350" s="2" t="str">
         <v>C</v>
@@ -13719,25 +13713,25 @@
     </row>
     <row r="351">
       <c r="A351" s="2">
-        <v>4970</v>
+        <v>5872</v>
       </c>
       <c r="B351" s="2" t="str">
-        <v>Messias</v>
+        <v>Helgason</v>
       </c>
       <c r="C351" s="2" t="str">
         <v/>
       </c>
       <c r="D351" s="2" t="str">
-        <v>Genoa</v>
+        <v>Venezia</v>
       </c>
       <c r="E351" s="2">
-        <v>35</v>
+        <v>26</v>
       </c>
       <c r="F351" s="2" t="str">
         <v>C</v>
       </c>
       <c r="G351" s="2" t="str">
-        <v>W/T</v>
+        <v>C/T</v>
       </c>
       <c r="H351" s="2">
         <v>0</v>
@@ -13757,25 +13751,25 @@
     </row>
     <row r="352">
       <c r="A352" s="2">
-        <v>4947</v>
+        <v>5131</v>
       </c>
       <c r="B352" s="2" t="str">
-        <v>Brescianini</v>
+        <v>Gilmour</v>
       </c>
       <c r="C352" s="2" t="str">
         <v/>
       </c>
       <c r="D352" s="2" t="str">
-        <v>Fiorentina</v>
+        <v>Napoli</v>
       </c>
       <c r="E352" s="2">
-        <v>26</v>
+        <v>25</v>
       </c>
       <c r="F352" s="2" t="str">
         <v>C</v>
       </c>
       <c r="G352" s="2" t="str">
-        <v>C/T</v>
+        <v>M/C</v>
       </c>
       <c r="H352" s="2">
         <v>0</v>
@@ -13795,25 +13789,25 @@
     </row>
     <row r="353">
       <c r="A353" s="2">
-        <v>4856</v>
+        <v>4970</v>
       </c>
       <c r="B353" s="2" t="str">
-        <v>Chukwueze</v>
+        <v>Messias</v>
       </c>
       <c r="C353" s="2" t="str">
         <v/>
       </c>
       <c r="D353" s="2" t="str">
-        <v>Milan</v>
+        <v>Genoa</v>
       </c>
       <c r="E353" s="2">
-        <v>27</v>
+        <v>35</v>
       </c>
       <c r="F353" s="2" t="str">
         <v>C</v>
       </c>
       <c r="G353" s="2" t="str">
-        <v>W</v>
+        <v>W/T</v>
       </c>
       <c r="H353" s="2">
         <v>0</v>
@@ -13828,30 +13822,30 @@
         <v>2</v>
       </c>
       <c r="L353" s="2">
-        <v>5</v>
+        <v>3</v>
       </c>
     </row>
     <row r="354">
       <c r="A354" s="2">
-        <v>1871</v>
+        <v>4947</v>
       </c>
       <c r="B354" s="2" t="str">
-        <v>Deiola</v>
+        <v>Brescianini</v>
       </c>
       <c r="C354" s="2" t="str">
         <v/>
       </c>
       <c r="D354" s="2" t="str">
-        <v>Cagliari</v>
+        <v>Fiorentina</v>
       </c>
       <c r="E354" s="2">
-        <v>31</v>
+        <v>26</v>
       </c>
       <c r="F354" s="2" t="str">
         <v>C</v>
       </c>
       <c r="G354" s="2" t="str">
-        <v>M/C</v>
+        <v>C/T</v>
       </c>
       <c r="H354" s="2">
         <v>0</v>
@@ -13871,25 +13865,25 @@
     </row>
     <row r="355">
       <c r="A355" s="2">
-        <v>7540</v>
+        <v>4856</v>
       </c>
       <c r="B355" s="2" t="str">
-        <v>Akpoguma</v>
+        <v>Chukwueze</v>
       </c>
       <c r="C355" s="2" t="str">
         <v/>
       </c>
       <c r="D355" s="2" t="str">
-        <v>Frosinone</v>
+        <v>Milan</v>
       </c>
       <c r="E355" s="2">
-        <v>31</v>
+        <v>27</v>
       </c>
       <c r="F355" s="2" t="str">
-        <v>D</v>
+        <v>C</v>
       </c>
       <c r="G355" s="2" t="str">
-        <v>Dc</v>
+        <v>W</v>
       </c>
       <c r="H355" s="2">
         <v>0</v>
@@ -13904,30 +13898,30 @@
         <v>2</v>
       </c>
       <c r="L355" s="2">
-        <v>3</v>
+        <v>5</v>
       </c>
     </row>
     <row r="356">
       <c r="A356" s="2">
-        <v>7538</v>
+        <v>1871</v>
       </c>
       <c r="B356" s="2" t="str">
-        <v>Halhal</v>
+        <v>Deiola</v>
       </c>
       <c r="C356" s="2" t="str">
         <v/>
       </c>
       <c r="D356" s="2" t="str">
-        <v>Venezia</v>
+        <v>Cagliari</v>
       </c>
       <c r="E356" s="2">
-        <v>23</v>
+        <v>31</v>
       </c>
       <c r="F356" s="2" t="str">
-        <v>D</v>
+        <v>C</v>
       </c>
       <c r="G356" s="2" t="str">
-        <v>Dc</v>
+        <v>M/C</v>
       </c>
       <c r="H356" s="2">
         <v>0</v>
@@ -13942,30 +13936,30 @@
         <v>2</v>
       </c>
       <c r="L356" s="2">
-        <v>4</v>
+        <v>3</v>
       </c>
     </row>
     <row r="357">
       <c r="A357" s="2">
-        <v>7537</v>
+        <v>7540</v>
       </c>
       <c r="B357" s="2" t="str">
-        <v>Mitaj</v>
+        <v>Akpoguma</v>
       </c>
       <c r="C357" s="2" t="str">
         <v/>
       </c>
       <c r="D357" s="2" t="str">
-        <v>Genoa</v>
+        <v>Frosinone</v>
       </c>
       <c r="E357" s="2">
-        <v>23</v>
+        <v>31</v>
       </c>
       <c r="F357" s="2" t="str">
         <v>D</v>
       </c>
       <c r="G357" s="2" t="str">
-        <v>Ds/E</v>
+        <v>Dc</v>
       </c>
       <c r="H357" s="2">
         <v>0</v>
@@ -13980,24 +13974,24 @@
         <v>2</v>
       </c>
       <c r="L357" s="2">
-        <v>4</v>
+        <v>3</v>
       </c>
     </row>
     <row r="358">
       <c r="A358" s="2">
-        <v>7526</v>
+        <v>7538</v>
       </c>
       <c r="B358" s="2" t="str">
-        <v>Comert</v>
+        <v>Halhal</v>
       </c>
       <c r="C358" s="2" t="str">
         <v/>
       </c>
       <c r="D358" s="2" t="str">
-        <v>Torino</v>
+        <v>Venezia</v>
       </c>
       <c r="E358" s="2">
-        <v>28</v>
+        <v>23</v>
       </c>
       <c r="F358" s="2" t="str">
         <v>D</v>
@@ -14023,25 +14017,25 @@
     </row>
     <row r="359">
       <c r="A359" s="2">
-        <v>7467</v>
+        <v>7537</v>
       </c>
       <c r="B359" s="2" t="str">
-        <v>Calvani</v>
+        <v>Mitaj</v>
       </c>
       <c r="C359" s="2" t="str">
         <v/>
       </c>
       <c r="D359" s="2" t="str">
-        <v>Frosinone</v>
+        <v>Genoa</v>
       </c>
       <c r="E359" s="2">
-        <v>22</v>
+        <v>23</v>
       </c>
       <c r="F359" s="2" t="str">
         <v>D</v>
       </c>
       <c r="G359" s="2" t="str">
-        <v>Dc</v>
+        <v>Ds/E</v>
       </c>
       <c r="H359" s="2">
         <v>0</v>
@@ -14061,25 +14055,25 @@
     </row>
     <row r="360">
       <c r="A360" s="2">
-        <v>7413</v>
+        <v>7526</v>
       </c>
       <c r="B360" s="2" t="str">
-        <v>Puczka</v>
+        <v>Comert</v>
       </c>
       <c r="C360" s="2" t="str">
         <v/>
       </c>
       <c r="D360" s="2" t="str">
-        <v>Genoa</v>
+        <v>Torino</v>
       </c>
       <c r="E360" s="2">
-        <v>21</v>
+        <v>28</v>
       </c>
       <c r="F360" s="2" t="str">
         <v>D</v>
       </c>
       <c r="G360" s="2" t="str">
-        <v>Ds/E</v>
+        <v>Dc</v>
       </c>
       <c r="H360" s="2">
         <v>0</v>
@@ -14094,30 +14088,30 @@
         <v>2</v>
       </c>
       <c r="L360" s="2">
-        <v>2</v>
+        <v>4</v>
       </c>
     </row>
     <row r="361">
       <c r="A361" s="2">
-        <v>7407</v>
+        <v>7467</v>
       </c>
       <c r="B361" s="2" t="str">
-        <v>Cuenca A.</v>
+        <v>Calvani</v>
       </c>
       <c r="C361" s="2" t="str">
         <v/>
       </c>
       <c r="D361" s="2" t="str">
-        <v>Como</v>
+        <v>Frosinone</v>
       </c>
       <c r="E361" s="2">
-        <v>19</v>
+        <v>22</v>
       </c>
       <c r="F361" s="2" t="str">
         <v>D</v>
       </c>
       <c r="G361" s="2" t="str">
-        <v>Ds/Dc</v>
+        <v>Dc</v>
       </c>
       <c r="H361" s="2">
         <v>0</v>
@@ -14132,21 +14126,21 @@
         <v>2</v>
       </c>
       <c r="L361" s="2">
-        <v>1</v>
+        <v>4</v>
       </c>
     </row>
     <row r="362">
       <c r="A362" s="2">
-        <v>7312</v>
+        <v>7413</v>
       </c>
       <c r="B362" s="2" t="str">
-        <v>Arizala</v>
+        <v>Puczka</v>
       </c>
       <c r="C362" s="2" t="str">
         <v/>
       </c>
       <c r="D362" s="2" t="str">
-        <v>Udinese</v>
+        <v>Genoa</v>
       </c>
       <c r="E362" s="2">
         <v>21</v>
@@ -14170,30 +14164,30 @@
         <v>2</v>
       </c>
       <c r="L362" s="2">
-        <v>4</v>
+        <v>2</v>
       </c>
     </row>
     <row r="363">
       <c r="A363" s="2">
-        <v>7238</v>
+        <v>7407</v>
       </c>
       <c r="B363" s="2" t="str">
-        <v>Kouadio</v>
+        <v>Cuenca A.</v>
       </c>
       <c r="C363" s="2" t="str">
-        <v/>
+        <v>*</v>
       </c>
       <c r="D363" s="2" t="str">
-        <v>Monza</v>
+        <v>Como</v>
       </c>
       <c r="E363" s="2">
-        <v>20</v>
+        <v>19</v>
       </c>
       <c r="F363" s="2" t="str">
         <v>D</v>
       </c>
       <c r="G363" s="2" t="str">
-        <v>Dd/Dc</v>
+        <v>Ds/Dc</v>
       </c>
       <c r="H363" s="2">
         <v>0</v>
@@ -14208,30 +14202,30 @@
         <v>2</v>
       </c>
       <c r="L363" s="2">
-        <v>3</v>
+        <v>1</v>
       </c>
     </row>
     <row r="364">
       <c r="A364" s="2">
-        <v>7235</v>
+        <v>7312</v>
       </c>
       <c r="B364" s="2" t="str">
-        <v>Troilo</v>
+        <v>Arizala</v>
       </c>
       <c r="C364" s="2" t="str">
         <v/>
       </c>
       <c r="D364" s="2" t="str">
-        <v>Parma</v>
+        <v>Udinese</v>
       </c>
       <c r="E364" s="2">
-        <v>23</v>
+        <v>21</v>
       </c>
       <c r="F364" s="2" t="str">
         <v>D</v>
       </c>
       <c r="G364" s="2" t="str">
-        <v>Dc</v>
+        <v>Ds/E</v>
       </c>
       <c r="H364" s="2">
         <v>0</v>
@@ -14246,30 +14240,30 @@
         <v>2</v>
       </c>
       <c r="L364" s="2">
-        <v>3</v>
+        <v>4</v>
       </c>
     </row>
     <row r="365">
       <c r="A365" s="2">
-        <v>7211</v>
+        <v>7238</v>
       </c>
       <c r="B365" s="2" t="str">
-        <v>Athekame</v>
+        <v>Kouadio</v>
       </c>
       <c r="C365" s="2" t="str">
-        <v>*</v>
+        <v/>
       </c>
       <c r="D365" s="2" t="str">
-        <v>Milan</v>
+        <v>Monza</v>
       </c>
       <c r="E365" s="2">
-        <v>22</v>
+        <v>20</v>
       </c>
       <c r="F365" s="2" t="str">
         <v>D</v>
       </c>
       <c r="G365" s="2" t="str">
-        <v>Dd/E</v>
+        <v>Dd/Dc</v>
       </c>
       <c r="H365" s="2">
         <v>0</v>
@@ -14289,25 +14283,25 @@
     </row>
     <row r="366">
       <c r="A366" s="2">
-        <v>7175</v>
+        <v>7235</v>
       </c>
       <c r="B366" s="2" t="str">
-        <v>Joao Mario</v>
+        <v>Troilo</v>
       </c>
       <c r="C366" s="2" t="str">
         <v/>
       </c>
       <c r="D366" s="2" t="str">
-        <v>Fiorentina</v>
+        <v>Parma</v>
       </c>
       <c r="E366" s="2">
-        <v>26</v>
+        <v>23</v>
       </c>
       <c r="F366" s="2" t="str">
         <v>D</v>
       </c>
       <c r="G366" s="2" t="str">
-        <v>Dd/E</v>
+        <v>Dc</v>
       </c>
       <c r="H366" s="2">
         <v>0</v>
@@ -14327,25 +14321,25 @@
     </row>
     <row r="367">
       <c r="A367" s="2">
-        <v>7125</v>
+        <v>7211</v>
       </c>
       <c r="B367" s="2" t="str">
-        <v>Idrissi R.</v>
+        <v>Athekame</v>
       </c>
       <c r="C367" s="2" t="str">
-        <v/>
+        <v>*</v>
       </c>
       <c r="D367" s="2" t="str">
-        <v>Cagliari</v>
+        <v>Milan</v>
       </c>
       <c r="E367" s="2">
-        <v>21</v>
+        <v>22</v>
       </c>
       <c r="F367" s="2" t="str">
         <v>D</v>
       </c>
       <c r="G367" s="2" t="str">
-        <v>Ds/E</v>
+        <v>Dd/E</v>
       </c>
       <c r="H367" s="2">
         <v>0</v>
@@ -14365,16 +14359,16 @@
     </row>
     <row r="368">
       <c r="A368" s="2">
-        <v>7014</v>
+        <v>7175</v>
       </c>
       <c r="B368" s="2" t="str">
-        <v>Smolcic I.</v>
+        <v>Joao Mario</v>
       </c>
       <c r="C368" s="2" t="str">
         <v/>
       </c>
       <c r="D368" s="2" t="str">
-        <v>Como</v>
+        <v>Fiorentina</v>
       </c>
       <c r="E368" s="2">
         <v>26</v>
@@ -14398,30 +14392,30 @@
         <v>2</v>
       </c>
       <c r="L368" s="2">
-        <v>4</v>
+        <v>3</v>
       </c>
     </row>
     <row r="369">
       <c r="A369" s="2">
-        <v>7012</v>
+        <v>7125</v>
       </c>
       <c r="B369" s="2" t="str">
-        <v>Provstgaard</v>
+        <v>Idrissi R.</v>
       </c>
       <c r="C369" s="2" t="str">
         <v/>
       </c>
       <c r="D369" s="2" t="str">
-        <v>Lazio</v>
+        <v>Cagliari</v>
       </c>
       <c r="E369" s="2">
-        <v>23</v>
+        <v>21</v>
       </c>
       <c r="F369" s="2" t="str">
         <v>D</v>
       </c>
       <c r="G369" s="2" t="str">
-        <v>Dc</v>
+        <v>Ds/E</v>
       </c>
       <c r="H369" s="2">
         <v>0</v>
@@ -14441,25 +14435,25 @@
     </row>
     <row r="370">
       <c r="A370" s="2">
-        <v>6892</v>
+        <v>7014</v>
       </c>
       <c r="B370" s="2" t="str">
-        <v>Schingtienne</v>
+        <v>Smolcic I.</v>
       </c>
       <c r="C370" s="2" t="str">
         <v/>
       </c>
       <c r="D370" s="2" t="str">
-        <v>Venezia</v>
+        <v>Como</v>
       </c>
       <c r="E370" s="2">
-        <v>24</v>
+        <v>26</v>
       </c>
       <c r="F370" s="2" t="str">
         <v>D</v>
       </c>
       <c r="G370" s="2" t="str">
-        <v>Dc</v>
+        <v>Dd/E</v>
       </c>
       <c r="H370" s="2">
         <v>0</v>
@@ -14474,30 +14468,30 @@
         <v>2</v>
       </c>
       <c r="L370" s="2">
-        <v>3</v>
+        <v>4</v>
       </c>
     </row>
     <row r="371">
       <c r="A371" s="2">
-        <v>6821</v>
+        <v>7012</v>
       </c>
       <c r="B371" s="2" t="str">
-        <v>Hainaut</v>
+        <v>Provstgaard</v>
       </c>
       <c r="C371" s="2" t="str">
         <v/>
       </c>
       <c r="D371" s="2" t="str">
-        <v>Venezia</v>
+        <v>Lazio</v>
       </c>
       <c r="E371" s="2">
-        <v>24</v>
+        <v>23</v>
       </c>
       <c r="F371" s="2" t="str">
         <v>D</v>
       </c>
       <c r="G371" s="2" t="str">
-        <v>Dd/E</v>
+        <v>Dc</v>
       </c>
       <c r="H371" s="2">
         <v>0</v>
@@ -14517,10 +14511,10 @@
     </row>
     <row r="372">
       <c r="A372" s="2">
-        <v>6673</v>
+        <v>6892</v>
       </c>
       <c r="B372" s="2" t="str">
-        <v>Sverko</v>
+        <v>Schingtienne</v>
       </c>
       <c r="C372" s="2" t="str">
         <v/>
@@ -14529,13 +14523,13 @@
         <v>Venezia</v>
       </c>
       <c r="E372" s="2">
-        <v>28</v>
+        <v>24</v>
       </c>
       <c r="F372" s="2" t="str">
         <v>D</v>
       </c>
       <c r="G372" s="2" t="str">
-        <v>Ds/Dc</v>
+        <v>Dc</v>
       </c>
       <c r="H372" s="2">
         <v>0</v>
@@ -14555,25 +14549,25 @@
     </row>
     <row r="373">
       <c r="A373" s="2">
-        <v>6631</v>
+        <v>6821</v>
       </c>
       <c r="B373" s="2" t="str">
-        <v>Ghilardi</v>
+        <v>Hainaut</v>
       </c>
       <c r="C373" s="2" t="str">
         <v/>
       </c>
       <c r="D373" s="2" t="str">
-        <v>Roma</v>
+        <v>Venezia</v>
       </c>
       <c r="E373" s="2">
-        <v>23</v>
+        <v>24</v>
       </c>
       <c r="F373" s="2" t="str">
         <v>D</v>
       </c>
       <c r="G373" s="2" t="str">
-        <v>Dc</v>
+        <v>Dd/E</v>
       </c>
       <c r="H373" s="2">
         <v>0</v>
@@ -14588,30 +14582,30 @@
         <v>2</v>
       </c>
       <c r="L373" s="2">
-        <v>4</v>
+        <v>3</v>
       </c>
     </row>
     <row r="374">
       <c r="A374" s="2">
-        <v>5851</v>
+        <v>6673</v>
       </c>
       <c r="B374" s="2" t="str">
-        <v>Doig</v>
+        <v>Sverko</v>
       </c>
       <c r="C374" s="2" t="str">
         <v/>
       </c>
       <c r="D374" s="2" t="str">
-        <v>Sassuolo</v>
+        <v>Venezia</v>
       </c>
       <c r="E374" s="2">
-        <v>24</v>
+        <v>28</v>
       </c>
       <c r="F374" s="2" t="str">
         <v>D</v>
       </c>
       <c r="G374" s="2" t="str">
-        <v>Ds/E</v>
+        <v>Ds/Dc</v>
       </c>
       <c r="H374" s="2">
         <v>0</v>
@@ -14626,24 +14620,24 @@
         <v>2</v>
       </c>
       <c r="L374" s="2">
-        <v>4</v>
+        <v>3</v>
       </c>
     </row>
     <row r="375">
       <c r="A375" s="2">
-        <v>5831</v>
+        <v>6631</v>
       </c>
       <c r="B375" s="2" t="str">
-        <v>Gatti</v>
+        <v>Ghilardi</v>
       </c>
       <c r="C375" s="2" t="str">
         <v/>
       </c>
       <c r="D375" s="2" t="str">
-        <v>Juventus</v>
+        <v>Roma</v>
       </c>
       <c r="E375" s="2">
-        <v>28</v>
+        <v>23</v>
       </c>
       <c r="F375" s="2" t="str">
         <v>D</v>
@@ -14669,16 +14663,16 @@
     </row>
     <row r="376">
       <c r="A376" s="2">
-        <v>5757</v>
+        <v>5851</v>
       </c>
       <c r="B376" s="2" t="str">
-        <v>Cittadini</v>
+        <v>Doig</v>
       </c>
       <c r="C376" s="2" t="str">
         <v/>
       </c>
       <c r="D376" s="2" t="str">
-        <v>Frosinone</v>
+        <v>Sassuolo</v>
       </c>
       <c r="E376" s="2">
         <v>24</v>
@@ -14687,7 +14681,7 @@
         <v>D</v>
       </c>
       <c r="G376" s="2" t="str">
-        <v>Dc</v>
+        <v>Ds/E</v>
       </c>
       <c r="H376" s="2">
         <v>0</v>
@@ -14702,24 +14696,24 @@
         <v>2</v>
       </c>
       <c r="L376" s="2">
-        <v>3</v>
+        <v>4</v>
       </c>
     </row>
     <row r="377">
       <c r="A377" s="2">
-        <v>5603</v>
+        <v>5831</v>
       </c>
       <c r="B377" s="2" t="str">
-        <v>Pongracic</v>
+        <v>Gatti</v>
       </c>
       <c r="C377" s="2" t="str">
         <v/>
       </c>
       <c r="D377" s="2" t="str">
-        <v>Fiorentina</v>
+        <v>Juventus</v>
       </c>
       <c r="E377" s="2">
-        <v>29</v>
+        <v>28</v>
       </c>
       <c r="F377" s="2" t="str">
         <v>D</v>
@@ -14745,25 +14739,25 @@
     </row>
     <row r="378">
       <c r="A378" s="2">
-        <v>5578</v>
+        <v>5757</v>
       </c>
       <c r="B378" s="2" t="str">
-        <v>Kossounou</v>
+        <v>Cittadini</v>
       </c>
       <c r="C378" s="2" t="str">
         <v/>
       </c>
       <c r="D378" s="2" t="str">
-        <v>Atalanta</v>
+        <v>Frosinone</v>
       </c>
       <c r="E378" s="2">
-        <v>25</v>
+        <v>24</v>
       </c>
       <c r="F378" s="2" t="str">
         <v>D</v>
       </c>
       <c r="G378" s="2" t="str">
-        <v>Dd/Dc</v>
+        <v>Dc</v>
       </c>
       <c r="H378" s="2">
         <v>0</v>
@@ -14783,25 +14777,25 @@
     </row>
     <row r="379">
       <c r="A379" s="2">
-        <v>5527</v>
+        <v>5603</v>
       </c>
       <c r="B379" s="2" t="str">
-        <v>Zanoli</v>
+        <v>Pongracic</v>
       </c>
       <c r="C379" s="2" t="str">
         <v/>
       </c>
       <c r="D379" s="2" t="str">
-        <v>Udinese</v>
+        <v>Fiorentina</v>
       </c>
       <c r="E379" s="2">
-        <v>26</v>
+        <v>29</v>
       </c>
       <c r="F379" s="2" t="str">
         <v>D</v>
       </c>
       <c r="G379" s="2" t="str">
-        <v>Dd/E</v>
+        <v>Dc</v>
       </c>
       <c r="H379" s="2">
         <v>0</v>
@@ -14821,25 +14815,25 @@
     </row>
     <row r="380">
       <c r="A380" s="2">
-        <v>5307</v>
+        <v>5578</v>
       </c>
       <c r="B380" s="2" t="str">
-        <v>Valenti</v>
+        <v>Kossounou</v>
       </c>
       <c r="C380" s="2" t="str">
         <v/>
       </c>
       <c r="D380" s="2" t="str">
-        <v>Parma</v>
+        <v>Atalanta</v>
       </c>
       <c r="E380" s="2">
-        <v>27</v>
+        <v>25</v>
       </c>
       <c r="F380" s="2" t="str">
         <v>D</v>
       </c>
       <c r="G380" s="2" t="str">
-        <v>Dc</v>
+        <v>Dd/Dc</v>
       </c>
       <c r="H380" s="2">
         <v>0</v>
@@ -14854,30 +14848,30 @@
         <v>2</v>
       </c>
       <c r="L380" s="2">
-        <v>4</v>
+        <v>3</v>
       </c>
     </row>
     <row r="381">
       <c r="A381" s="2">
-        <v>5273</v>
+        <v>5527</v>
       </c>
       <c r="B381" s="2" t="str">
-        <v>Estupinan</v>
+        <v>Zanoli</v>
       </c>
       <c r="C381" s="2" t="str">
         <v/>
       </c>
       <c r="D381" s="2" t="str">
-        <v>Milan</v>
+        <v>Udinese</v>
       </c>
       <c r="E381" s="2">
-        <v>28</v>
+        <v>26</v>
       </c>
       <c r="F381" s="2" t="str">
         <v>D</v>
       </c>
       <c r="G381" s="2" t="str">
-        <v>Ds/E</v>
+        <v>Dd/E</v>
       </c>
       <c r="H381" s="2">
         <v>0</v>
@@ -14892,21 +14886,21 @@
         <v>2</v>
       </c>
       <c r="L381" s="2">
-        <v>3</v>
+        <v>4</v>
       </c>
     </row>
     <row r="382">
       <c r="A382" s="2">
-        <v>4378</v>
+        <v>5307</v>
       </c>
       <c r="B382" s="2" t="str">
-        <v>Ranieri L.</v>
+        <v>Valenti</v>
       </c>
       <c r="C382" s="2" t="str">
         <v/>
       </c>
       <c r="D382" s="2" t="str">
-        <v>Fiorentina</v>
+        <v>Parma</v>
       </c>
       <c r="E382" s="2">
         <v>27</v>
@@ -14915,7 +14909,7 @@
         <v>D</v>
       </c>
       <c r="G382" s="2" t="str">
-        <v>Ds/Dc</v>
+        <v>Dc</v>
       </c>
       <c r="H382" s="2">
         <v>0</v>
@@ -14930,30 +14924,30 @@
         <v>2</v>
       </c>
       <c r="L382" s="2">
-        <v>3</v>
+        <v>4</v>
       </c>
     </row>
     <row r="383">
       <c r="A383" s="2">
-        <v>4263</v>
+        <v>5273</v>
       </c>
       <c r="B383" s="2" t="str">
-        <v>Kabasele</v>
+        <v>Estupinan</v>
       </c>
       <c r="C383" s="2" t="str">
         <v/>
       </c>
       <c r="D383" s="2" t="str">
-        <v>Udinese</v>
+        <v>Milan</v>
       </c>
       <c r="E383" s="2">
-        <v>35</v>
+        <v>28</v>
       </c>
       <c r="F383" s="2" t="str">
         <v>D</v>
       </c>
       <c r="G383" s="2" t="str">
-        <v>Dc</v>
+        <v>Ds/E</v>
       </c>
       <c r="H383" s="2">
         <v>0</v>
@@ -14968,30 +14962,30 @@
         <v>2</v>
       </c>
       <c r="L383" s="2">
-        <v>4</v>
+        <v>3</v>
       </c>
     </row>
     <row r="384">
       <c r="A384" s="2">
-        <v>2263</v>
+        <v>4378</v>
       </c>
       <c r="B384" s="2" t="str">
-        <v>Lazzari</v>
+        <v>Ranieri L.</v>
       </c>
       <c r="C384" s="2" t="str">
         <v/>
       </c>
       <c r="D384" s="2" t="str">
-        <v>Lazio</v>
+        <v>Fiorentina</v>
       </c>
       <c r="E384" s="2">
-        <v>33</v>
+        <v>27</v>
       </c>
       <c r="F384" s="2" t="str">
         <v>D</v>
       </c>
       <c r="G384" s="2" t="str">
-        <v>Dd/E</v>
+        <v>Ds/Dc</v>
       </c>
       <c r="H384" s="2">
         <v>0</v>
@@ -15006,30 +15000,30 @@
         <v>2</v>
       </c>
       <c r="L384" s="2">
-        <v>2</v>
+        <v>3</v>
       </c>
     </row>
     <row r="385">
       <c r="A385" s="2">
-        <v>7463</v>
+        <v>4263</v>
       </c>
       <c r="B385" s="2" t="str">
-        <v>Desplanches</v>
+        <v>Kabasele</v>
       </c>
       <c r="C385" s="2" t="str">
         <v/>
       </c>
       <c r="D385" s="2" t="str">
-        <v>Frosinone</v>
+        <v>Udinese</v>
       </c>
       <c r="E385" s="2">
-        <v>23</v>
+        <v>35</v>
       </c>
       <c r="F385" s="2" t="str">
-        <v>P</v>
+        <v>D</v>
       </c>
       <c r="G385" s="2" t="str">
-        <v>Por</v>
+        <v>Dc</v>
       </c>
       <c r="H385" s="2">
         <v>0</v>
@@ -15044,30 +15038,30 @@
         <v>2</v>
       </c>
       <c r="L385" s="2">
-        <v>2</v>
+        <v>4</v>
       </c>
     </row>
     <row r="386">
       <c r="A386" s="2">
-        <v>6415</v>
+        <v>2263</v>
       </c>
       <c r="B386" s="2" t="str">
-        <v>Palmisani</v>
+        <v>Lazzari</v>
       </c>
       <c r="C386" s="2" t="str">
         <v/>
       </c>
       <c r="D386" s="2" t="str">
-        <v>Frosinone</v>
+        <v>Lazio</v>
       </c>
       <c r="E386" s="2">
-        <v>22</v>
+        <v>33</v>
       </c>
       <c r="F386" s="2" t="str">
-        <v>P</v>
+        <v>D</v>
       </c>
       <c r="G386" s="2" t="str">
-        <v>Por</v>
+        <v>Dd/E</v>
       </c>
       <c r="H386" s="2">
         <v>0</v>
@@ -15082,24 +15076,24 @@
         <v>2</v>
       </c>
       <c r="L386" s="2">
-        <v>4</v>
+        <v>2</v>
       </c>
     </row>
     <row r="387">
       <c r="A387" s="2">
-        <v>2170</v>
+        <v>7463</v>
       </c>
       <c r="B387" s="2" t="str">
-        <v>Milinkovic-Savic V.</v>
+        <v>Desplanches</v>
       </c>
       <c r="C387" s="2" t="str">
         <v/>
       </c>
       <c r="D387" s="2" t="str">
-        <v>Napoli</v>
+        <v>Frosinone</v>
       </c>
       <c r="E387" s="2">
-        <v>29</v>
+        <v>23</v>
       </c>
       <c r="F387" s="2" t="str">
         <v>P</v>
@@ -15120,24 +15114,24 @@
         <v>2</v>
       </c>
       <c r="L387" s="2">
-        <v>5</v>
+        <v>2</v>
       </c>
     </row>
     <row r="388">
       <c r="A388" s="2">
-        <v>218</v>
+        <v>6415</v>
       </c>
       <c r="B388" s="2" t="str">
-        <v>Perin</v>
+        <v>Palmisani</v>
       </c>
       <c r="C388" s="2" t="str">
         <v/>
       </c>
       <c r="D388" s="2" t="str">
-        <v>Juventus</v>
+        <v>Frosinone</v>
       </c>
       <c r="E388" s="2">
-        <v>34</v>
+        <v>22</v>
       </c>
       <c r="F388" s="2" t="str">
         <v>P</v>
@@ -15158,30 +15152,30 @@
         <v>2</v>
       </c>
       <c r="L388" s="2">
-        <v>6</v>
+        <v>4</v>
       </c>
     </row>
     <row r="389">
       <c r="A389" s="2">
-        <v>7523</v>
+        <v>5876</v>
       </c>
       <c r="B389" s="2" t="str">
-        <v>Varela G.</v>
+        <v>Di Gregorio</v>
       </c>
       <c r="C389" s="2" t="str">
         <v/>
       </c>
       <c r="D389" s="2" t="str">
-        <v>Monza</v>
+        <v>Juventus</v>
       </c>
       <c r="E389" s="2">
-        <v>21</v>
+        <v>29</v>
       </c>
       <c r="F389" s="2" t="str">
-        <v>A</v>
+        <v>P</v>
       </c>
       <c r="G389" s="2" t="str">
-        <v>Pc</v>
+        <v>Por</v>
       </c>
       <c r="H389" s="2">
         <v>0</v>
@@ -15193,33 +15187,33 @@
         <v>0</v>
       </c>
       <c r="K389" s="2">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="L389" s="2">
-        <v>3</v>
+        <v>9</v>
       </c>
     </row>
     <row r="390">
       <c r="A390" s="2">
-        <v>7482</v>
+        <v>2170</v>
       </c>
       <c r="B390" s="2" t="str">
-        <v>Lauberbach</v>
+        <v>Milinkovic-Savic V.</v>
       </c>
       <c r="C390" s="2" t="str">
         <v/>
       </c>
       <c r="D390" s="2" t="str">
-        <v>Venezia</v>
+        <v>Napoli</v>
       </c>
       <c r="E390" s="2">
-        <v>28</v>
+        <v>29</v>
       </c>
       <c r="F390" s="2" t="str">
-        <v>A</v>
+        <v>P</v>
       </c>
       <c r="G390" s="2" t="str">
-        <v>Pc</v>
+        <v>Por</v>
       </c>
       <c r="H390" s="2">
         <v>0</v>
@@ -15231,33 +15225,33 @@
         <v>0</v>
       </c>
       <c r="K390" s="2">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="L390" s="2">
-        <v>1</v>
+        <v>5</v>
       </c>
     </row>
     <row r="391">
       <c r="A391" s="2">
-        <v>7408</v>
+        <v>7568</v>
       </c>
       <c r="B391" s="2" t="str">
-        <v>Lisman</v>
+        <v>De Martis</v>
       </c>
       <c r="C391" s="2" t="str">
         <v/>
       </c>
       <c r="D391" s="2" t="str">
-        <v>Venezia</v>
+        <v>Parma</v>
       </c>
       <c r="E391" s="2">
-        <v>20</v>
+        <v>18</v>
       </c>
       <c r="F391" s="2" t="str">
         <v>A</v>
       </c>
       <c r="G391" s="2" t="str">
-        <v>W/A</v>
+        <v>Pc</v>
       </c>
       <c r="H391" s="2">
         <v>0</v>
@@ -15277,19 +15271,19 @@
     </row>
     <row r="392">
       <c r="A392" s="2">
-        <v>7338</v>
+        <v>7561</v>
       </c>
       <c r="B392" s="2" t="str">
-        <v>Albarracin</v>
+        <v>Lontani</v>
       </c>
       <c r="C392" s="2" t="str">
         <v/>
       </c>
       <c r="D392" s="2" t="str">
-        <v>Cagliari</v>
+        <v>Parma</v>
       </c>
       <c r="E392" s="2">
-        <v>21</v>
+        <v>18</v>
       </c>
       <c r="F392" s="2" t="str">
         <v>A</v>
@@ -15315,19 +15309,19 @@
     </row>
     <row r="393">
       <c r="A393" s="2">
-        <v>7317</v>
+        <v>7523</v>
       </c>
       <c r="B393" s="2" t="str">
-        <v>Trepy</v>
+        <v>Varela G.</v>
       </c>
       <c r="C393" s="2" t="str">
         <v/>
       </c>
       <c r="D393" s="2" t="str">
-        <v>Cagliari</v>
+        <v>Monza</v>
       </c>
       <c r="E393" s="2">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="F393" s="2" t="str">
         <v>A</v>
@@ -15348,24 +15342,24 @@
         <v>1</v>
       </c>
       <c r="L393" s="2">
-        <v>1</v>
+        <v>3</v>
       </c>
     </row>
     <row r="394">
       <c r="A394" s="2">
-        <v>7272</v>
+        <v>7482</v>
       </c>
       <c r="B394" s="2" t="str">
-        <v>Gueye</v>
+        <v>Lauberbach</v>
       </c>
       <c r="C394" s="2" t="str">
         <v/>
       </c>
       <c r="D394" s="2" t="str">
-        <v>Udinese</v>
+        <v>Venezia</v>
       </c>
       <c r="E394" s="2">
-        <v>20</v>
+        <v>28</v>
       </c>
       <c r="F394" s="2" t="str">
         <v>A</v>
@@ -15386,30 +15380,30 @@
         <v>1</v>
       </c>
       <c r="L394" s="2">
-        <v>3</v>
+        <v>1</v>
       </c>
     </row>
     <row r="395">
       <c r="A395" s="2">
-        <v>7249</v>
+        <v>7408</v>
       </c>
       <c r="B395" s="2" t="str">
-        <v>Buksa</v>
+        <v>Lisman</v>
       </c>
       <c r="C395" s="2" t="str">
         <v/>
       </c>
       <c r="D395" s="2" t="str">
-        <v>Udinese</v>
+        <v>Venezia</v>
       </c>
       <c r="E395" s="2">
-        <v>30</v>
+        <v>20</v>
       </c>
       <c r="F395" s="2" t="str">
         <v>A</v>
       </c>
       <c r="G395" s="2" t="str">
-        <v>Pc</v>
+        <v>W/A</v>
       </c>
       <c r="H395" s="2">
         <v>0</v>
@@ -15424,30 +15418,30 @@
         <v>1</v>
       </c>
       <c r="L395" s="2">
-        <v>2</v>
+        <v>1</v>
       </c>
     </row>
     <row r="396">
       <c r="A396" s="2">
-        <v>7161</v>
+        <v>7338</v>
       </c>
       <c r="B396" s="2" t="str">
-        <v>Bayo V.</v>
+        <v>Albarracin</v>
       </c>
       <c r="C396" s="2" t="str">
         <v/>
       </c>
       <c r="D396" s="2" t="str">
-        <v>Udinese</v>
+        <v>Cagliari</v>
       </c>
       <c r="E396" s="2">
-        <v>29</v>
+        <v>21</v>
       </c>
       <c r="F396" s="2" t="str">
         <v>A</v>
       </c>
       <c r="G396" s="2" t="str">
-        <v>Pc</v>
+        <v>A</v>
       </c>
       <c r="H396" s="2">
         <v>0</v>
@@ -15467,19 +15461,19 @@
     </row>
     <row r="397">
       <c r="A397" s="2">
-        <v>7158</v>
+        <v>7317</v>
       </c>
       <c r="B397" s="2" t="str">
-        <v>Moro L.</v>
+        <v>Trepy</v>
       </c>
       <c r="C397" s="2" t="str">
         <v/>
       </c>
       <c r="D397" s="2" t="str">
-        <v>Sassuolo</v>
+        <v>Cagliari</v>
       </c>
       <c r="E397" s="2">
-        <v>25</v>
+        <v>20</v>
       </c>
       <c r="F397" s="2" t="str">
         <v>A</v>
@@ -15505,19 +15499,19 @@
     </row>
     <row r="398">
       <c r="A398" s="2">
-        <v>7027</v>
+        <v>7272</v>
       </c>
       <c r="B398" s="2" t="str">
-        <v>Azon</v>
+        <v>Gueye</v>
       </c>
       <c r="C398" s="2" t="str">
         <v/>
       </c>
       <c r="D398" s="2" t="str">
-        <v>Como</v>
+        <v>Udinese</v>
       </c>
       <c r="E398" s="2">
-        <v>24</v>
+        <v>20</v>
       </c>
       <c r="F398" s="2" t="str">
         <v>A</v>
@@ -15538,24 +15532,24 @@
         <v>1</v>
       </c>
       <c r="L398" s="2">
-        <v>1</v>
+        <v>3</v>
       </c>
     </row>
     <row r="399">
       <c r="A399" s="2">
-        <v>6981</v>
+        <v>7249</v>
       </c>
       <c r="B399" s="2" t="str">
-        <v>Vaz</v>
+        <v>Buksa</v>
       </c>
       <c r="C399" s="2" t="str">
         <v/>
       </c>
       <c r="D399" s="2" t="str">
-        <v>Roma</v>
+        <v>Udinese</v>
       </c>
       <c r="E399" s="2">
-        <v>19</v>
+        <v>30</v>
       </c>
       <c r="F399" s="2" t="str">
         <v>A</v>
@@ -15576,24 +15570,24 @@
         <v>1</v>
       </c>
       <c r="L399" s="2">
-        <v>1</v>
+        <v>2</v>
       </c>
     </row>
     <row r="400">
       <c r="A400" s="2">
-        <v>383</v>
+        <v>7161</v>
       </c>
       <c r="B400" s="2" t="str">
-        <v>Petagna</v>
+        <v>Bayo V.</v>
       </c>
       <c r="C400" s="2" t="str">
         <v/>
       </c>
       <c r="D400" s="2" t="str">
-        <v>Monza</v>
+        <v>Udinese</v>
       </c>
       <c r="E400" s="2">
-        <v>31</v>
+        <v>29</v>
       </c>
       <c r="F400" s="2" t="str">
         <v>A</v>
@@ -15614,30 +15608,30 @@
         <v>1</v>
       </c>
       <c r="L400" s="2">
-        <v>2</v>
+        <v>1</v>
       </c>
     </row>
     <row r="401">
       <c r="A401" s="2">
-        <v>7481</v>
+        <v>7158</v>
       </c>
       <c r="B401" s="2" t="str">
-        <v>Dagasso</v>
+        <v>Moro L.</v>
       </c>
       <c r="C401" s="2" t="str">
         <v/>
       </c>
       <c r="D401" s="2" t="str">
-        <v>Venezia</v>
+        <v>Sassuolo</v>
       </c>
       <c r="E401" s="2">
-        <v>22</v>
+        <v>25</v>
       </c>
       <c r="F401" s="2" t="str">
-        <v>C</v>
+        <v>A</v>
       </c>
       <c r="G401" s="2" t="str">
-        <v>C</v>
+        <v>Pc</v>
       </c>
       <c r="H401" s="2">
         <v>0</v>
@@ -15657,25 +15651,25 @@
     </row>
     <row r="402">
       <c r="A402" s="2">
-        <v>7456</v>
+        <v>7027</v>
       </c>
       <c r="B402" s="2" t="str">
-        <v>El Azzouzi A.</v>
+        <v>Azon</v>
       </c>
       <c r="C402" s="2" t="str">
         <v/>
       </c>
       <c r="D402" s="2" t="str">
-        <v>Frosinone</v>
+        <v>Como</v>
       </c>
       <c r="E402" s="2">
-        <v>25</v>
+        <v>24</v>
       </c>
       <c r="F402" s="2" t="str">
-        <v>C</v>
+        <v>A</v>
       </c>
       <c r="G402" s="2" t="str">
-        <v>M/C</v>
+        <v>Pc</v>
       </c>
       <c r="H402" s="2">
         <v>0</v>
@@ -15695,25 +15689,25 @@
     </row>
     <row r="403">
       <c r="A403" s="2">
-        <v>7418</v>
+        <v>6981</v>
       </c>
       <c r="B403" s="2" t="str">
-        <v>Chakvetadze</v>
+        <v>Vaz</v>
       </c>
       <c r="C403" s="2" t="str">
         <v/>
       </c>
       <c r="D403" s="2" t="str">
-        <v>Udinese</v>
+        <v>Roma</v>
       </c>
       <c r="E403" s="2">
-        <v>27</v>
+        <v>19</v>
       </c>
       <c r="F403" s="2" t="str">
-        <v>C</v>
+        <v>A</v>
       </c>
       <c r="G403" s="2" t="str">
-        <v>W/T</v>
+        <v>Pc</v>
       </c>
       <c r="H403" s="2">
         <v>0</v>
@@ -15728,30 +15722,30 @@
         <v>1</v>
       </c>
       <c r="L403" s="2">
-        <v>2</v>
+        <v>1</v>
       </c>
     </row>
     <row r="404">
       <c r="A404" s="2">
-        <v>7392</v>
+        <v>383</v>
       </c>
       <c r="B404" s="2" t="str">
-        <v>Camara A.</v>
+        <v>Petagna</v>
       </c>
       <c r="C404" s="2" t="str">
         <v/>
       </c>
       <c r="D404" s="2" t="str">
-        <v>Udinese</v>
+        <v>Monza</v>
       </c>
       <c r="E404" s="2">
-        <v>18</v>
+        <v>31</v>
       </c>
       <c r="F404" s="2" t="str">
-        <v>C</v>
+        <v>A</v>
       </c>
       <c r="G404" s="2" t="str">
-        <v>M/C</v>
+        <v>Pc</v>
       </c>
       <c r="H404" s="2">
         <v>0</v>
@@ -15766,30 +15760,30 @@
         <v>1</v>
       </c>
       <c r="L404" s="2">
-        <v>1</v>
+        <v>2</v>
       </c>
     </row>
     <row r="405">
       <c r="A405" s="2">
-        <v>7357</v>
+        <v>7481</v>
       </c>
       <c r="B405" s="2" t="str">
-        <v>Lahdo</v>
+        <v>Dagasso</v>
       </c>
       <c r="C405" s="2" t="str">
         <v/>
       </c>
       <c r="D405" s="2" t="str">
-        <v>Como</v>
+        <v>Venezia</v>
       </c>
       <c r="E405" s="2">
-        <v>19</v>
+        <v>22</v>
       </c>
       <c r="F405" s="2" t="str">
         <v>C</v>
       </c>
       <c r="G405" s="2" t="str">
-        <v>C/T</v>
+        <v>C</v>
       </c>
       <c r="H405" s="2">
         <v>0</v>
@@ -15809,25 +15803,25 @@
     </row>
     <row r="406">
       <c r="A406" s="2">
-        <v>7345</v>
+        <v>7456</v>
       </c>
       <c r="B406" s="2" t="str">
-        <v>Przyborek</v>
+        <v>El Azzouzi A.</v>
       </c>
       <c r="C406" s="2" t="str">
         <v/>
       </c>
       <c r="D406" s="2" t="str">
-        <v>Lazio</v>
+        <v>Frosinone</v>
       </c>
       <c r="E406" s="2">
-        <v>19</v>
+        <v>25</v>
       </c>
       <c r="F406" s="2" t="str">
         <v>C</v>
       </c>
       <c r="G406" s="2" t="str">
-        <v>W/T</v>
+        <v>M/C</v>
       </c>
       <c r="H406" s="2">
         <v>0</v>
@@ -15847,25 +15841,25 @@
     </row>
     <row r="407">
       <c r="A407" s="2">
-        <v>7319</v>
+        <v>7418</v>
       </c>
       <c r="B407" s="2" t="str">
-        <v>Fofana Sa.</v>
+        <v>Chakvetadze</v>
       </c>
       <c r="C407" s="2" t="str">
         <v/>
       </c>
       <c r="D407" s="2" t="str">
-        <v>Lecce</v>
+        <v>Udinese</v>
       </c>
       <c r="E407" s="2">
-        <v>23</v>
+        <v>27</v>
       </c>
       <c r="F407" s="2" t="str">
         <v>C</v>
       </c>
       <c r="G407" s="2" t="str">
-        <v>M/C</v>
+        <v>W/T</v>
       </c>
       <c r="H407" s="2">
         <v>0</v>
@@ -15880,30 +15874,30 @@
         <v>1</v>
       </c>
       <c r="L407" s="2">
-        <v>1</v>
+        <v>2</v>
       </c>
     </row>
     <row r="408">
       <c r="A408" s="2">
-        <v>7276</v>
+        <v>7392</v>
       </c>
       <c r="B408" s="2" t="str">
-        <v>Cremaschi</v>
+        <v>Camara A.</v>
       </c>
       <c r="C408" s="2" t="str">
         <v/>
       </c>
       <c r="D408" s="2" t="str">
-        <v>Parma</v>
+        <v>Udinese</v>
       </c>
       <c r="E408" s="2">
-        <v>21</v>
+        <v>18</v>
       </c>
       <c r="F408" s="2" t="str">
         <v>C</v>
       </c>
       <c r="G408" s="2" t="str">
-        <v>E/C</v>
+        <v>M/C</v>
       </c>
       <c r="H408" s="2">
         <v>0</v>
@@ -15923,25 +15917,25 @@
     </row>
     <row r="409">
       <c r="A409" s="2">
-        <v>7248</v>
+        <v>7357</v>
       </c>
       <c r="B409" s="2" t="str">
-        <v>Gorter</v>
+        <v>Lahdo</v>
       </c>
       <c r="C409" s="2" t="str">
         <v/>
       </c>
       <c r="D409" s="2" t="str">
-        <v>Lecce</v>
+        <v>Como</v>
       </c>
       <c r="E409" s="2">
-        <v>21</v>
+        <v>19</v>
       </c>
       <c r="F409" s="2" t="str">
         <v>C</v>
       </c>
       <c r="G409" s="2" t="str">
-        <v>M/C</v>
+        <v>C/T</v>
       </c>
       <c r="H409" s="2">
         <v>0</v>
@@ -15961,25 +15955,25 @@
     </row>
     <row r="410">
       <c r="A410" s="2">
-        <v>7183</v>
+        <v>7345</v>
       </c>
       <c r="B410" s="2" t="str">
-        <v>Aboukhlal</v>
+        <v>Przyborek</v>
       </c>
       <c r="C410" s="2" t="str">
         <v/>
       </c>
       <c r="D410" s="2" t="str">
-        <v>Torino</v>
+        <v>Lazio</v>
       </c>
       <c r="E410" s="2">
-        <v>26</v>
+        <v>19</v>
       </c>
       <c r="F410" s="2" t="str">
         <v>C</v>
       </c>
       <c r="G410" s="2" t="str">
-        <v>W/A</v>
+        <v>W/T</v>
       </c>
       <c r="H410" s="2">
         <v>0</v>
@@ -15994,24 +15988,24 @@
         <v>1</v>
       </c>
       <c r="L410" s="2">
-        <v>2</v>
+        <v>1</v>
       </c>
     </row>
     <row r="411">
       <c r="A411" s="2">
-        <v>7165</v>
+        <v>7319</v>
       </c>
       <c r="B411" s="2" t="str">
-        <v>Liteta</v>
+        <v>Fofana Sa.</v>
       </c>
       <c r="C411" s="2" t="str">
         <v/>
       </c>
       <c r="D411" s="2" t="str">
-        <v>Cagliari</v>
+        <v>Lecce</v>
       </c>
       <c r="E411" s="2">
-        <v>20</v>
+        <v>23</v>
       </c>
       <c r="F411" s="2" t="str">
         <v>C</v>
@@ -16037,25 +16031,25 @@
     </row>
     <row r="412">
       <c r="A412" s="2">
-        <v>7157</v>
+        <v>7276</v>
       </c>
       <c r="B412" s="2" t="str">
-        <v>Iannoni</v>
+        <v>Cremaschi</v>
       </c>
       <c r="C412" s="2" t="str">
         <v/>
       </c>
       <c r="D412" s="2" t="str">
-        <v>Sassuolo</v>
+        <v>Parma</v>
       </c>
       <c r="E412" s="2">
-        <v>25</v>
+        <v>21</v>
       </c>
       <c r="F412" s="2" t="str">
         <v>C</v>
       </c>
       <c r="G412" s="2" t="str">
-        <v>M/C</v>
+        <v>E/C</v>
       </c>
       <c r="H412" s="2">
         <v>0</v>
@@ -16075,19 +16069,19 @@
     </row>
     <row r="413">
       <c r="A413" s="2">
-        <v>7138</v>
+        <v>7248</v>
       </c>
       <c r="B413" s="2" t="str">
-        <v>Ordonez C.</v>
+        <v>Gorter</v>
       </c>
       <c r="C413" s="2" t="str">
         <v/>
       </c>
       <c r="D413" s="2" t="str">
-        <v>Parma</v>
+        <v>Lecce</v>
       </c>
       <c r="E413" s="2">
-        <v>22</v>
+        <v>21</v>
       </c>
       <c r="F413" s="2" t="str">
         <v>C</v>
@@ -16108,30 +16102,30 @@
         <v>1</v>
       </c>
       <c r="L413" s="2">
-        <v>2</v>
+        <v>1</v>
       </c>
     </row>
     <row r="414">
       <c r="A414" s="2">
-        <v>6980</v>
+        <v>7183</v>
       </c>
       <c r="B414" s="2" t="str">
-        <v>Venturino</v>
+        <v>Aboukhlal</v>
       </c>
       <c r="C414" s="2" t="str">
         <v/>
       </c>
       <c r="D414" s="2" t="str">
-        <v>Genoa</v>
+        <v>Torino</v>
       </c>
       <c r="E414" s="2">
-        <v>20</v>
+        <v>26</v>
       </c>
       <c r="F414" s="2" t="str">
         <v>C</v>
       </c>
       <c r="G414" s="2" t="str">
-        <v>W</v>
+        <v>W/A</v>
       </c>
       <c r="H414" s="2">
         <v>0</v>
@@ -16151,19 +16145,19 @@
     </row>
     <row r="415">
       <c r="A415" s="2">
-        <v>6917</v>
+        <v>7165</v>
       </c>
       <c r="B415" s="2" t="str">
-        <v>Masini</v>
+        <v>Liteta</v>
       </c>
       <c r="C415" s="2" t="str">
         <v/>
       </c>
       <c r="D415" s="2" t="str">
-        <v>Frosinone</v>
+        <v>Cagliari</v>
       </c>
       <c r="E415" s="2">
-        <v>25</v>
+        <v>20</v>
       </c>
       <c r="F415" s="2" t="str">
         <v>C</v>
@@ -16184,30 +16178,30 @@
         <v>1</v>
       </c>
       <c r="L415" s="2">
-        <v>2</v>
+        <v>1</v>
       </c>
     </row>
     <row r="416">
       <c r="A416" s="2">
-        <v>6903</v>
+        <v>7157</v>
       </c>
       <c r="B416" s="2" t="str">
-        <v>Hasa</v>
+        <v>Iannoni</v>
       </c>
       <c r="C416" s="2" t="str">
         <v/>
       </c>
       <c r="D416" s="2" t="str">
-        <v>Frosinone</v>
+        <v>Sassuolo</v>
       </c>
       <c r="E416" s="2">
-        <v>22</v>
+        <v>25</v>
       </c>
       <c r="F416" s="2" t="str">
         <v>C</v>
       </c>
       <c r="G416" s="2" t="str">
-        <v>C/T</v>
+        <v>M/C</v>
       </c>
       <c r="H416" s="2">
         <v>0</v>
@@ -16222,30 +16216,30 @@
         <v>1</v>
       </c>
       <c r="L416" s="2">
-        <v>2</v>
+        <v>1</v>
       </c>
     </row>
     <row r="417">
       <c r="A417" s="2">
-        <v>6889</v>
+        <v>7138</v>
       </c>
       <c r="B417" s="2" t="str">
-        <v>Anjorin</v>
+        <v>Ordonez C.</v>
       </c>
       <c r="C417" s="2" t="str">
         <v/>
       </c>
       <c r="D417" s="2" t="str">
-        <v>Torino</v>
+        <v>Parma</v>
       </c>
       <c r="E417" s="2">
-        <v>25</v>
+        <v>22</v>
       </c>
       <c r="F417" s="2" t="str">
         <v>C</v>
       </c>
       <c r="G417" s="2" t="str">
-        <v>C/T</v>
+        <v>M/C</v>
       </c>
       <c r="H417" s="2">
         <v>0</v>
@@ -16260,24 +16254,24 @@
         <v>1</v>
       </c>
       <c r="L417" s="2">
-        <v>1</v>
+        <v>2</v>
       </c>
     </row>
     <row r="418">
       <c r="A418" s="2">
-        <v>6815</v>
+        <v>6980</v>
       </c>
       <c r="B418" s="2" t="str">
-        <v>Fadera</v>
+        <v>Venturino</v>
       </c>
       <c r="C418" s="2" t="str">
         <v/>
       </c>
       <c r="D418" s="2" t="str">
-        <v>Como</v>
+        <v>Genoa</v>
       </c>
       <c r="E418" s="2">
-        <v>25</v>
+        <v>20</v>
       </c>
       <c r="F418" s="2" t="str">
         <v>C</v>
@@ -16303,16 +16297,16 @@
     </row>
     <row r="419">
       <c r="A419" s="2">
-        <v>6410</v>
+        <v>6917</v>
       </c>
       <c r="B419" s="2" t="str">
-        <v>Kaba</v>
+        <v>Masini</v>
       </c>
       <c r="C419" s="2" t="str">
         <v/>
       </c>
       <c r="D419" s="2" t="str">
-        <v>Lecce</v>
+        <v>Frosinone</v>
       </c>
       <c r="E419" s="2">
         <v>25</v>
@@ -16336,30 +16330,30 @@
         <v>1</v>
       </c>
       <c r="L419" s="2">
-        <v>1</v>
+        <v>2</v>
       </c>
     </row>
     <row r="420">
       <c r="A420" s="2">
-        <v>6246</v>
+        <v>6903</v>
       </c>
       <c r="B420" s="2" t="str">
-        <v>Lipani</v>
+        <v>Hasa</v>
       </c>
       <c r="C420" s="2" t="str">
         <v/>
       </c>
       <c r="D420" s="2" t="str">
-        <v>Sassuolo</v>
+        <v>Frosinone</v>
       </c>
       <c r="E420" s="2">
-        <v>21</v>
+        <v>22</v>
       </c>
       <c r="F420" s="2" t="str">
         <v>C</v>
       </c>
       <c r="G420" s="2" t="str">
-        <v>M/C</v>
+        <v>C/T</v>
       </c>
       <c r="H420" s="2">
         <v>0</v>
@@ -16379,16 +16373,16 @@
     </row>
     <row r="421">
       <c r="A421" s="2">
-        <v>6225</v>
+        <v>6889</v>
       </c>
       <c r="B421" s="2" t="str">
-        <v>El Azzouzi O.</v>
+        <v>Anjorin</v>
       </c>
       <c r="C421" s="2" t="str">
         <v/>
       </c>
       <c r="D421" s="2" t="str">
-        <v>Bologna</v>
+        <v>Torino</v>
       </c>
       <c r="E421" s="2">
         <v>25</v>
@@ -16397,7 +16391,7 @@
         <v>C</v>
       </c>
       <c r="G421" s="2" t="str">
-        <v>M/C</v>
+        <v>C/T</v>
       </c>
       <c r="H421" s="2">
         <v>0</v>
@@ -16412,30 +16406,30 @@
         <v>1</v>
       </c>
       <c r="L421" s="2">
-        <v>2</v>
+        <v>1</v>
       </c>
     </row>
     <row r="422">
       <c r="A422" s="2">
-        <v>6219</v>
+        <v>6815</v>
       </c>
       <c r="B422" s="2" t="str">
-        <v>Boloca</v>
+        <v>Fadera</v>
       </c>
       <c r="C422" s="2" t="str">
         <v/>
       </c>
       <c r="D422" s="2" t="str">
-        <v>Sassuolo</v>
+        <v>Como</v>
       </c>
       <c r="E422" s="2">
-        <v>28</v>
+        <v>25</v>
       </c>
       <c r="F422" s="2" t="str">
         <v>C</v>
       </c>
       <c r="G422" s="2" t="str">
-        <v>M/C</v>
+        <v>W</v>
       </c>
       <c r="H422" s="2">
         <v>0</v>
@@ -16455,25 +16449,25 @@
     </row>
     <row r="423">
       <c r="A423" s="2">
-        <v>6212</v>
+        <v>6592</v>
       </c>
       <c r="B423" s="2" t="str">
-        <v>Zarraga</v>
+        <v>Forson O.</v>
       </c>
       <c r="C423" s="2" t="str">
         <v/>
       </c>
       <c r="D423" s="2" t="str">
-        <v>Udinese</v>
+        <v>Monza</v>
       </c>
       <c r="E423" s="2">
-        <v>27</v>
+        <v>22</v>
       </c>
       <c r="F423" s="2" t="str">
         <v>C</v>
       </c>
       <c r="G423" s="2" t="str">
-        <v>M/C</v>
+        <v>W/T</v>
       </c>
       <c r="H423" s="2">
         <v>0</v>
@@ -16493,19 +16487,19 @@
     </row>
     <row r="424">
       <c r="A424" s="2">
-        <v>6191</v>
+        <v>6410</v>
       </c>
       <c r="B424" s="2" t="str">
-        <v>Belahyane</v>
+        <v>Kaba</v>
       </c>
       <c r="C424" s="2" t="str">
         <v/>
       </c>
       <c r="D424" s="2" t="str">
-        <v>Lazio</v>
+        <v>Lecce</v>
       </c>
       <c r="E424" s="2">
-        <v>22</v>
+        <v>25</v>
       </c>
       <c r="F424" s="2" t="str">
         <v>C</v>
@@ -16531,25 +16525,25 @@
     </row>
     <row r="425">
       <c r="A425" s="2">
-        <v>5880</v>
+        <v>6246</v>
       </c>
       <c r="B425" s="2" t="str">
-        <v>Ciurria</v>
+        <v>Lipani</v>
       </c>
       <c r="C425" s="2" t="str">
         <v/>
       </c>
       <c r="D425" s="2" t="str">
-        <v>Monza</v>
+        <v>Sassuolo</v>
       </c>
       <c r="E425" s="2">
-        <v>31</v>
+        <v>21</v>
       </c>
       <c r="F425" s="2" t="str">
         <v>C</v>
       </c>
       <c r="G425" s="2" t="str">
-        <v>E/W</v>
+        <v>M/C</v>
       </c>
       <c r="H425" s="2">
         <v>0</v>
@@ -16569,25 +16563,25 @@
     </row>
     <row r="426">
       <c r="A426" s="2">
-        <v>5725</v>
+        <v>6225</v>
       </c>
       <c r="B426" s="2" t="str">
-        <v>Kone B.</v>
+        <v>El Azzouzi O.</v>
       </c>
       <c r="C426" s="2" t="str">
         <v/>
       </c>
       <c r="D426" s="2" t="str">
-        <v>Frosinone</v>
+        <v>Bologna</v>
       </c>
       <c r="E426" s="2">
-        <v>26</v>
+        <v>25</v>
       </c>
       <c r="F426" s="2" t="str">
         <v>C</v>
       </c>
       <c r="G426" s="2" t="str">
-        <v>C</v>
+        <v>M/C</v>
       </c>
       <c r="H426" s="2">
         <v>0</v>
@@ -16602,30 +16596,30 @@
         <v>1</v>
       </c>
       <c r="L426" s="2">
-        <v>1</v>
+        <v>2</v>
       </c>
     </row>
     <row r="427">
       <c r="A427" s="2">
-        <v>5485</v>
+        <v>6219</v>
       </c>
       <c r="B427" s="2" t="str">
-        <v>Bjarkason</v>
+        <v>Boloca</v>
       </c>
       <c r="C427" s="2" t="str">
-        <v>*</v>
+        <v/>
       </c>
       <c r="D427" s="2" t="str">
-        <v>Venezia</v>
+        <v>Sassuolo</v>
       </c>
       <c r="E427" s="2">
-        <v>26</v>
+        <v>28</v>
       </c>
       <c r="F427" s="2" t="str">
         <v>C</v>
       </c>
       <c r="G427" s="2" t="str">
-        <v>E/W</v>
+        <v>M/C</v>
       </c>
       <c r="H427" s="2">
         <v>0</v>
@@ -16640,24 +16634,24 @@
         <v>1</v>
       </c>
       <c r="L427" s="2">
-        <v>1</v>
+        <v>2</v>
       </c>
     </row>
     <row r="428">
       <c r="A428" s="2">
-        <v>5457</v>
+        <v>6212</v>
       </c>
       <c r="B428" s="2" t="str">
-        <v>Maleh</v>
+        <v>Zarraga</v>
       </c>
       <c r="C428" s="2" t="str">
         <v/>
       </c>
       <c r="D428" s="2" t="str">
-        <v>Lecce</v>
+        <v>Udinese</v>
       </c>
       <c r="E428" s="2">
-        <v>28</v>
+        <v>27</v>
       </c>
       <c r="F428" s="2" t="str">
         <v>C</v>
@@ -16678,30 +16672,30 @@
         <v>1</v>
       </c>
       <c r="L428" s="2">
-        <v>2</v>
+        <v>1</v>
       </c>
     </row>
     <row r="429">
       <c r="A429" s="2">
-        <v>5295</v>
+        <v>6191</v>
       </c>
       <c r="B429" s="2" t="str">
-        <v>Musah</v>
+        <v>Belahyane</v>
       </c>
       <c r="C429" s="2" t="str">
         <v/>
       </c>
       <c r="D429" s="2" t="str">
-        <v>Milan</v>
+        <v>Lazio</v>
       </c>
       <c r="E429" s="2">
-        <v>24</v>
+        <v>22</v>
       </c>
       <c r="F429" s="2" t="str">
         <v>C</v>
       </c>
       <c r="G429" s="2" t="str">
-        <v>C/W</v>
+        <v>M/C</v>
       </c>
       <c r="H429" s="2">
         <v>0</v>
@@ -16716,30 +16710,30 @@
         <v>1</v>
       </c>
       <c r="L429" s="2">
-        <v>2</v>
+        <v>1</v>
       </c>
     </row>
     <row r="430">
       <c r="A430" s="2">
-        <v>5007</v>
+        <v>5880</v>
       </c>
       <c r="B430" s="2" t="str">
-        <v>Ilic</v>
+        <v>Ciurria</v>
       </c>
       <c r="C430" s="2" t="str">
         <v/>
       </c>
       <c r="D430" s="2" t="str">
-        <v>Torino</v>
+        <v>Monza</v>
       </c>
       <c r="E430" s="2">
-        <v>25</v>
+        <v>31</v>
       </c>
       <c r="F430" s="2" t="str">
         <v>C</v>
       </c>
       <c r="G430" s="2" t="str">
-        <v>C</v>
+        <v>E/W</v>
       </c>
       <c r="H430" s="2">
         <v>0</v>
@@ -16754,24 +16748,24 @@
         <v>1</v>
       </c>
       <c r="L430" s="2">
-        <v>1</v>
+        <v>2</v>
       </c>
     </row>
     <row r="431">
       <c r="A431" s="2">
-        <v>526</v>
+        <v>5725</v>
       </c>
       <c r="B431" s="2" t="str">
-        <v>Duncan</v>
+        <v>Kone B.</v>
       </c>
       <c r="C431" s="2" t="str">
         <v/>
       </c>
       <c r="D431" s="2" t="str">
-        <v>Venezia</v>
+        <v>Frosinone</v>
       </c>
       <c r="E431" s="2">
-        <v>33</v>
+        <v>26</v>
       </c>
       <c r="F431" s="2" t="str">
         <v>C</v>
@@ -16792,30 +16786,30 @@
         <v>1</v>
       </c>
       <c r="L431" s="2">
-        <v>2</v>
+        <v>1</v>
       </c>
     </row>
     <row r="432">
       <c r="A432" s="2">
-        <v>7548</v>
+        <v>5485</v>
       </c>
       <c r="B432" s="2" t="str">
-        <v>Aurelio</v>
+        <v>Bjarkason</v>
       </c>
       <c r="C432" s="2" t="str">
-        <v/>
+        <v>*</v>
       </c>
       <c r="D432" s="2" t="str">
-        <v>Cagliari</v>
+        <v>Venezia</v>
       </c>
       <c r="E432" s="2">
         <v>26</v>
       </c>
       <c r="F432" s="2" t="str">
-        <v>D</v>
+        <v>C</v>
       </c>
       <c r="G432" s="2" t="str">
-        <v>Ds/E</v>
+        <v>E/W</v>
       </c>
       <c r="H432" s="2">
         <v>0</v>
@@ -16830,30 +16824,30 @@
         <v>1</v>
       </c>
       <c r="L432" s="2">
-        <v>2</v>
+        <v>1</v>
       </c>
     </row>
     <row r="433">
       <c r="A433" s="2">
-        <v>7525</v>
+        <v>5457</v>
       </c>
       <c r="B433" s="2" t="str">
-        <v>Diawara S.</v>
+        <v>Maleh</v>
       </c>
       <c r="C433" s="2" t="str">
         <v/>
       </c>
       <c r="D433" s="2" t="str">
-        <v>Milan</v>
+        <v>Lecce</v>
       </c>
       <c r="E433" s="2">
-        <v>20</v>
+        <v>28</v>
       </c>
       <c r="F433" s="2" t="str">
-        <v>D</v>
+        <v>C</v>
       </c>
       <c r="G433" s="2" t="str">
-        <v>Ds/Dc</v>
+        <v>M/C</v>
       </c>
       <c r="H433" s="2">
         <v>0</v>
@@ -16873,25 +16867,25 @@
     </row>
     <row r="434">
       <c r="A434" s="2">
-        <v>7483</v>
+        <v>5295</v>
       </c>
       <c r="B434" s="2" t="str">
-        <v>Alhassane</v>
+        <v>Musah</v>
       </c>
       <c r="C434" s="2" t="str">
         <v/>
       </c>
       <c r="D434" s="2" t="str">
-        <v>Bologna</v>
+        <v>Milan</v>
       </c>
       <c r="E434" s="2">
         <v>24</v>
       </c>
       <c r="F434" s="2" t="str">
-        <v>D</v>
+        <v>C</v>
       </c>
       <c r="G434" s="2" t="str">
-        <v>Ds/E</v>
+        <v>C/W</v>
       </c>
       <c r="H434" s="2">
         <v>0</v>
@@ -16911,25 +16905,25 @@
     </row>
     <row r="435">
       <c r="A435" s="2">
-        <v>7478</v>
+        <v>5007</v>
       </c>
       <c r="B435" s="2" t="str">
-        <v>Franjic</v>
+        <v>Ilic</v>
       </c>
       <c r="C435" s="2" t="str">
         <v/>
       </c>
       <c r="D435" s="2" t="str">
-        <v>Venezia</v>
+        <v>Torino</v>
       </c>
       <c r="E435" s="2">
-        <v>26</v>
+        <v>25</v>
       </c>
       <c r="F435" s="2" t="str">
-        <v>D</v>
+        <v>C</v>
       </c>
       <c r="G435" s="2" t="str">
-        <v>B/Ds/E</v>
+        <v>C</v>
       </c>
       <c r="H435" s="2">
         <v>0</v>
@@ -16944,30 +16938,30 @@
         <v>1</v>
       </c>
       <c r="L435" s="2">
-        <v>2</v>
+        <v>1</v>
       </c>
     </row>
     <row r="436">
       <c r="A436" s="2">
-        <v>7476</v>
+        <v>526</v>
       </c>
       <c r="B436" s="2" t="str">
-        <v>Bakoune</v>
+        <v>Duncan</v>
       </c>
       <c r="C436" s="2" t="str">
         <v/>
       </c>
       <c r="D436" s="2" t="str">
-        <v>Monza</v>
+        <v>Venezia</v>
       </c>
       <c r="E436" s="2">
-        <v>20</v>
+        <v>33</v>
       </c>
       <c r="F436" s="2" t="str">
-        <v>D</v>
+        <v>C</v>
       </c>
       <c r="G436" s="2" t="str">
-        <v>Dd/E</v>
+        <v>C</v>
       </c>
       <c r="H436" s="2">
         <v>0</v>
@@ -16982,21 +16976,21 @@
         <v>1</v>
       </c>
       <c r="L436" s="2">
-        <v>1</v>
+        <v>2</v>
       </c>
     </row>
     <row r="437">
       <c r="A437" s="2">
-        <v>7471</v>
+        <v>7548</v>
       </c>
       <c r="B437" s="2" t="str">
-        <v>Corrado</v>
+        <v>Aurelio</v>
       </c>
       <c r="C437" s="2" t="str">
         <v/>
       </c>
       <c r="D437" s="2" t="str">
-        <v>Frosinone</v>
+        <v>Cagliari</v>
       </c>
       <c r="E437" s="2">
         <v>26</v>
@@ -17020,30 +17014,30 @@
         <v>1</v>
       </c>
       <c r="L437" s="2">
-        <v>1</v>
+        <v>2</v>
       </c>
     </row>
     <row r="438">
       <c r="A438" s="2">
-        <v>7470</v>
+        <v>7525</v>
       </c>
       <c r="B438" s="2" t="str">
-        <v>Oyono J.</v>
+        <v>Diawara S.</v>
       </c>
       <c r="C438" s="2" t="str">
         <v/>
       </c>
       <c r="D438" s="2" t="str">
-        <v>Frosinone</v>
+        <v>Milan</v>
       </c>
       <c r="E438" s="2">
-        <v>25</v>
+        <v>20</v>
       </c>
       <c r="F438" s="2" t="str">
         <v>D</v>
       </c>
       <c r="G438" s="2" t="str">
-        <v>Dd/E</v>
+        <v>Ds/Dc</v>
       </c>
       <c r="H438" s="2">
         <v>0</v>
@@ -17058,30 +17052,30 @@
         <v>1</v>
       </c>
       <c r="L438" s="2">
-        <v>1</v>
+        <v>2</v>
       </c>
     </row>
     <row r="439">
       <c r="A439" s="2">
-        <v>7468</v>
+        <v>7483</v>
       </c>
       <c r="B439" s="2" t="str">
-        <v>Gelli J.</v>
+        <v>Alhassane</v>
       </c>
       <c r="C439" s="2" t="str">
         <v/>
       </c>
       <c r="D439" s="2" t="str">
-        <v>Frosinone</v>
+        <v>Bologna</v>
       </c>
       <c r="E439" s="2">
-        <v>25</v>
+        <v>24</v>
       </c>
       <c r="F439" s="2" t="str">
         <v>D</v>
       </c>
       <c r="G439" s="2" t="str">
-        <v>Dc</v>
+        <v>Ds/E</v>
       </c>
       <c r="H439" s="2">
         <v>0</v>
@@ -17096,15 +17090,15 @@
         <v>1</v>
       </c>
       <c r="L439" s="2">
-        <v>1</v>
+        <v>2</v>
       </c>
     </row>
     <row r="440">
       <c r="A440" s="2">
-        <v>7454</v>
+        <v>7478</v>
       </c>
       <c r="B440" s="2" t="str">
-        <v>Gomes</v>
+        <v>Franjic</v>
       </c>
       <c r="C440" s="2" t="str">
         <v/>
@@ -17113,13 +17107,13 @@
         <v>Venezia</v>
       </c>
       <c r="E440" s="2">
-        <v>18</v>
+        <v>26</v>
       </c>
       <c r="F440" s="2" t="str">
         <v>D</v>
       </c>
       <c r="G440" s="2" t="str">
-        <v>Ds/Dc</v>
+        <v>B/Ds/E</v>
       </c>
       <c r="H440" s="2">
         <v>0</v>
@@ -17134,30 +17128,30 @@
         <v>1</v>
       </c>
       <c r="L440" s="2">
-        <v>1</v>
+        <v>2</v>
       </c>
     </row>
     <row r="441">
       <c r="A441" s="2">
-        <v>7356</v>
+        <v>7476</v>
       </c>
       <c r="B441" s="2" t="str">
-        <v>Mlacic</v>
+        <v>Bakoune</v>
       </c>
       <c r="C441" s="2" t="str">
         <v/>
       </c>
       <c r="D441" s="2" t="str">
-        <v>Udinese</v>
+        <v>Monza</v>
       </c>
       <c r="E441" s="2">
-        <v>19</v>
+        <v>20</v>
       </c>
       <c r="F441" s="2" t="str">
         <v>D</v>
       </c>
       <c r="G441" s="2" t="str">
-        <v>Dc</v>
+        <v>Dd/E</v>
       </c>
       <c r="H441" s="2">
         <v>0</v>
@@ -17177,25 +17171,25 @@
     </row>
     <row r="442">
       <c r="A442" s="2">
-        <v>7346</v>
+        <v>7471</v>
       </c>
       <c r="B442" s="2" t="str">
-        <v>Raterink</v>
+        <v>Corrado</v>
       </c>
       <c r="C442" s="2" t="str">
-        <v>*</v>
+        <v/>
       </c>
       <c r="D442" s="2" t="str">
-        <v>Cagliari</v>
+        <v>Frosinone</v>
       </c>
       <c r="E442" s="2">
-        <v>20</v>
+        <v>26</v>
       </c>
       <c r="F442" s="2" t="str">
         <v>D</v>
       </c>
       <c r="G442" s="2" t="str">
-        <v>Dd/E</v>
+        <v>Ds/E</v>
       </c>
       <c r="H442" s="2">
         <v>0</v>
@@ -17215,25 +17209,25 @@
     </row>
     <row r="443">
       <c r="A443" s="2">
-        <v>7326</v>
+        <v>7470</v>
       </c>
       <c r="B443" s="2" t="str">
-        <v>Helland</v>
+        <v>Oyono J.</v>
       </c>
       <c r="C443" s="2" t="str">
         <v/>
       </c>
       <c r="D443" s="2" t="str">
-        <v>Bologna</v>
+        <v>Frosinone</v>
       </c>
       <c r="E443" s="2">
-        <v>21</v>
+        <v>25</v>
       </c>
       <c r="F443" s="2" t="str">
         <v>D</v>
       </c>
       <c r="G443" s="2" t="str">
-        <v>Dd/Dc</v>
+        <v>Dd/E</v>
       </c>
       <c r="H443" s="2">
         <v>0</v>
@@ -17248,24 +17242,24 @@
         <v>1</v>
       </c>
       <c r="L443" s="2">
-        <v>2</v>
+        <v>1</v>
       </c>
     </row>
     <row r="444">
       <c r="A444" s="2">
-        <v>7260</v>
+        <v>7468</v>
       </c>
       <c r="B444" s="2" t="str">
-        <v>Ziolkowski</v>
+        <v>Gelli J.</v>
       </c>
       <c r="C444" s="2" t="str">
         <v/>
       </c>
       <c r="D444" s="2" t="str">
-        <v>Roma</v>
+        <v>Frosinone</v>
       </c>
       <c r="E444" s="2">
-        <v>21</v>
+        <v>25</v>
       </c>
       <c r="F444" s="2" t="str">
         <v>D</v>
@@ -17291,25 +17285,25 @@
     </row>
     <row r="445">
       <c r="A445" s="2">
-        <v>7202</v>
+        <v>7454</v>
       </c>
       <c r="B445" s="2" t="str">
-        <v>Ndiaye</v>
+        <v>Gomes</v>
       </c>
       <c r="C445" s="2" t="str">
         <v/>
       </c>
       <c r="D445" s="2" t="str">
-        <v>Parma</v>
+        <v>Venezia</v>
       </c>
       <c r="E445" s="2">
-        <v>24</v>
+        <v>18</v>
       </c>
       <c r="F445" s="2" t="str">
         <v>D</v>
       </c>
       <c r="G445" s="2" t="str">
-        <v>Dc</v>
+        <v>Ds/Dc</v>
       </c>
       <c r="H445" s="2">
         <v>0</v>
@@ -17329,25 +17323,25 @@
     </row>
     <row r="446">
       <c r="A446" s="2">
-        <v>7182</v>
+        <v>7356</v>
       </c>
       <c r="B446" s="2" t="str">
-        <v>Ndaba</v>
+        <v>Mlacic</v>
       </c>
       <c r="C446" s="2" t="str">
         <v/>
       </c>
       <c r="D446" s="2" t="str">
-        <v>Lecce</v>
+        <v>Udinese</v>
       </c>
       <c r="E446" s="2">
-        <v>27</v>
+        <v>19</v>
       </c>
       <c r="F446" s="2" t="str">
         <v>D</v>
       </c>
       <c r="G446" s="2" t="str">
-        <v>Ds/E</v>
+        <v>Dc</v>
       </c>
       <c r="H446" s="2">
         <v>0</v>
@@ -17367,25 +17361,25 @@
     </row>
     <row r="447">
       <c r="A447" s="2">
-        <v>7164</v>
+        <v>7346</v>
       </c>
       <c r="B447" s="2" t="str">
-        <v>Perez M.</v>
+        <v>Raterink</v>
       </c>
       <c r="C447" s="2" t="str">
         <v>*</v>
       </c>
       <c r="D447" s="2" t="str">
-        <v>Lecce</v>
+        <v>Cagliari</v>
       </c>
       <c r="E447" s="2">
-        <v>21</v>
+        <v>20</v>
       </c>
       <c r="F447" s="2" t="str">
         <v>D</v>
       </c>
       <c r="G447" s="2" t="str">
-        <v>Dd/Dc</v>
+        <v>Dd/E</v>
       </c>
       <c r="H447" s="2">
         <v>0</v>
@@ -17405,25 +17399,25 @@
     </row>
     <row r="448">
       <c r="A448" s="2">
-        <v>7156</v>
+        <v>7326</v>
       </c>
       <c r="B448" s="2" t="str">
-        <v>Pieragnolo</v>
+        <v>Helland</v>
       </c>
       <c r="C448" s="2" t="str">
         <v/>
       </c>
       <c r="D448" s="2" t="str">
-        <v>Sassuolo</v>
+        <v>Bologna</v>
       </c>
       <c r="E448" s="2">
-        <v>23</v>
+        <v>21</v>
       </c>
       <c r="F448" s="2" t="str">
         <v>D</v>
       </c>
       <c r="G448" s="2" t="str">
-        <v>Ds/E</v>
+        <v>Dd/Dc</v>
       </c>
       <c r="H448" s="2">
         <v>0</v>
@@ -17438,24 +17432,24 @@
         <v>1</v>
       </c>
       <c r="L448" s="2">
-        <v>1</v>
+        <v>2</v>
       </c>
     </row>
     <row r="449">
       <c r="A449" s="2">
-        <v>6977</v>
+        <v>7260</v>
       </c>
       <c r="B449" s="2" t="str">
-        <v>Otoa</v>
+        <v>Ziolkowski</v>
       </c>
       <c r="C449" s="2" t="str">
         <v/>
       </c>
       <c r="D449" s="2" t="str">
-        <v>Genoa</v>
+        <v>Roma</v>
       </c>
       <c r="E449" s="2">
-        <v>22</v>
+        <v>21</v>
       </c>
       <c r="F449" s="2" t="str">
         <v>D</v>
@@ -17476,24 +17470,24 @@
         <v>1</v>
       </c>
       <c r="L449" s="2">
-        <v>2</v>
+        <v>1</v>
       </c>
     </row>
     <row r="450">
       <c r="A450" s="2">
-        <v>6925</v>
+        <v>7202</v>
       </c>
       <c r="B450" s="2" t="str">
-        <v>Palma</v>
+        <v>Ndiaye</v>
       </c>
       <c r="C450" s="2" t="str">
         <v/>
       </c>
       <c r="D450" s="2" t="str">
-        <v>Udinese</v>
+        <v>Parma</v>
       </c>
       <c r="E450" s="2">
-        <v>18</v>
+        <v>24</v>
       </c>
       <c r="F450" s="2" t="str">
         <v>D</v>
@@ -17514,30 +17508,30 @@
         <v>1</v>
       </c>
       <c r="L450" s="2">
-        <v>2</v>
+        <v>1</v>
       </c>
     </row>
     <row r="451">
       <c r="A451" s="2">
-        <v>6896</v>
+        <v>7182</v>
       </c>
       <c r="B451" s="2" t="str">
-        <v>Van Der Brempt</v>
+        <v>Ndaba</v>
       </c>
       <c r="C451" s="2" t="str">
         <v/>
       </c>
       <c r="D451" s="2" t="str">
-        <v>Como</v>
+        <v>Lecce</v>
       </c>
       <c r="E451" s="2">
-        <v>24</v>
+        <v>27</v>
       </c>
       <c r="F451" s="2" t="str">
         <v>D</v>
       </c>
       <c r="G451" s="2" t="str">
-        <v>Dd/E</v>
+        <v>Ds/E</v>
       </c>
       <c r="H451" s="2">
         <v>0</v>
@@ -17552,30 +17546,30 @@
         <v>1</v>
       </c>
       <c r="L451" s="2">
-        <v>2</v>
+        <v>1</v>
       </c>
     </row>
     <row r="452">
       <c r="A452" s="2">
-        <v>6883</v>
+        <v>7164</v>
       </c>
       <c r="B452" s="2" t="str">
-        <v>Jean</v>
+        <v>Perez M.</v>
       </c>
       <c r="C452" s="2" t="str">
-        <v/>
+        <v>*</v>
       </c>
       <c r="D452" s="2" t="str">
         <v>Lecce</v>
       </c>
       <c r="E452" s="2">
-        <v>26</v>
+        <v>21</v>
       </c>
       <c r="F452" s="2" t="str">
         <v>D</v>
       </c>
       <c r="G452" s="2" t="str">
-        <v>Dc</v>
+        <v>Dd/Dc</v>
       </c>
       <c r="H452" s="2">
         <v>0</v>
@@ -17590,30 +17584,30 @@
         <v>1</v>
       </c>
       <c r="L452" s="2">
-        <v>2</v>
+        <v>1</v>
       </c>
     </row>
     <row r="453">
       <c r="A453" s="2">
-        <v>6809</v>
+        <v>7156</v>
       </c>
       <c r="B453" s="2" t="str">
-        <v>Marianucci</v>
+        <v>Pieragnolo</v>
       </c>
       <c r="C453" s="2" t="str">
         <v/>
       </c>
       <c r="D453" s="2" t="str">
-        <v>Napoli</v>
+        <v>Sassuolo</v>
       </c>
       <c r="E453" s="2">
-        <v>22</v>
+        <v>23</v>
       </c>
       <c r="F453" s="2" t="str">
         <v>D</v>
       </c>
       <c r="G453" s="2" t="str">
-        <v>Dc</v>
+        <v>Ds/E</v>
       </c>
       <c r="H453" s="2">
         <v>0</v>
@@ -17633,16 +17627,16 @@
     </row>
     <row r="454">
       <c r="A454" s="2">
-        <v>6681</v>
+        <v>6977</v>
       </c>
       <c r="B454" s="2" t="str">
-        <v>Sagrado</v>
+        <v>Otoa</v>
       </c>
       <c r="C454" s="2" t="str">
         <v/>
       </c>
       <c r="D454" s="2" t="str">
-        <v>Venezia</v>
+        <v>Genoa</v>
       </c>
       <c r="E454" s="2">
         <v>22</v>
@@ -17651,7 +17645,7 @@
         <v>D</v>
       </c>
       <c r="G454" s="2" t="str">
-        <v>Dd/E</v>
+        <v>Dc</v>
       </c>
       <c r="H454" s="2">
         <v>0</v>
@@ -17671,19 +17665,19 @@
     </row>
     <row r="455">
       <c r="A455" s="2">
-        <v>6638</v>
+        <v>6925</v>
       </c>
       <c r="B455" s="2" t="str">
-        <v>Marin R.</v>
+        <v>Palma</v>
       </c>
       <c r="C455" s="2" t="str">
         <v/>
       </c>
       <c r="D455" s="2" t="str">
-        <v>Napoli</v>
+        <v>Udinese</v>
       </c>
       <c r="E455" s="2">
-        <v>24</v>
+        <v>18</v>
       </c>
       <c r="F455" s="2" t="str">
         <v>D</v>
@@ -17709,25 +17703,25 @@
     </row>
     <row r="456">
       <c r="A456" s="2">
-        <v>6245</v>
+        <v>6896</v>
       </c>
       <c r="B456" s="2" t="str">
-        <v>Vogliacco</v>
+        <v>Van Der Brempt</v>
       </c>
       <c r="C456" s="2" t="str">
-        <v>*</v>
+        <v/>
       </c>
       <c r="D456" s="2" t="str">
-        <v>Genoa</v>
+        <v>Como</v>
       </c>
       <c r="E456" s="2">
-        <v>28</v>
+        <v>24</v>
       </c>
       <c r="F456" s="2" t="str">
         <v>D</v>
       </c>
       <c r="G456" s="2" t="str">
-        <v>Dd/Dc</v>
+        <v>Dd/E</v>
       </c>
       <c r="H456" s="2">
         <v>0</v>
@@ -17742,30 +17736,30 @@
         <v>1</v>
       </c>
       <c r="L456" s="2">
-        <v>1</v>
+        <v>2</v>
       </c>
     </row>
     <row r="457">
       <c r="A457" s="2">
-        <v>6244</v>
+        <v>6883</v>
       </c>
       <c r="B457" s="2" t="str">
-        <v>Matturro</v>
+        <v>Jean</v>
       </c>
       <c r="C457" s="2" t="str">
         <v/>
       </c>
       <c r="D457" s="2" t="str">
-        <v>Genoa</v>
+        <v>Lecce</v>
       </c>
       <c r="E457" s="2">
-        <v>22</v>
+        <v>26</v>
       </c>
       <c r="F457" s="2" t="str">
         <v>D</v>
       </c>
       <c r="G457" s="2" t="str">
-        <v>Ds/Dc</v>
+        <v>Dc</v>
       </c>
       <c r="H457" s="2">
         <v>0</v>
@@ -17780,21 +17774,21 @@
         <v>1</v>
       </c>
       <c r="L457" s="2">
-        <v>1</v>
+        <v>2</v>
       </c>
     </row>
     <row r="458">
       <c r="A458" s="2">
-        <v>6189</v>
+        <v>6809</v>
       </c>
       <c r="B458" s="2" t="str">
-        <v>Missori</v>
+        <v>Marianucci</v>
       </c>
       <c r="C458" s="2" t="str">
         <v/>
       </c>
       <c r="D458" s="2" t="str">
-        <v>Sassuolo</v>
+        <v>Napoli</v>
       </c>
       <c r="E458" s="2">
         <v>22</v>
@@ -17803,7 +17797,7 @@
         <v>D</v>
       </c>
       <c r="G458" s="2" t="str">
-        <v>Dd/E</v>
+        <v>Dc</v>
       </c>
       <c r="H458" s="2">
         <v>0</v>
@@ -17823,25 +17817,25 @@
     </row>
     <row r="459">
       <c r="A459" s="2">
-        <v>6149</v>
+        <v>6681</v>
       </c>
       <c r="B459" s="2" t="str">
-        <v>Carboni F.</v>
+        <v>Sagrado</v>
       </c>
       <c r="C459" s="2" t="str">
         <v/>
       </c>
       <c r="D459" s="2" t="str">
-        <v>Parma</v>
+        <v>Venezia</v>
       </c>
       <c r="E459" s="2">
-        <v>23</v>
+        <v>22</v>
       </c>
       <c r="F459" s="2" t="str">
         <v>D</v>
       </c>
       <c r="G459" s="2" t="str">
-        <v>Ds/E</v>
+        <v>Dd/E</v>
       </c>
       <c r="H459" s="2">
         <v>0</v>
@@ -17856,30 +17850,30 @@
         <v>1</v>
       </c>
       <c r="L459" s="2">
-        <v>1</v>
+        <v>2</v>
       </c>
     </row>
     <row r="460">
       <c r="A460" s="2">
-        <v>6039</v>
+        <v>6638</v>
       </c>
       <c r="B460" s="2" t="str">
-        <v>Cabal</v>
+        <v>Marin R.</v>
       </c>
       <c r="C460" s="2" t="str">
         <v/>
       </c>
       <c r="D460" s="2" t="str">
-        <v>Juventus</v>
+        <v>Napoli</v>
       </c>
       <c r="E460" s="2">
-        <v>25</v>
+        <v>24</v>
       </c>
       <c r="F460" s="2" t="str">
         <v>D</v>
       </c>
       <c r="G460" s="2" t="str">
-        <v>B/Ds/E</v>
+        <v>Dc</v>
       </c>
       <c r="H460" s="2">
         <v>0</v>
@@ -17894,24 +17888,24 @@
         <v>1</v>
       </c>
       <c r="L460" s="2">
-        <v>1</v>
+        <v>2</v>
       </c>
     </row>
     <row r="461">
       <c r="A461" s="2">
-        <v>6021</v>
+        <v>6245</v>
       </c>
       <c r="B461" s="2" t="str">
-        <v>Abankwah</v>
+        <v>Vogliacco</v>
       </c>
       <c r="C461" s="2" t="str">
-        <v/>
+        <v>*</v>
       </c>
       <c r="D461" s="2" t="str">
-        <v>Udinese</v>
+        <v>Genoa</v>
       </c>
       <c r="E461" s="2">
-        <v>22</v>
+        <v>28</v>
       </c>
       <c r="F461" s="2" t="str">
         <v>D</v>
@@ -17937,19 +17931,19 @@
     </row>
     <row r="462">
       <c r="A462" s="2">
-        <v>5994</v>
+        <v>6244</v>
       </c>
       <c r="B462" s="2" t="str">
-        <v>Ebosse</v>
+        <v>Matturro</v>
       </c>
       <c r="C462" s="2" t="str">
         <v/>
       </c>
       <c r="D462" s="2" t="str">
-        <v>Udinese</v>
+        <v>Genoa</v>
       </c>
       <c r="E462" s="2">
-        <v>27</v>
+        <v>22</v>
       </c>
       <c r="F462" s="2" t="str">
         <v>D</v>
@@ -17970,30 +17964,30 @@
         <v>1</v>
       </c>
       <c r="L462" s="2">
-        <v>2</v>
+        <v>1</v>
       </c>
     </row>
     <row r="463">
       <c r="A463" s="2">
-        <v>5498</v>
+        <v>6189</v>
       </c>
       <c r="B463" s="2" t="str">
-        <v>Casale</v>
+        <v>Missori</v>
       </c>
       <c r="C463" s="2" t="str">
         <v/>
       </c>
       <c r="D463" s="2" t="str">
-        <v>Bologna</v>
+        <v>Sassuolo</v>
       </c>
       <c r="E463" s="2">
-        <v>28</v>
+        <v>22</v>
       </c>
       <c r="F463" s="2" t="str">
         <v>D</v>
       </c>
       <c r="G463" s="2" t="str">
-        <v>Dc</v>
+        <v>Dd/E</v>
       </c>
       <c r="H463" s="2">
         <v>0</v>
@@ -18008,30 +18002,30 @@
         <v>1</v>
       </c>
       <c r="L463" s="2">
-        <v>3</v>
+        <v>1</v>
       </c>
     </row>
     <row r="464">
       <c r="A464" s="2">
-        <v>5481</v>
+        <v>6149</v>
       </c>
       <c r="B464" s="2" t="str">
-        <v>Mazzocchi</v>
+        <v>Carboni F.</v>
       </c>
       <c r="C464" s="2" t="str">
         <v/>
       </c>
       <c r="D464" s="2" t="str">
-        <v>Napoli</v>
+        <v>Parma</v>
       </c>
       <c r="E464" s="2">
-        <v>31</v>
+        <v>23</v>
       </c>
       <c r="F464" s="2" t="str">
         <v>D</v>
       </c>
       <c r="G464" s="2" t="str">
-        <v>Dd/Ds/E</v>
+        <v>Ds/E</v>
       </c>
       <c r="H464" s="2">
         <v>0</v>
@@ -18051,25 +18045,25 @@
     </row>
     <row r="465">
       <c r="A465" s="2">
-        <v>5424</v>
+        <v>6039</v>
       </c>
       <c r="B465" s="2" t="str">
-        <v>Amey</v>
+        <v>Cabal</v>
       </c>
       <c r="C465" s="2" t="str">
         <v/>
       </c>
       <c r="D465" s="2" t="str">
-        <v>Frosinone</v>
+        <v>Juventus</v>
       </c>
       <c r="E465" s="2">
-        <v>21</v>
+        <v>25</v>
       </c>
       <c r="F465" s="2" t="str">
         <v>D</v>
       </c>
       <c r="G465" s="2" t="str">
-        <v>Dc</v>
+        <v>B/Ds/E</v>
       </c>
       <c r="H465" s="2">
         <v>0</v>
@@ -18089,25 +18083,25 @@
     </row>
     <row r="466">
       <c r="A466" s="2">
-        <v>5399</v>
+        <v>6021</v>
       </c>
       <c r="B466" s="2" t="str">
-        <v>Antov</v>
+        <v>Abankwah</v>
       </c>
       <c r="C466" s="2" t="str">
         <v/>
       </c>
       <c r="D466" s="2" t="str">
-        <v>Monza</v>
+        <v>Udinese</v>
       </c>
       <c r="E466" s="2">
-        <v>26</v>
+        <v>22</v>
       </c>
       <c r="F466" s="2" t="str">
         <v>D</v>
       </c>
       <c r="G466" s="2" t="str">
-        <v>Dc</v>
+        <v>Dd/Dc</v>
       </c>
       <c r="H466" s="2">
         <v>0</v>
@@ -18127,16 +18121,16 @@
     </row>
     <row r="467">
       <c r="A467" s="2">
-        <v>2728</v>
+        <v>5994</v>
       </c>
       <c r="B467" s="2" t="str">
-        <v>Pellegrini Lu.</v>
+        <v>Ebosse</v>
       </c>
       <c r="C467" s="2" t="str">
         <v/>
       </c>
       <c r="D467" s="2" t="str">
-        <v>Lazio</v>
+        <v>Udinese</v>
       </c>
       <c r="E467" s="2">
         <v>27</v>
@@ -18145,7 +18139,7 @@
         <v>D</v>
       </c>
       <c r="G467" s="2" t="str">
-        <v>Ds/E</v>
+        <v>Ds/Dc</v>
       </c>
       <c r="H467" s="2">
         <v>0</v>
@@ -18165,25 +18159,25 @@
     </row>
     <row r="468">
       <c r="A468" s="2">
-        <v>791</v>
+        <v>5498</v>
       </c>
       <c r="B468" s="2" t="str">
-        <v>Sabelli</v>
+        <v>Casale</v>
       </c>
       <c r="C468" s="2" t="str">
         <v/>
       </c>
       <c r="D468" s="2" t="str">
-        <v>Genoa</v>
+        <v>Bologna</v>
       </c>
       <c r="E468" s="2">
-        <v>33</v>
+        <v>28</v>
       </c>
       <c r="F468" s="2" t="str">
         <v>D</v>
       </c>
       <c r="G468" s="2" t="str">
-        <v>Dd/Ds/E</v>
+        <v>Dc</v>
       </c>
       <c r="H468" s="2">
         <v>0</v>
@@ -18198,30 +18192,30 @@
         <v>1</v>
       </c>
       <c r="L468" s="2">
-        <v>2</v>
+        <v>3</v>
       </c>
     </row>
     <row r="469">
       <c r="A469" s="2">
-        <v>487</v>
+        <v>5481</v>
       </c>
       <c r="B469" s="2" t="str">
-        <v>De Silvestri</v>
+        <v>Mazzocchi</v>
       </c>
       <c r="C469" s="2" t="str">
         <v/>
       </c>
       <c r="D469" s="2" t="str">
-        <v>Bologna</v>
+        <v>Napoli</v>
       </c>
       <c r="E469" s="2">
-        <v>38</v>
+        <v>31</v>
       </c>
       <c r="F469" s="2" t="str">
         <v>D</v>
       </c>
       <c r="G469" s="2" t="str">
-        <v>Dd/E</v>
+        <v>Dd/Ds/E</v>
       </c>
       <c r="H469" s="2">
         <v>0</v>
@@ -18241,19 +18235,19 @@
     </row>
     <row r="470">
       <c r="A470" s="2">
-        <v>418</v>
+        <v>5424</v>
       </c>
       <c r="B470" s="2" t="str">
-        <v>Goldaniga</v>
+        <v>Amey</v>
       </c>
       <c r="C470" s="2" t="str">
         <v/>
       </c>
       <c r="D470" s="2" t="str">
-        <v>Como</v>
+        <v>Frosinone</v>
       </c>
       <c r="E470" s="2">
-        <v>33</v>
+        <v>21</v>
       </c>
       <c r="F470" s="2" t="str">
         <v>D</v>
@@ -18279,25 +18273,25 @@
     </row>
     <row r="471">
       <c r="A471" s="2">
-        <v>327</v>
+        <v>5399</v>
       </c>
       <c r="B471" s="2" t="str">
-        <v>Patric</v>
+        <v>Antov</v>
       </c>
       <c r="C471" s="2" t="str">
         <v/>
       </c>
       <c r="D471" s="2" t="str">
-        <v>Lazio</v>
+        <v>Monza</v>
       </c>
       <c r="E471" s="2">
-        <v>33</v>
+        <v>26</v>
       </c>
       <c r="F471" s="2" t="str">
         <v>D</v>
       </c>
       <c r="G471" s="2" t="str">
-        <v>Dd/Dc</v>
+        <v>Dc</v>
       </c>
       <c r="H471" s="2">
         <v>0</v>
@@ -18317,25 +18311,25 @@
     </row>
     <row r="472">
       <c r="A472" s="2">
-        <v>294</v>
+        <v>2728</v>
       </c>
       <c r="B472" s="2" t="str">
-        <v>Rugani</v>
+        <v>Pellegrini Lu.</v>
       </c>
       <c r="C472" s="2" t="str">
         <v/>
       </c>
       <c r="D472" s="2" t="str">
-        <v>Juventus</v>
+        <v>Lazio</v>
       </c>
       <c r="E472" s="2">
-        <v>32</v>
+        <v>27</v>
       </c>
       <c r="F472" s="2" t="str">
         <v>D</v>
       </c>
       <c r="G472" s="2" t="str">
-        <v>Dc</v>
+        <v>Ds/E</v>
       </c>
       <c r="H472" s="2">
         <v>0</v>
@@ -18350,30 +18344,30 @@
         <v>1</v>
       </c>
       <c r="L472" s="2">
-        <v>1</v>
+        <v>2</v>
       </c>
     </row>
     <row r="473">
       <c r="A473" s="2">
-        <v>252</v>
+        <v>791</v>
       </c>
       <c r="B473" s="2" t="str">
-        <v>Biraghi</v>
+        <v>Sabelli</v>
       </c>
       <c r="C473" s="2" t="str">
         <v/>
       </c>
       <c r="D473" s="2" t="str">
-        <v>Torino</v>
+        <v>Genoa</v>
       </c>
       <c r="E473" s="2">
-        <v>34</v>
+        <v>33</v>
       </c>
       <c r="F473" s="2" t="str">
         <v>D</v>
       </c>
       <c r="G473" s="2" t="str">
-        <v>B/Ds/E</v>
+        <v>Dd/Ds/E</v>
       </c>
       <c r="H473" s="2">
         <v>0</v>
@@ -18393,25 +18387,25 @@
     </row>
     <row r="474">
       <c r="A474" s="2">
-        <v>7557</v>
+        <v>487</v>
       </c>
       <c r="B474" s="2" t="str">
-        <v>Penev</v>
+        <v>De Silvestri</v>
       </c>
       <c r="C474" s="2" t="str">
         <v/>
       </c>
       <c r="D474" s="2" t="str">
-        <v>Lecce</v>
+        <v>Bologna</v>
       </c>
       <c r="E474" s="2">
-        <v>18</v>
+        <v>38</v>
       </c>
       <c r="F474" s="2" t="str">
-        <v>P</v>
+        <v>D</v>
       </c>
       <c r="G474" s="2" t="str">
-        <v>Por</v>
+        <v>Dd/E</v>
       </c>
       <c r="H474" s="2">
         <v>0</v>
@@ -18431,25 +18425,25 @@
     </row>
     <row r="475">
       <c r="A475" s="2">
-        <v>7545</v>
+        <v>418</v>
       </c>
       <c r="B475" s="2" t="str">
-        <v>Vismara</v>
+        <v>Goldaniga</v>
       </c>
       <c r="C475" s="2" t="str">
         <v/>
       </c>
       <c r="D475" s="2" t="str">
-        <v>Atalanta</v>
+        <v>Como</v>
       </c>
       <c r="E475" s="2">
-        <v>23</v>
+        <v>33</v>
       </c>
       <c r="F475" s="2" t="str">
-        <v>P</v>
+        <v>D</v>
       </c>
       <c r="G475" s="2" t="str">
-        <v>Por</v>
+        <v>Dc</v>
       </c>
       <c r="H475" s="2">
         <v>0</v>
@@ -18469,10 +18463,10 @@
     </row>
     <row r="476">
       <c r="A476" s="2">
-        <v>7534</v>
+        <v>327</v>
       </c>
       <c r="B476" s="2" t="str">
-        <v>Renzetti</v>
+        <v>Patric</v>
       </c>
       <c r="C476" s="2" t="str">
         <v/>
@@ -18481,13 +18475,13 @@
         <v>Lazio</v>
       </c>
       <c r="E476" s="2">
-        <v>20</v>
+        <v>33</v>
       </c>
       <c r="F476" s="2" t="str">
-        <v>P</v>
+        <v>D</v>
       </c>
       <c r="G476" s="2" t="str">
-        <v>Por</v>
+        <v>Dd/Dc</v>
       </c>
       <c r="H476" s="2">
         <v>0</v>
@@ -18507,25 +18501,25 @@
     </row>
     <row r="477">
       <c r="A477" s="2">
-        <v>7533</v>
+        <v>294</v>
       </c>
       <c r="B477" s="2" t="str">
-        <v>Happonen</v>
+        <v>Rugani</v>
       </c>
       <c r="C477" s="2" t="str">
         <v/>
       </c>
       <c r="D477" s="2" t="str">
-        <v>Bologna</v>
+        <v>Juventus</v>
       </c>
       <c r="E477" s="2">
-        <v>19</v>
+        <v>32</v>
       </c>
       <c r="F477" s="2" t="str">
-        <v>P</v>
+        <v>D</v>
       </c>
       <c r="G477" s="2" t="str">
-        <v>Por</v>
+        <v>Dc</v>
       </c>
       <c r="H477" s="2">
         <v>0</v>
@@ -18545,25 +18539,25 @@
     </row>
     <row r="478">
       <c r="A478" s="2">
-        <v>7531</v>
+        <v>252</v>
       </c>
       <c r="B478" s="2" t="str">
-        <v>Pozzi</v>
+        <v>Biraghi</v>
       </c>
       <c r="C478" s="2" t="str">
         <v/>
       </c>
       <c r="D478" s="2" t="str">
-        <v>Venezia</v>
+        <v>Torino</v>
       </c>
       <c r="E478" s="2">
-        <v>26</v>
+        <v>34</v>
       </c>
       <c r="F478" s="2" t="str">
-        <v>P</v>
+        <v>D</v>
       </c>
       <c r="G478" s="2" t="str">
-        <v>Por</v>
+        <v>B/Ds/E</v>
       </c>
       <c r="H478" s="2">
         <v>0</v>
@@ -18578,24 +18572,24 @@
         <v>1</v>
       </c>
       <c r="L478" s="2">
-        <v>1</v>
+        <v>2</v>
       </c>
     </row>
     <row r="479">
       <c r="A479" s="2">
-        <v>7475</v>
+        <v>7560</v>
       </c>
       <c r="B479" s="2" t="str">
-        <v>Strajnar</v>
+        <v>Pisseri</v>
       </c>
       <c r="C479" s="2" t="str">
         <v/>
       </c>
       <c r="D479" s="2" t="str">
-        <v>Monza</v>
+        <v>Frosinone</v>
       </c>
       <c r="E479" s="2">
-        <v>19</v>
+        <v>35</v>
       </c>
       <c r="F479" s="2" t="str">
         <v>P</v>
@@ -18621,19 +18615,19 @@
     </row>
     <row r="480">
       <c r="A480" s="2">
-        <v>7466</v>
+        <v>7557</v>
       </c>
       <c r="B480" s="2" t="str">
-        <v>Lolic</v>
+        <v>Penev</v>
       </c>
       <c r="C480" s="2" t="str">
         <v/>
       </c>
       <c r="D480" s="2" t="str">
-        <v>Frosinone</v>
+        <v>Lecce</v>
       </c>
       <c r="E480" s="2">
-        <v>22</v>
+        <v>18</v>
       </c>
       <c r="F480" s="2" t="str">
         <v>P</v>
@@ -18659,19 +18653,19 @@
     </row>
     <row r="481">
       <c r="A481" s="2">
-        <v>7457</v>
+        <v>7545</v>
       </c>
       <c r="B481" s="2" t="str">
-        <v>Mascardi</v>
+        <v>Vismara</v>
       </c>
       <c r="C481" s="2" t="str">
         <v/>
       </c>
       <c r="D481" s="2" t="str">
-        <v>Torino</v>
+        <v>Atalanta</v>
       </c>
       <c r="E481" s="2">
-        <v>20</v>
+        <v>23</v>
       </c>
       <c r="F481" s="2" t="str">
         <v>P</v>
@@ -18697,19 +18691,19 @@
     </row>
     <row r="482">
       <c r="A482" s="2">
-        <v>7411</v>
+        <v>7534</v>
       </c>
       <c r="B482" s="2" t="str">
-        <v>Daffara</v>
+        <v>Renzetti</v>
       </c>
       <c r="C482" s="2" t="str">
         <v/>
       </c>
       <c r="D482" s="2" t="str">
-        <v>Parma</v>
+        <v>Lazio</v>
       </c>
       <c r="E482" s="2">
-        <v>22</v>
+        <v>20</v>
       </c>
       <c r="F482" s="2" t="str">
         <v>P</v>
@@ -18730,24 +18724,24 @@
         <v>1</v>
       </c>
       <c r="L482" s="2">
-        <v>7</v>
+        <v>1</v>
       </c>
     </row>
     <row r="483">
       <c r="A483" s="2">
-        <v>7363</v>
+        <v>7533</v>
       </c>
       <c r="B483" s="2" t="str">
-        <v>Siviero</v>
+        <v>Happonen</v>
       </c>
       <c r="C483" s="2" t="str">
         <v/>
       </c>
       <c r="D483" s="2" t="str">
-        <v>Torino</v>
+        <v>Bologna</v>
       </c>
       <c r="E483" s="2">
-        <v>20</v>
+        <v>19</v>
       </c>
       <c r="F483" s="2" t="str">
         <v>P</v>
@@ -18773,19 +18767,19 @@
     </row>
     <row r="484">
       <c r="A484" s="2">
-        <v>7337</v>
+        <v>7531</v>
       </c>
       <c r="B484" s="2" t="str">
-        <v>Motta</v>
+        <v>Pozzi</v>
       </c>
       <c r="C484" s="2" t="str">
         <v/>
       </c>
       <c r="D484" s="2" t="str">
-        <v>Lazio</v>
+        <v>Venezia</v>
       </c>
       <c r="E484" s="2">
-        <v>21</v>
+        <v>26</v>
       </c>
       <c r="F484" s="2" t="str">
         <v>P</v>
@@ -18811,19 +18805,19 @@
     </row>
     <row r="485">
       <c r="A485" s="2">
-        <v>7301</v>
+        <v>7475</v>
       </c>
       <c r="B485" s="2" t="str">
-        <v>Tornqvist</v>
+        <v>Strajnar</v>
       </c>
       <c r="C485" s="2" t="str">
         <v/>
       </c>
       <c r="D485" s="2" t="str">
-        <v>Como</v>
+        <v>Monza</v>
       </c>
       <c r="E485" s="2">
-        <v>24</v>
+        <v>19</v>
       </c>
       <c r="F485" s="2" t="str">
         <v>P</v>
@@ -18849,19 +18843,19 @@
     </row>
     <row r="486">
       <c r="A486" s="2">
-        <v>7172</v>
+        <v>7466</v>
       </c>
       <c r="B486" s="2" t="str">
-        <v>Pessina Mas.</v>
+        <v>Lolic</v>
       </c>
       <c r="C486" s="2" t="str">
         <v/>
       </c>
       <c r="D486" s="2" t="str">
-        <v>Bologna</v>
+        <v>Frosinone</v>
       </c>
       <c r="E486" s="2">
-        <v>19</v>
+        <v>22</v>
       </c>
       <c r="F486" s="2" t="str">
         <v>P</v>
@@ -18887,19 +18881,19 @@
     </row>
     <row r="487">
       <c r="A487" s="2">
-        <v>7048</v>
+        <v>7457</v>
       </c>
       <c r="B487" s="2" t="str">
-        <v>De Marzi</v>
+        <v>Mascardi</v>
       </c>
       <c r="C487" s="2" t="str">
         <v/>
       </c>
       <c r="D487" s="2" t="str">
-        <v>Roma</v>
+        <v>Torino</v>
       </c>
       <c r="E487" s="2">
-        <v>19</v>
+        <v>20</v>
       </c>
       <c r="F487" s="2" t="str">
         <v>P</v>
@@ -18925,19 +18919,19 @@
     </row>
     <row r="488">
       <c r="A488" s="2">
-        <v>6813</v>
+        <v>7411</v>
       </c>
       <c r="B488" s="2" t="str">
-        <v>Torriani</v>
+        <v>Daffara</v>
       </c>
       <c r="C488" s="2" t="str">
         <v/>
       </c>
       <c r="D488" s="2" t="str">
-        <v>Milan</v>
+        <v>Parma</v>
       </c>
       <c r="E488" s="2">
-        <v>21</v>
+        <v>22</v>
       </c>
       <c r="F488" s="2" t="str">
         <v>P</v>
@@ -18958,24 +18952,24 @@
         <v>1</v>
       </c>
       <c r="L488" s="2">
-        <v>1</v>
+        <v>7</v>
       </c>
     </row>
     <row r="489">
       <c r="A489" s="2">
-        <v>6682</v>
+        <v>7363</v>
       </c>
       <c r="B489" s="2" t="str">
-        <v>Pizzignacco</v>
+        <v>Siviero</v>
       </c>
       <c r="C489" s="2" t="str">
         <v/>
       </c>
       <c r="D489" s="2" t="str">
-        <v>Monza</v>
+        <v>Torino</v>
       </c>
       <c r="E489" s="2">
-        <v>25</v>
+        <v>20</v>
       </c>
       <c r="F489" s="2" t="str">
         <v>P</v>
@@ -19001,19 +18995,19 @@
     </row>
     <row r="490">
       <c r="A490" s="2">
-        <v>6671</v>
+        <v>7337</v>
       </c>
       <c r="B490" s="2" t="str">
-        <v>Grandi</v>
+        <v>Motta</v>
       </c>
       <c r="C490" s="2" t="str">
         <v/>
       </c>
       <c r="D490" s="2" t="str">
-        <v>Venezia</v>
+        <v>Lazio</v>
       </c>
       <c r="E490" s="2">
-        <v>34</v>
+        <v>21</v>
       </c>
       <c r="F490" s="2" t="str">
         <v>P</v>
@@ -19039,19 +19033,19 @@
     </row>
     <row r="491">
       <c r="A491" s="2">
-        <v>6662</v>
+        <v>7301</v>
       </c>
       <c r="B491" s="2" t="str">
-        <v>Corvi</v>
+        <v>Tornqvist</v>
       </c>
       <c r="C491" s="2" t="str">
         <v/>
       </c>
       <c r="D491" s="2" t="str">
-        <v>Parma</v>
+        <v>Como</v>
       </c>
       <c r="E491" s="2">
-        <v>25</v>
+        <v>24</v>
       </c>
       <c r="F491" s="2" t="str">
         <v>P</v>
@@ -19077,19 +19071,19 @@
     </row>
     <row r="492">
       <c r="A492" s="2">
-        <v>6650</v>
+        <v>7172</v>
       </c>
       <c r="B492" s="2" t="str">
-        <v>Sherri</v>
+        <v>Pessina Mas.</v>
       </c>
       <c r="C492" s="2" t="str">
         <v/>
       </c>
       <c r="D492" s="2" t="str">
-        <v>Cagliari</v>
+        <v>Bologna</v>
       </c>
       <c r="E492" s="2">
-        <v>29</v>
+        <v>19</v>
       </c>
       <c r="F492" s="2" t="str">
         <v>P</v>
@@ -19115,19 +19109,19 @@
     </row>
     <row r="493">
       <c r="A493" s="2">
-        <v>6569</v>
+        <v>7048</v>
       </c>
       <c r="B493" s="2" t="str">
-        <v>Stolz</v>
+        <v>De Marzi</v>
       </c>
       <c r="C493" s="2" t="str">
         <v/>
       </c>
       <c r="D493" s="2" t="str">
-        <v>Genoa</v>
+        <v>Roma</v>
       </c>
       <c r="E493" s="2">
-        <v>25</v>
+        <v>19</v>
       </c>
       <c r="F493" s="2" t="str">
         <v>P</v>
@@ -19153,19 +19147,19 @@
     </row>
     <row r="494">
       <c r="A494" s="2">
-        <v>6523</v>
+        <v>6813</v>
       </c>
       <c r="B494" s="2" t="str">
-        <v>Samooja</v>
+        <v>Torriani</v>
       </c>
       <c r="C494" s="2" t="str">
-        <v>*</v>
+        <v/>
       </c>
       <c r="D494" s="2" t="str">
-        <v>Lecce</v>
+        <v>Milan</v>
       </c>
       <c r="E494" s="2">
-        <v>23</v>
+        <v>21</v>
       </c>
       <c r="F494" s="2" t="str">
         <v>P</v>
@@ -19191,19 +19185,19 @@
     </row>
     <row r="495">
       <c r="A495" s="2">
-        <v>6403</v>
+        <v>6682</v>
       </c>
       <c r="B495" s="2" t="str">
-        <v>Christensen O.</v>
+        <v>Pizzignacco</v>
       </c>
       <c r="C495" s="2" t="str">
         <v/>
       </c>
       <c r="D495" s="2" t="str">
-        <v>Fiorentina</v>
+        <v>Monza</v>
       </c>
       <c r="E495" s="2">
-        <v>27</v>
+        <v>25</v>
       </c>
       <c r="F495" s="2" t="str">
         <v>P</v>
@@ -19229,19 +19223,19 @@
     </row>
     <row r="496">
       <c r="A496" s="2">
-        <v>5707</v>
+        <v>6671</v>
       </c>
       <c r="B496" s="2" t="str">
-        <v>Piana</v>
+        <v>Grandi</v>
       </c>
       <c r="C496" s="2" t="str">
         <v/>
       </c>
       <c r="D496" s="2" t="str">
-        <v>Udinese</v>
+        <v>Venezia</v>
       </c>
       <c r="E496" s="2">
-        <v>23</v>
+        <v>34</v>
       </c>
       <c r="F496" s="2" t="str">
         <v>P</v>
@@ -19267,19 +19261,19 @@
     </row>
     <row r="497">
       <c r="A497" s="2">
-        <v>5320</v>
+        <v>6662</v>
       </c>
       <c r="B497" s="2" t="str">
-        <v>Paleari</v>
+        <v>Corvi</v>
       </c>
       <c r="C497" s="2" t="str">
         <v/>
       </c>
       <c r="D497" s="2" t="str">
-        <v>Torino</v>
+        <v>Parma</v>
       </c>
       <c r="E497" s="2">
-        <v>34</v>
+        <v>25</v>
       </c>
       <c r="F497" s="2" t="str">
         <v>P</v>
@@ -19305,19 +19299,19 @@
     </row>
     <row r="498">
       <c r="A498" s="2">
-        <v>4929</v>
+        <v>6650</v>
       </c>
       <c r="B498" s="2" t="str">
-        <v>Ciocci</v>
+        <v>Sherri</v>
       </c>
       <c r="C498" s="2" t="str">
-        <v>*</v>
+        <v/>
       </c>
       <c r="D498" s="2" t="str">
         <v>Cagliari</v>
       </c>
       <c r="E498" s="2">
-        <v>24</v>
+        <v>29</v>
       </c>
       <c r="F498" s="2" t="str">
         <v>P</v>
@@ -19343,16 +19337,16 @@
     </row>
     <row r="499">
       <c r="A499" s="2">
-        <v>4867</v>
+        <v>6569</v>
       </c>
       <c r="B499" s="2" t="str">
-        <v>Turati</v>
+        <v>Stolz</v>
       </c>
       <c r="C499" s="2" t="str">
         <v/>
       </c>
       <c r="D499" s="2" t="str">
-        <v>Sassuolo</v>
+        <v>Genoa</v>
       </c>
       <c r="E499" s="2">
         <v>25</v>
@@ -19381,19 +19375,19 @@
     </row>
     <row r="500">
       <c r="A500" s="2">
-        <v>4518</v>
+        <v>6523</v>
       </c>
       <c r="B500" s="2" t="str">
-        <v>Russo A.</v>
+        <v>Samooja</v>
       </c>
       <c r="C500" s="2" t="str">
-        <v/>
+        <v>*</v>
       </c>
       <c r="D500" s="2" t="str">
-        <v>Sassuolo</v>
+        <v>Lecce</v>
       </c>
       <c r="E500" s="2">
-        <v>25</v>
+        <v>23</v>
       </c>
       <c r="F500" s="2" t="str">
         <v>P</v>
@@ -19419,19 +19413,19 @@
     </row>
     <row r="501">
       <c r="A501" s="2">
-        <v>2845</v>
+        <v>6403</v>
       </c>
       <c r="B501" s="2" t="str">
-        <v>Contini</v>
+        <v>Christensen O.</v>
       </c>
       <c r="C501" s="2" t="str">
         <v/>
       </c>
       <c r="D501" s="2" t="str">
-        <v>Napoli</v>
+        <v>Fiorentina</v>
       </c>
       <c r="E501" s="2">
-        <v>30</v>
+        <v>27</v>
       </c>
       <c r="F501" s="2" t="str">
         <v>P</v>
@@ -19457,19 +19451,19 @@
     </row>
     <row r="502">
       <c r="A502" s="2">
-        <v>2815</v>
+        <v>5707</v>
       </c>
       <c r="B502" s="2" t="str">
-        <v>Terracciano</v>
+        <v>Piana</v>
       </c>
       <c r="C502" s="2" t="str">
         <v/>
       </c>
       <c r="D502" s="2" t="str">
-        <v>Milan</v>
+        <v>Udinese</v>
       </c>
       <c r="E502" s="2">
-        <v>36</v>
+        <v>23</v>
       </c>
       <c r="F502" s="2" t="str">
         <v>P</v>
@@ -19495,19 +19489,19 @@
     </row>
     <row r="503">
       <c r="A503" s="2">
-        <v>2814</v>
+        <v>5320</v>
       </c>
       <c r="B503" s="2" t="str">
-        <v>Provedel</v>
+        <v>Paleari</v>
       </c>
       <c r="C503" s="2" t="str">
         <v/>
       </c>
       <c r="D503" s="2" t="str">
-        <v>Inter</v>
+        <v>Torino</v>
       </c>
       <c r="E503" s="2">
-        <v>32</v>
+        <v>34</v>
       </c>
       <c r="F503" s="2" t="str">
         <v>P</v>
@@ -19528,24 +19522,24 @@
         <v>1</v>
       </c>
       <c r="L503" s="2">
-        <v>2</v>
+        <v>1</v>
       </c>
     </row>
     <row r="504">
       <c r="A504" s="2">
-        <v>2809</v>
+        <v>4929</v>
       </c>
       <c r="B504" s="2" t="str">
-        <v>Vigorito</v>
+        <v>Ciocci</v>
       </c>
       <c r="C504" s="2" t="str">
-        <v/>
+        <v>*</v>
       </c>
       <c r="D504" s="2" t="str">
-        <v>Como</v>
+        <v>Cagliari</v>
       </c>
       <c r="E504" s="2">
-        <v>36</v>
+        <v>24</v>
       </c>
       <c r="F504" s="2" t="str">
         <v>P</v>
@@ -19571,19 +19565,19 @@
     </row>
     <row r="505">
       <c r="A505" s="2">
-        <v>2401</v>
+        <v>4867</v>
       </c>
       <c r="B505" s="2" t="str">
-        <v>Fruchtl</v>
+        <v>Turati</v>
       </c>
       <c r="C505" s="2" t="str">
-        <v>*</v>
+        <v/>
       </c>
       <c r="D505" s="2" t="str">
-        <v>Lecce</v>
+        <v>Sassuolo</v>
       </c>
       <c r="E505" s="2">
-        <v>26</v>
+        <v>25</v>
       </c>
       <c r="F505" s="2" t="str">
         <v>P</v>
@@ -19609,19 +19603,19 @@
     </row>
     <row r="506">
       <c r="A506" s="2">
-        <v>2297</v>
+        <v>4518</v>
       </c>
       <c r="B506" s="2" t="str">
-        <v>Rossi F.</v>
+        <v>Russo A.</v>
       </c>
       <c r="C506" s="2" t="str">
-        <v>*</v>
+        <v/>
       </c>
       <c r="D506" s="2" t="str">
-        <v>Atalanta</v>
+        <v>Sassuolo</v>
       </c>
       <c r="E506" s="2">
-        <v>35</v>
+        <v>25</v>
       </c>
       <c r="F506" s="2" t="str">
         <v>P</v>
@@ -19647,19 +19641,19 @@
     </row>
     <row r="507">
       <c r="A507" s="2">
-        <v>2127</v>
+        <v>2845</v>
       </c>
       <c r="B507" s="2" t="str">
-        <v>Satalino</v>
+        <v>Contini</v>
       </c>
       <c r="C507" s="2" t="str">
         <v/>
       </c>
       <c r="D507" s="2" t="str">
-        <v>Sassuolo</v>
+        <v>Napoli</v>
       </c>
       <c r="E507" s="2">
-        <v>27</v>
+        <v>30</v>
       </c>
       <c r="F507" s="2" t="str">
         <v>P</v>
@@ -19685,16 +19679,16 @@
     </row>
     <row r="508">
       <c r="A508" s="2">
-        <v>1930</v>
+        <v>2815</v>
       </c>
       <c r="B508" s="2" t="str">
-        <v>Pinsoglio</v>
+        <v>Terracciano</v>
       </c>
       <c r="C508" s="2" t="str">
         <v/>
       </c>
       <c r="D508" s="2" t="str">
-        <v>Juventus</v>
+        <v>Milan</v>
       </c>
       <c r="E508" s="2">
         <v>36</v>
@@ -19723,10 +19717,10 @@
     </row>
     <row r="509">
       <c r="A509" s="2">
-        <v>1926</v>
+        <v>2814</v>
       </c>
       <c r="B509" s="2" t="str">
-        <v>Di Gennaro</v>
+        <v>Provedel</v>
       </c>
       <c r="C509" s="2" t="str">
         <v/>
@@ -19735,7 +19729,7 @@
         <v>Inter</v>
       </c>
       <c r="E509" s="2">
-        <v>33</v>
+        <v>32</v>
       </c>
       <c r="F509" s="2" t="str">
         <v>P</v>
@@ -19756,24 +19750,24 @@
         <v>1</v>
       </c>
       <c r="L509" s="2">
-        <v>1</v>
+        <v>2</v>
       </c>
     </row>
     <row r="510">
       <c r="A510" s="2">
-        <v>610</v>
+        <v>2809</v>
       </c>
       <c r="B510" s="2" t="str">
-        <v>Gollini</v>
+        <v>Vigorito</v>
       </c>
       <c r="C510" s="2" t="str">
         <v/>
       </c>
       <c r="D510" s="2" t="str">
-        <v>Roma</v>
+        <v>Como</v>
       </c>
       <c r="E510" s="2">
-        <v>31</v>
+        <v>36</v>
       </c>
       <c r="F510" s="2" t="str">
         <v>P</v>
@@ -19799,19 +19793,19 @@
     </row>
     <row r="511">
       <c r="A511" s="2">
-        <v>543</v>
+        <v>2401</v>
       </c>
       <c r="B511" s="2" t="str">
-        <v>Padelli</v>
+        <v>Fruchtl</v>
       </c>
       <c r="C511" s="2" t="str">
-        <v/>
+        <v>*</v>
       </c>
       <c r="D511" s="2" t="str">
-        <v>Udinese</v>
+        <v>Lecce</v>
       </c>
       <c r="E511" s="2">
-        <v>41</v>
+        <v>26</v>
       </c>
       <c r="F511" s="2" t="str">
         <v>P</v>
@@ -19837,19 +19831,19 @@
     </row>
     <row r="512">
       <c r="A512" s="2">
-        <v>219</v>
+        <v>2297</v>
       </c>
       <c r="B512" s="2" t="str">
-        <v>Sommariva</v>
+        <v>Rossi F.</v>
       </c>
       <c r="C512" s="2" t="str">
-        <v/>
+        <v>*</v>
       </c>
       <c r="D512" s="2" t="str">
-        <v>Genoa</v>
+        <v>Atalanta</v>
       </c>
       <c r="E512" s="2">
-        <v>29</v>
+        <v>35</v>
       </c>
       <c r="F512" s="2" t="str">
         <v>P</v>
@@ -19875,19 +19869,19 @@
     </row>
     <row r="513">
       <c r="A513" s="2">
-        <v>158</v>
+        <v>2127</v>
       </c>
       <c r="B513" s="2" t="str">
-        <v>Lezzerini</v>
+        <v>Satalino</v>
       </c>
       <c r="C513" s="2" t="str">
         <v/>
       </c>
       <c r="D513" s="2" t="str">
-        <v>Fiorentina</v>
+        <v>Sassuolo</v>
       </c>
       <c r="E513" s="2">
-        <v>31</v>
+        <v>27</v>
       </c>
       <c r="F513" s="2" t="str">
         <v>P</v>
@@ -19913,19 +19907,19 @@
     </row>
     <row r="514">
       <c r="A514" s="2">
-        <v>4</v>
+        <v>1930</v>
       </c>
       <c r="B514" s="2" t="str">
-        <v>Sportiello</v>
+        <v>Pinsoglio</v>
       </c>
       <c r="C514" s="2" t="str">
         <v/>
       </c>
       <c r="D514" s="2" t="str">
-        <v>Atalanta</v>
+        <v>Juventus</v>
       </c>
       <c r="E514" s="2">
-        <v>34</v>
+        <v>36</v>
       </c>
       <c r="F514" s="2" t="str">
         <v>P</v>
@@ -19949,9 +19943,313 @@
         <v>1</v>
       </c>
     </row>
+    <row r="515">
+      <c r="A515" s="2">
+        <v>1926</v>
+      </c>
+      <c r="B515" s="2" t="str">
+        <v>Di Gennaro</v>
+      </c>
+      <c r="C515" s="2" t="str">
+        <v/>
+      </c>
+      <c r="D515" s="2" t="str">
+        <v>Inter</v>
+      </c>
+      <c r="E515" s="2">
+        <v>33</v>
+      </c>
+      <c r="F515" s="2" t="str">
+        <v>P</v>
+      </c>
+      <c r="G515" s="2" t="str">
+        <v>Por</v>
+      </c>
+      <c r="H515" s="2">
+        <v>0</v>
+      </c>
+      <c r="I515" s="2">
+        <v>0</v>
+      </c>
+      <c r="J515" s="2">
+        <v>0</v>
+      </c>
+      <c r="K515" s="2">
+        <v>1</v>
+      </c>
+      <c r="L515" s="2">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="516">
+      <c r="A516" s="2">
+        <v>610</v>
+      </c>
+      <c r="B516" s="2" t="str">
+        <v>Gollini</v>
+      </c>
+      <c r="C516" s="2" t="str">
+        <v/>
+      </c>
+      <c r="D516" s="2" t="str">
+        <v>Roma</v>
+      </c>
+      <c r="E516" s="2">
+        <v>31</v>
+      </c>
+      <c r="F516" s="2" t="str">
+        <v>P</v>
+      </c>
+      <c r="G516" s="2" t="str">
+        <v>Por</v>
+      </c>
+      <c r="H516" s="2">
+        <v>0</v>
+      </c>
+      <c r="I516" s="2">
+        <v>0</v>
+      </c>
+      <c r="J516" s="2">
+        <v>0</v>
+      </c>
+      <c r="K516" s="2">
+        <v>1</v>
+      </c>
+      <c r="L516" s="2">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="517">
+      <c r="A517" s="2">
+        <v>543</v>
+      </c>
+      <c r="B517" s="2" t="str">
+        <v>Padelli</v>
+      </c>
+      <c r="C517" s="2" t="str">
+        <v/>
+      </c>
+      <c r="D517" s="2" t="str">
+        <v>Udinese</v>
+      </c>
+      <c r="E517" s="2">
+        <v>41</v>
+      </c>
+      <c r="F517" s="2" t="str">
+        <v>P</v>
+      </c>
+      <c r="G517" s="2" t="str">
+        <v>Por</v>
+      </c>
+      <c r="H517" s="2">
+        <v>0</v>
+      </c>
+      <c r="I517" s="2">
+        <v>0</v>
+      </c>
+      <c r="J517" s="2">
+        <v>0</v>
+      </c>
+      <c r="K517" s="2">
+        <v>1</v>
+      </c>
+      <c r="L517" s="2">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="518">
+      <c r="A518" s="2">
+        <v>219</v>
+      </c>
+      <c r="B518" s="2" t="str">
+        <v>Sommariva</v>
+      </c>
+      <c r="C518" s="2" t="str">
+        <v/>
+      </c>
+      <c r="D518" s="2" t="str">
+        <v>Genoa</v>
+      </c>
+      <c r="E518" s="2">
+        <v>29</v>
+      </c>
+      <c r="F518" s="2" t="str">
+        <v>P</v>
+      </c>
+      <c r="G518" s="2" t="str">
+        <v>Por</v>
+      </c>
+      <c r="H518" s="2">
+        <v>0</v>
+      </c>
+      <c r="I518" s="2">
+        <v>0</v>
+      </c>
+      <c r="J518" s="2">
+        <v>0</v>
+      </c>
+      <c r="K518" s="2">
+        <v>1</v>
+      </c>
+      <c r="L518" s="2">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="519">
+      <c r="A519" s="2">
+        <v>218</v>
+      </c>
+      <c r="B519" s="2" t="str">
+        <v>Perin</v>
+      </c>
+      <c r="C519" s="2" t="str">
+        <v/>
+      </c>
+      <c r="D519" s="2" t="str">
+        <v>Juventus</v>
+      </c>
+      <c r="E519" s="2">
+        <v>34</v>
+      </c>
+      <c r="F519" s="2" t="str">
+        <v>P</v>
+      </c>
+      <c r="G519" s="2" t="str">
+        <v>Por</v>
+      </c>
+      <c r="H519" s="2">
+        <v>0</v>
+      </c>
+      <c r="I519" s="2">
+        <v>0</v>
+      </c>
+      <c r="J519" s="2">
+        <v>0</v>
+      </c>
+      <c r="K519" s="2">
+        <v>1</v>
+      </c>
+      <c r="L519" s="2">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="520">
+      <c r="A520" s="2">
+        <v>158</v>
+      </c>
+      <c r="B520" s="2" t="str">
+        <v>Lezzerini</v>
+      </c>
+      <c r="C520" s="2" t="str">
+        <v/>
+      </c>
+      <c r="D520" s="2" t="str">
+        <v>Fiorentina</v>
+      </c>
+      <c r="E520" s="2">
+        <v>31</v>
+      </c>
+      <c r="F520" s="2" t="str">
+        <v>P</v>
+      </c>
+      <c r="G520" s="2" t="str">
+        <v>Por</v>
+      </c>
+      <c r="H520" s="2">
+        <v>0</v>
+      </c>
+      <c r="I520" s="2">
+        <v>0</v>
+      </c>
+      <c r="J520" s="2">
+        <v>0</v>
+      </c>
+      <c r="K520" s="2">
+        <v>1</v>
+      </c>
+      <c r="L520" s="2">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="521">
+      <c r="A521" s="2">
+        <v>4</v>
+      </c>
+      <c r="B521" s="2" t="str">
+        <v>Sportiello</v>
+      </c>
+      <c r="C521" s="2" t="str">
+        <v/>
+      </c>
+      <c r="D521" s="2" t="str">
+        <v>Atalanta</v>
+      </c>
+      <c r="E521" s="2">
+        <v>34</v>
+      </c>
+      <c r="F521" s="2" t="str">
+        <v>P</v>
+      </c>
+      <c r="G521" s="2" t="str">
+        <v>Por</v>
+      </c>
+      <c r="H521" s="2">
+        <v>0</v>
+      </c>
+      <c r="I521" s="2">
+        <v>0</v>
+      </c>
+      <c r="J521" s="2">
+        <v>0</v>
+      </c>
+      <c r="K521" s="2">
+        <v>1</v>
+      </c>
+      <c r="L521" s="2">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="522">
+      <c r="A522" s="2">
+        <v>3</v>
+      </c>
+      <c r="B522" s="2" t="str">
+        <v>Radunovic</v>
+      </c>
+      <c r="C522" s="2" t="str">
+        <v/>
+      </c>
+      <c r="D522" s="2" t="str">
+        <v>Cagliari</v>
+      </c>
+      <c r="E522" s="2">
+        <v>30</v>
+      </c>
+      <c r="F522" s="2" t="str">
+        <v>P</v>
+      </c>
+      <c r="G522" s="2" t="str">
+        <v>Por</v>
+      </c>
+      <c r="H522" s="2">
+        <v>0</v>
+      </c>
+      <c r="I522" s="2">
+        <v>0</v>
+      </c>
+      <c r="J522" s="2">
+        <v>0</v>
+      </c>
+      <c r="K522" s="2">
+        <v>1</v>
+      </c>
+      <c r="L522" s="2">
+        <v>1</v>
+      </c>
+    </row>
   </sheetData>
   <ignoredErrors>
-    <ignoredError numberStoredAsText="1" sqref="A1:N514"/>
+    <ignoredError numberStoredAsText="1" sqref="A1:L522"/>
   </ignoredErrors>
 </worksheet>
 </file>